--- a/График_отпусков_2027.xlsx
+++ b/График_отпусков_2027.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
   <si>
     <t xml:space="preserve">График отпусков 2027 — по дням</t>
   </si>
@@ -4190,1467 +4190,1467 @@
         <v>55</v>
       </c>
       <c r="C7" s="9" t="n">
-        <f aca="false">SUMIF(Отпуска!$A$5:$A$17,$A7,Отпуска!$C$5:$C$17)</f>
+        <f aca="false">SUMIF(Отпуска!$A$5:$A$16,$A7,Отпуска!$C$5:$C$16)</f>
         <v>55</v>
       </c>
       <c r="D7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=D$5)*(Отпуска!$D$5:$D$17&gt;=D$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=D$5)*(Отпуска!$D$5:$D$16&gt;=D$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="E7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=E$5)*(Отпуска!$D$5:$D$17&gt;=E$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=E$5)*(Отпуска!$D$5:$D$16&gt;=E$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="F7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=F$5)*(Отпуска!$D$5:$D$17&gt;=F$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=F$5)*(Отпуска!$D$5:$D$16&gt;=F$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="G7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=G$5)*(Отпуска!$D$5:$D$17&gt;=G$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=G$5)*(Отпуска!$D$5:$D$16&gt;=G$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="H7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=H$5)*(Отпуска!$D$5:$D$17&gt;=H$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=H$5)*(Отпуска!$D$5:$D$16&gt;=H$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="I7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=I$5)*(Отпуска!$D$5:$D$17&gt;=I$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=I$5)*(Отпуска!$D$5:$D$16&gt;=I$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="J7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=J$5)*(Отпуска!$D$5:$D$17&gt;=J$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=J$5)*(Отпуска!$D$5:$D$16&gt;=J$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="K7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=K$5)*(Отпуска!$D$5:$D$17&gt;=K$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=K$5)*(Отпуска!$D$5:$D$16&gt;=K$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="L7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=L$5)*(Отпуска!$D$5:$D$17&gt;=L$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=L$5)*(Отпуска!$D$5:$D$16&gt;=L$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="M7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=M$5)*(Отпуска!$D$5:$D$17&gt;=M$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=M$5)*(Отпуска!$D$5:$D$16&gt;=M$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="N7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=N$5)*(Отпуска!$D$5:$D$17&gt;=N$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=N$5)*(Отпуска!$D$5:$D$16&gt;=N$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="O7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=O$5)*(Отпуска!$D$5:$D$17&gt;=O$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=O$5)*(Отпуска!$D$5:$D$16&gt;=O$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="P7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=P$5)*(Отпуска!$D$5:$D$17&gt;=P$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=P$5)*(Отпуска!$D$5:$D$16&gt;=P$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="Q7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=Q$5)*(Отпуска!$D$5:$D$17&gt;=Q$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=Q$5)*(Отпуска!$D$5:$D$16&gt;=Q$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="R7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=R$5)*(Отпуска!$D$5:$D$17&gt;=R$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=R$5)*(Отпуска!$D$5:$D$16&gt;=R$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="S7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=S$5)*(Отпуска!$D$5:$D$17&gt;=S$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=S$5)*(Отпуска!$D$5:$D$16&gt;=S$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="T7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=T$5)*(Отпуска!$D$5:$D$17&gt;=T$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=T$5)*(Отпуска!$D$5:$D$16&gt;=T$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="U7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=U$5)*(Отпуска!$D$5:$D$17&gt;=U$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=U$5)*(Отпуска!$D$5:$D$16&gt;=U$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="V7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=V$5)*(Отпуска!$D$5:$D$17&gt;=V$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=V$5)*(Отпуска!$D$5:$D$16&gt;=V$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="W7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=W$5)*(Отпуска!$D$5:$D$17&gt;=W$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=W$5)*(Отпуска!$D$5:$D$16&gt;=W$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="X7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=X$5)*(Отпуска!$D$5:$D$17&gt;=X$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=X$5)*(Отпуска!$D$5:$D$16&gt;=X$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="Y7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=Y$5)*(Отпуска!$D$5:$D$17&gt;=Y$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=Y$5)*(Отпуска!$D$5:$D$16&gt;=Y$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="Z7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=Z$5)*(Отпуска!$D$5:$D$17&gt;=Z$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=Z$5)*(Отпуска!$D$5:$D$16&gt;=Z$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AA7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AA$5)*(Отпуска!$D$5:$D$17&gt;=AA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AA$5)*(Отпуска!$D$5:$D$16&gt;=AA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AB7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AB$5)*(Отпуска!$D$5:$D$17&gt;=AB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AB$5)*(Отпуска!$D$5:$D$16&gt;=AB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AC7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AC$5)*(Отпуска!$D$5:$D$17&gt;=AC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AC$5)*(Отпуска!$D$5:$D$16&gt;=AC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AD7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AD$5)*(Отпуска!$D$5:$D$17&gt;=AD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AD$5)*(Отпуска!$D$5:$D$16&gt;=AD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AE7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AE$5)*(Отпуска!$D$5:$D$17&gt;=AE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AE$5)*(Отпуска!$D$5:$D$16&gt;=AE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AF7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AF$5)*(Отпуска!$D$5:$D$17&gt;=AF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AF$5)*(Отпуска!$D$5:$D$16&gt;=AF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AG7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AG$5)*(Отпуска!$D$5:$D$17&gt;=AG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AG$5)*(Отпуска!$D$5:$D$16&gt;=AG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AH7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AH$5)*(Отпуска!$D$5:$D$17&gt;=AH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AH$5)*(Отпуска!$D$5:$D$16&gt;=AH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AI7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AI$5)*(Отпуска!$D$5:$D$17&gt;=AI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AI$5)*(Отпуска!$D$5:$D$16&gt;=AI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AJ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AJ$5)*(Отпуска!$D$5:$D$17&gt;=AJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AJ$5)*(Отпуска!$D$5:$D$16&gt;=AJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AK7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AK$5)*(Отпуска!$D$5:$D$17&gt;=AK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AK$5)*(Отпуска!$D$5:$D$16&gt;=AK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AL7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AL$5)*(Отпуска!$D$5:$D$17&gt;=AL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AL$5)*(Отпуска!$D$5:$D$16&gt;=AL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AM7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AM$5)*(Отпуска!$D$5:$D$17&gt;=AM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AM$5)*(Отпуска!$D$5:$D$16&gt;=AM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AN7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AN$5)*(Отпуска!$D$5:$D$17&gt;=AN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AN$5)*(Отпуска!$D$5:$D$16&gt;=AN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AO7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AO$5)*(Отпуска!$D$5:$D$17&gt;=AO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AO$5)*(Отпуска!$D$5:$D$16&gt;=AO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AP7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AP$5)*(Отпуска!$D$5:$D$17&gt;=AP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AP$5)*(Отпуска!$D$5:$D$16&gt;=AP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AQ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AQ$5)*(Отпуска!$D$5:$D$17&gt;=AQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AQ$5)*(Отпуска!$D$5:$D$16&gt;=AQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AR7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AR$5)*(Отпуска!$D$5:$D$17&gt;=AR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AR$5)*(Отпуска!$D$5:$D$16&gt;=AR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AS7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AS$5)*(Отпуска!$D$5:$D$17&gt;=AS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AS$5)*(Отпуска!$D$5:$D$16&gt;=AS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AT7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AT$5)*(Отпуска!$D$5:$D$17&gt;=AT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AT$5)*(Отпуска!$D$5:$D$16&gt;=AT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AU7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AU$5)*(Отпуска!$D$5:$D$17&gt;=AU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AU$5)*(Отпуска!$D$5:$D$16&gt;=AU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AV7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AV$5)*(Отпуска!$D$5:$D$17&gt;=AV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AV$5)*(Отпуска!$D$5:$D$16&gt;=AV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AW7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AW$5)*(Отпуска!$D$5:$D$17&gt;=AW$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AW$5)*(Отпуска!$D$5:$D$16&gt;=AW$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="AX7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AX$5)*(Отпуска!$D$5:$D$17&gt;=AX$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AX$5)*(Отпуска!$D$5:$D$16&gt;=AX$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="AY7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AY$5)*(Отпуска!$D$5:$D$17&gt;=AY$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AY$5)*(Отпуска!$D$5:$D$16&gt;=AY$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="AZ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=AZ$5)*(Отпуска!$D$5:$D$17&gt;=AZ$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=AZ$5)*(Отпуска!$D$5:$D$16&gt;=AZ$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="BA7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BA$5)*(Отпуска!$D$5:$D$17&gt;=BA$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BA$5)*(Отпуска!$D$5:$D$16&gt;=BA$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="BB7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BB$5)*(Отпуска!$D$5:$D$17&gt;=BB$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BB$5)*(Отпуска!$D$5:$D$16&gt;=BB$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="BC7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BC$5)*(Отпуска!$D$5:$D$17&gt;=BC$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BC$5)*(Отпуска!$D$5:$D$16&gt;=BC$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="BD7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BD$5)*(Отпуска!$D$5:$D$17&gt;=BD$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BD$5)*(Отпуска!$D$5:$D$16&gt;=BD$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="BE7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BE$5)*(Отпуска!$D$5:$D$17&gt;=BE$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BE$5)*(Отпуска!$D$5:$D$16&gt;=BE$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="BF7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BF$5)*(Отпуска!$D$5:$D$17&gt;=BF$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BF$5)*(Отпуска!$D$5:$D$16&gt;=BF$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="BG7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BG$5)*(Отпуска!$D$5:$D$17&gt;=BG$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BG$5)*(Отпуска!$D$5:$D$16&gt;=BG$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="BH7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BH$5)*(Отпуска!$D$5:$D$17&gt;=BH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BH$5)*(Отпуска!$D$5:$D$16&gt;=BH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BI7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BI$5)*(Отпуска!$D$5:$D$17&gt;=BI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BI$5)*(Отпуска!$D$5:$D$16&gt;=BI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BJ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BJ$5)*(Отпуска!$D$5:$D$17&gt;=BJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BJ$5)*(Отпуска!$D$5:$D$16&gt;=BJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BK7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BK$5)*(Отпуска!$D$5:$D$17&gt;=BK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BK$5)*(Отпуска!$D$5:$D$16&gt;=BK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BL7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BL$5)*(Отпуска!$D$5:$D$17&gt;=BL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BL$5)*(Отпуска!$D$5:$D$16&gt;=BL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BM7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BM$5)*(Отпуска!$D$5:$D$17&gt;=BM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BM$5)*(Отпуска!$D$5:$D$16&gt;=BM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BN7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BN$5)*(Отпуска!$D$5:$D$17&gt;=BN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BN$5)*(Отпуска!$D$5:$D$16&gt;=BN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BO7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BO$5)*(Отпуска!$D$5:$D$17&gt;=BO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BO$5)*(Отпуска!$D$5:$D$16&gt;=BO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BP7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BP$5)*(Отпуска!$D$5:$D$17&gt;=BP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BP$5)*(Отпуска!$D$5:$D$16&gt;=BP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BQ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BQ$5)*(Отпуска!$D$5:$D$17&gt;=BQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BQ$5)*(Отпуска!$D$5:$D$16&gt;=BQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BR7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BR$5)*(Отпуска!$D$5:$D$17&gt;=BR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BR$5)*(Отпуска!$D$5:$D$16&gt;=BR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BS7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BS$5)*(Отпуска!$D$5:$D$17&gt;=BS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BS$5)*(Отпуска!$D$5:$D$16&gt;=BS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BT7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BT$5)*(Отпуска!$D$5:$D$17&gt;=BT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BT$5)*(Отпуска!$D$5:$D$16&gt;=BT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BU7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BU$5)*(Отпуска!$D$5:$D$17&gt;=BU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BU$5)*(Отпуска!$D$5:$D$16&gt;=BU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BV7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BV$5)*(Отпуска!$D$5:$D$17&gt;=BV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BV$5)*(Отпуска!$D$5:$D$16&gt;=BV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BW7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BW$5)*(Отпуска!$D$5:$D$17&gt;=BW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BW$5)*(Отпуска!$D$5:$D$16&gt;=BW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BX7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BX$5)*(Отпуска!$D$5:$D$17&gt;=BX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BX$5)*(Отпуска!$D$5:$D$16&gt;=BX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BY7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BY$5)*(Отпуска!$D$5:$D$17&gt;=BY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BY$5)*(Отпуска!$D$5:$D$16&gt;=BY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BZ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=BZ$5)*(Отпуска!$D$5:$D$17&gt;=BZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=BZ$5)*(Отпуска!$D$5:$D$16&gt;=BZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CA7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CA$5)*(Отпуска!$D$5:$D$17&gt;=CA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CA$5)*(Отпуска!$D$5:$D$16&gt;=CA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CB7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CB$5)*(Отпуска!$D$5:$D$17&gt;=CB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CB$5)*(Отпуска!$D$5:$D$16&gt;=CB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CC7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CC$5)*(Отпуска!$D$5:$D$17&gt;=CC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CC$5)*(Отпуска!$D$5:$D$16&gt;=CC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CD7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CD$5)*(Отпуска!$D$5:$D$17&gt;=CD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CD$5)*(Отпуска!$D$5:$D$16&gt;=CD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CE7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CE$5)*(Отпуска!$D$5:$D$17&gt;=CE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CE$5)*(Отпуска!$D$5:$D$16&gt;=CE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CF7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CF$5)*(Отпуска!$D$5:$D$17&gt;=CF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CF$5)*(Отпуска!$D$5:$D$16&gt;=CF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CG7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CG$5)*(Отпуска!$D$5:$D$17&gt;=CG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CG$5)*(Отпуска!$D$5:$D$16&gt;=CG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CH7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CH$5)*(Отпуска!$D$5:$D$17&gt;=CH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CH$5)*(Отпуска!$D$5:$D$16&gt;=CH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CI7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CI$5)*(Отпуска!$D$5:$D$17&gt;=CI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CI$5)*(Отпуска!$D$5:$D$16&gt;=CI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CJ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CJ$5)*(Отпуска!$D$5:$D$17&gt;=CJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CJ$5)*(Отпуска!$D$5:$D$16&gt;=CJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CK7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CK$5)*(Отпуска!$D$5:$D$17&gt;=CK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CK$5)*(Отпуска!$D$5:$D$16&gt;=CK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CL7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CL$5)*(Отпуска!$D$5:$D$17&gt;=CL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CL$5)*(Отпуска!$D$5:$D$16&gt;=CL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CM7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CM$5)*(Отпуска!$D$5:$D$17&gt;=CM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CM$5)*(Отпуска!$D$5:$D$16&gt;=CM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CN7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CN$5)*(Отпуска!$D$5:$D$17&gt;=CN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CN$5)*(Отпуска!$D$5:$D$16&gt;=CN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CO7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CO$5)*(Отпуска!$D$5:$D$17&gt;=CO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CO$5)*(Отпуска!$D$5:$D$16&gt;=CO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CP7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CP$5)*(Отпуска!$D$5:$D$17&gt;=CP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CP$5)*(Отпуска!$D$5:$D$16&gt;=CP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CQ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CQ$5)*(Отпуска!$D$5:$D$17&gt;=CQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CQ$5)*(Отпуска!$D$5:$D$16&gt;=CQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CR7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CR$5)*(Отпуска!$D$5:$D$17&gt;=CR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CR$5)*(Отпуска!$D$5:$D$16&gt;=CR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CS7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CS$5)*(Отпуска!$D$5:$D$17&gt;=CS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CS$5)*(Отпуска!$D$5:$D$16&gt;=CS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CT7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CT$5)*(Отпуска!$D$5:$D$17&gt;=CT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CT$5)*(Отпуска!$D$5:$D$16&gt;=CT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CU7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CU$5)*(Отпуска!$D$5:$D$17&gt;=CU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CU$5)*(Отпуска!$D$5:$D$16&gt;=CU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CV7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CV$5)*(Отпуска!$D$5:$D$17&gt;=CV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CV$5)*(Отпуска!$D$5:$D$16&gt;=CV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CW7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CW$5)*(Отпуска!$D$5:$D$17&gt;=CW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CW$5)*(Отпуска!$D$5:$D$16&gt;=CW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CX7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CX$5)*(Отпуска!$D$5:$D$17&gt;=CX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CX$5)*(Отпуска!$D$5:$D$16&gt;=CX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CY7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CY$5)*(Отпуска!$D$5:$D$17&gt;=CY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CY$5)*(Отпуска!$D$5:$D$16&gt;=CY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CZ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=CZ$5)*(Отпуска!$D$5:$D$17&gt;=CZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=CZ$5)*(Отпуска!$D$5:$D$16&gt;=CZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DA7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DA$5)*(Отпуска!$D$5:$D$17&gt;=DA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DA$5)*(Отпуска!$D$5:$D$16&gt;=DA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DB7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DB$5)*(Отпуска!$D$5:$D$17&gt;=DB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DB$5)*(Отпуска!$D$5:$D$16&gt;=DB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DC7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DC$5)*(Отпуска!$D$5:$D$17&gt;=DC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DC$5)*(Отпуска!$D$5:$D$16&gt;=DC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DD7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DD$5)*(Отпуска!$D$5:$D$17&gt;=DD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DD$5)*(Отпуска!$D$5:$D$16&gt;=DD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DE7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DE$5)*(Отпуска!$D$5:$D$17&gt;=DE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DE$5)*(Отпуска!$D$5:$D$16&gt;=DE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DF7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DF$5)*(Отпуска!$D$5:$D$17&gt;=DF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DF$5)*(Отпуска!$D$5:$D$16&gt;=DF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DG7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DG$5)*(Отпуска!$D$5:$D$17&gt;=DG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DG$5)*(Отпуска!$D$5:$D$16&gt;=DG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DH7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DH$5)*(Отпуска!$D$5:$D$17&gt;=DH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DH$5)*(Отпуска!$D$5:$D$16&gt;=DH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DI7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DI$5)*(Отпуска!$D$5:$D$17&gt;=DI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DI$5)*(Отпуска!$D$5:$D$16&gt;=DI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DJ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DJ$5)*(Отпуска!$D$5:$D$17&gt;=DJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DJ$5)*(Отпуска!$D$5:$D$16&gt;=DJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DK7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DK$5)*(Отпуска!$D$5:$D$17&gt;=DK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DK$5)*(Отпуска!$D$5:$D$16&gt;=DK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DL7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DL$5)*(Отпуска!$D$5:$D$17&gt;=DL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DL$5)*(Отпуска!$D$5:$D$16&gt;=DL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DM7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DM$5)*(Отпуска!$D$5:$D$17&gt;=DM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DM$5)*(Отпуска!$D$5:$D$16&gt;=DM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DN7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DN$5)*(Отпуска!$D$5:$D$17&gt;=DN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DN$5)*(Отпуска!$D$5:$D$16&gt;=DN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DO7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DO$5)*(Отпуска!$D$5:$D$17&gt;=DO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DO$5)*(Отпуска!$D$5:$D$16&gt;=DO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DP7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DP$5)*(Отпуска!$D$5:$D$17&gt;=DP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DP$5)*(Отпуска!$D$5:$D$16&gt;=DP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DQ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DQ$5)*(Отпуска!$D$5:$D$17&gt;=DQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DQ$5)*(Отпуска!$D$5:$D$16&gt;=DQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DR7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DR$5)*(Отпуска!$D$5:$D$17&gt;=DR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DR$5)*(Отпуска!$D$5:$D$16&gt;=DR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DS7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DS$5)*(Отпуска!$D$5:$D$17&gt;=DS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DS$5)*(Отпуска!$D$5:$D$16&gt;=DS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DT7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DT$5)*(Отпуска!$D$5:$D$17&gt;=DT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DT$5)*(Отпуска!$D$5:$D$16&gt;=DT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DU7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DU$5)*(Отпуска!$D$5:$D$17&gt;=DU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DU$5)*(Отпуска!$D$5:$D$16&gt;=DU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DV7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DV$5)*(Отпуска!$D$5:$D$17&gt;=DV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DV$5)*(Отпуска!$D$5:$D$16&gt;=DV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DW7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DW$5)*(Отпуска!$D$5:$D$17&gt;=DW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DW$5)*(Отпуска!$D$5:$D$16&gt;=DW$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="DX7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DX$5)*(Отпуска!$D$5:$D$17&gt;=DX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DX$5)*(Отпуска!$D$5:$D$16&gt;=DX$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="DY7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DY$5)*(Отпуска!$D$5:$D$17&gt;=DY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DY$5)*(Отпуска!$D$5:$D$16&gt;=DY$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="DZ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=DZ$5)*(Отпуска!$D$5:$D$17&gt;=DZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=DZ$5)*(Отпуска!$D$5:$D$16&gt;=DZ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="EA7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EA$5)*(Отпуска!$D$5:$D$17&gt;=EA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EA$5)*(Отпуска!$D$5:$D$16&gt;=EA$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="EB7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EB$5)*(Отпуска!$D$5:$D$17&gt;=EB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EB$5)*(Отпуска!$D$5:$D$16&gt;=EB$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="EC7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EC$5)*(Отпуска!$D$5:$D$17&gt;=EC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EC$5)*(Отпуска!$D$5:$D$16&gt;=EC$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="ED7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=ED$5)*(Отпуска!$D$5:$D$17&gt;=ED$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=ED$5)*(Отпуска!$D$5:$D$16&gt;=ED$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="EE7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EE$5)*(Отпуска!$D$5:$D$17&gt;=EE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EE$5)*(Отпуска!$D$5:$D$16&gt;=EE$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="EF7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EF$5)*(Отпуска!$D$5:$D$17&gt;=EF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EF$5)*(Отпуска!$D$5:$D$16&gt;=EF$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="EG7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EG$5)*(Отпуска!$D$5:$D$17&gt;=EG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EG$5)*(Отпуска!$D$5:$D$16&gt;=EG$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="EH7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EH$5)*(Отпуска!$D$5:$D$17&gt;=EH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EH$5)*(Отпуска!$D$5:$D$16&gt;=EH$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="EI7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EI$5)*(Отпуска!$D$5:$D$17&gt;=EI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EI$5)*(Отпуска!$D$5:$D$16&gt;=EI$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="EJ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EJ$5)*(Отпуска!$D$5:$D$17&gt;=EJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EJ$5)*(Отпуска!$D$5:$D$16&gt;=EJ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="EK7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EK$5)*(Отпуска!$D$5:$D$17&gt;=EK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EK$5)*(Отпуска!$D$5:$D$16&gt;=EK$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="EL7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EL$5)*(Отпуска!$D$5:$D$17&gt;=EL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EL$5)*(Отпуска!$D$5:$D$16&gt;=EL$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="EM7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EM$5)*(Отпуска!$D$5:$D$17&gt;=EM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EM$5)*(Отпуска!$D$5:$D$16&gt;=EM$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="EN7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EN$5)*(Отпуска!$D$5:$D$17&gt;=EN$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EN$5)*(Отпуска!$D$5:$D$16&gt;=EN$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="EO7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EO$5)*(Отпуска!$D$5:$D$17&gt;=EO$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EO$5)*(Отпуска!$D$5:$D$16&gt;=EO$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="EP7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EP$5)*(Отпуска!$D$5:$D$17&gt;=EP$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EP$5)*(Отпуска!$D$5:$D$16&gt;=EP$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="EQ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EQ$5)*(Отпуска!$D$5:$D$17&gt;=EQ$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EQ$5)*(Отпуска!$D$5:$D$16&gt;=EQ$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="ER7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=ER$5)*(Отпуска!$D$5:$D$17&gt;=ER$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=ER$5)*(Отпуска!$D$5:$D$16&gt;=ER$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="ES7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=ES$5)*(Отпуска!$D$5:$D$17&gt;=ES$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=ES$5)*(Отпуска!$D$5:$D$16&gt;=ES$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="ET7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=ET$5)*(Отпуска!$D$5:$D$17&gt;=ET$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=ET$5)*(Отпуска!$D$5:$D$16&gt;=ET$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="EU7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EU$5)*(Отпуска!$D$5:$D$17&gt;=EU$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EU$5)*(Отпуска!$D$5:$D$16&gt;=EU$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="EV7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EV$5)*(Отпуска!$D$5:$D$17&gt;=EV$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EV$5)*(Отпуска!$D$5:$D$16&gt;=EV$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="EW7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EW$5)*(Отпуска!$D$5:$D$17&gt;=EW$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EW$5)*(Отпуска!$D$5:$D$16&gt;=EW$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="EX7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EX$5)*(Отпуска!$D$5:$D$17&gt;=EX$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EX$5)*(Отпуска!$D$5:$D$16&gt;=EX$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="EY7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EY$5)*(Отпуска!$D$5:$D$17&gt;=EY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EY$5)*(Отпуска!$D$5:$D$16&gt;=EY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EZ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=EZ$5)*(Отпуска!$D$5:$D$17&gt;=EZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=EZ$5)*(Отпуска!$D$5:$D$16&gt;=EZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FA7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FA$5)*(Отпуска!$D$5:$D$17&gt;=FA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FA$5)*(Отпуска!$D$5:$D$16&gt;=FA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FB7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FB$5)*(Отпуска!$D$5:$D$17&gt;=FB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FB$5)*(Отпуска!$D$5:$D$16&gt;=FB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FC7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FC$5)*(Отпуска!$D$5:$D$17&gt;=FC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FC$5)*(Отпуска!$D$5:$D$16&gt;=FC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FD7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FD$5)*(Отпуска!$D$5:$D$17&gt;=FD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FD$5)*(Отпуска!$D$5:$D$16&gt;=FD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FE7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FE$5)*(Отпуска!$D$5:$D$17&gt;=FE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FE$5)*(Отпуска!$D$5:$D$16&gt;=FE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FF7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FF$5)*(Отпуска!$D$5:$D$17&gt;=FF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FF$5)*(Отпуска!$D$5:$D$16&gt;=FF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FG7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FG$5)*(Отпуска!$D$5:$D$17&gt;=FG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FG$5)*(Отпуска!$D$5:$D$16&gt;=FG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FH7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FH$5)*(Отпуска!$D$5:$D$17&gt;=FH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FH$5)*(Отпуска!$D$5:$D$16&gt;=FH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FI7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FI$5)*(Отпуска!$D$5:$D$17&gt;=FI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FI$5)*(Отпуска!$D$5:$D$16&gt;=FI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FJ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FJ$5)*(Отпуска!$D$5:$D$17&gt;=FJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FJ$5)*(Отпуска!$D$5:$D$16&gt;=FJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FK7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FK$5)*(Отпуска!$D$5:$D$17&gt;=FK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FK$5)*(Отпуска!$D$5:$D$16&gt;=FK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FL7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FL$5)*(Отпуска!$D$5:$D$17&gt;=FL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FL$5)*(Отпуска!$D$5:$D$16&gt;=FL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FM7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FM$5)*(Отпуска!$D$5:$D$17&gt;=FM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FM$5)*(Отпуска!$D$5:$D$16&gt;=FM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FN7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FN$5)*(Отпуска!$D$5:$D$17&gt;=FN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FN$5)*(Отпуска!$D$5:$D$16&gt;=FN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FO7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FO$5)*(Отпуска!$D$5:$D$17&gt;=FO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FO$5)*(Отпуска!$D$5:$D$16&gt;=FO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FP7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FP$5)*(Отпуска!$D$5:$D$17&gt;=FP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FP$5)*(Отпуска!$D$5:$D$16&gt;=FP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FQ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FQ$5)*(Отпуска!$D$5:$D$17&gt;=FQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FQ$5)*(Отпуска!$D$5:$D$16&gt;=FQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FR7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FR$5)*(Отпуска!$D$5:$D$17&gt;=FR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FR$5)*(Отпуска!$D$5:$D$16&gt;=FR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FS7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FS$5)*(Отпуска!$D$5:$D$17&gt;=FS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FS$5)*(Отпуска!$D$5:$D$16&gt;=FS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FT7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FT$5)*(Отпуска!$D$5:$D$17&gt;=FT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FT$5)*(Отпуска!$D$5:$D$16&gt;=FT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FU7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FU$5)*(Отпуска!$D$5:$D$17&gt;=FU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FU$5)*(Отпуска!$D$5:$D$16&gt;=FU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FV7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FV$5)*(Отпуска!$D$5:$D$17&gt;=FV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FV$5)*(Отпуска!$D$5:$D$16&gt;=FV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FW7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FW$5)*(Отпуска!$D$5:$D$17&gt;=FW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FW$5)*(Отпуска!$D$5:$D$16&gt;=FW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FX7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FX$5)*(Отпуска!$D$5:$D$17&gt;=FX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FX$5)*(Отпуска!$D$5:$D$16&gt;=FX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FY7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FY$5)*(Отпуска!$D$5:$D$17&gt;=FY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FY$5)*(Отпуска!$D$5:$D$16&gt;=FY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FZ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=FZ$5)*(Отпуска!$D$5:$D$17&gt;=FZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=FZ$5)*(Отпуска!$D$5:$D$16&gt;=FZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GA7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GA$5)*(Отпуска!$D$5:$D$17&gt;=GA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GA$5)*(Отпуска!$D$5:$D$16&gt;=GA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GB7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GB$5)*(Отпуска!$D$5:$D$17&gt;=GB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GB$5)*(Отпуска!$D$5:$D$16&gt;=GB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GC7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GC$5)*(Отпуска!$D$5:$D$17&gt;=GC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GC$5)*(Отпуска!$D$5:$D$16&gt;=GC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GD7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GD$5)*(Отпуска!$D$5:$D$17&gt;=GD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GD$5)*(Отпуска!$D$5:$D$16&gt;=GD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GE7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GE$5)*(Отпуска!$D$5:$D$17&gt;=GE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GE$5)*(Отпуска!$D$5:$D$16&gt;=GE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GF7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GF$5)*(Отпуска!$D$5:$D$17&gt;=GF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GF$5)*(Отпуска!$D$5:$D$16&gt;=GF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GG7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GG$5)*(Отпуска!$D$5:$D$17&gt;=GG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GG$5)*(Отпуска!$D$5:$D$16&gt;=GG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GH7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GH$5)*(Отпуска!$D$5:$D$17&gt;=GH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GH$5)*(Отпуска!$D$5:$D$16&gt;=GH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GI7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GI$5)*(Отпуска!$D$5:$D$17&gt;=GI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GI$5)*(Отпуска!$D$5:$D$16&gt;=GI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GJ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GJ$5)*(Отпуска!$D$5:$D$17&gt;=GJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GJ$5)*(Отпуска!$D$5:$D$16&gt;=GJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GK7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GK$5)*(Отпуска!$D$5:$D$17&gt;=GK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GK$5)*(Отпуска!$D$5:$D$16&gt;=GK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GL7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GL$5)*(Отпуска!$D$5:$D$17&gt;=GL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GL$5)*(Отпуска!$D$5:$D$16&gt;=GL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GM7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GM$5)*(Отпуска!$D$5:$D$17&gt;=GM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GM$5)*(Отпуска!$D$5:$D$16&gt;=GM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GN7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GN$5)*(Отпуска!$D$5:$D$17&gt;=GN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GN$5)*(Отпуска!$D$5:$D$16&gt;=GN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GO7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GO$5)*(Отпуска!$D$5:$D$17&gt;=GO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GO$5)*(Отпуска!$D$5:$D$16&gt;=GO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GP7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GP$5)*(Отпуска!$D$5:$D$17&gt;=GP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GP$5)*(Отпуска!$D$5:$D$16&gt;=GP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GQ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GQ$5)*(Отпуска!$D$5:$D$17&gt;=GQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GQ$5)*(Отпуска!$D$5:$D$16&gt;=GQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GR7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GR$5)*(Отпуска!$D$5:$D$17&gt;=GR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GR$5)*(Отпуска!$D$5:$D$16&gt;=GR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GS7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GS$5)*(Отпуска!$D$5:$D$17&gt;=GS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GS$5)*(Отпуска!$D$5:$D$16&gt;=GS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GT7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GT$5)*(Отпуска!$D$5:$D$17&gt;=GT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GT$5)*(Отпуска!$D$5:$D$16&gt;=GT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GU7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GU$5)*(Отпуска!$D$5:$D$17&gt;=GU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GU$5)*(Отпуска!$D$5:$D$16&gt;=GU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GV7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GV$5)*(Отпуска!$D$5:$D$17&gt;=GV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GV$5)*(Отпуска!$D$5:$D$16&gt;=GV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GW7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GW$5)*(Отпуска!$D$5:$D$17&gt;=GW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GW$5)*(Отпуска!$D$5:$D$16&gt;=GW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GX7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GX$5)*(Отпуска!$D$5:$D$17&gt;=GX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GX$5)*(Отпуска!$D$5:$D$16&gt;=GX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GY7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GY$5)*(Отпуска!$D$5:$D$17&gt;=GY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GY$5)*(Отпуска!$D$5:$D$16&gt;=GY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GZ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=GZ$5)*(Отпуска!$D$5:$D$17&gt;=GZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=GZ$5)*(Отпуска!$D$5:$D$16&gt;=GZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HA7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HA$5)*(Отпуска!$D$5:$D$17&gt;=HA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HA$5)*(Отпуска!$D$5:$D$16&gt;=HA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HB7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HB$5)*(Отпуска!$D$5:$D$17&gt;=HB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HB$5)*(Отпуска!$D$5:$D$16&gt;=HB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HC7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HC$5)*(Отпуска!$D$5:$D$17&gt;=HC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HC$5)*(Отпуска!$D$5:$D$16&gt;=HC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HD7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HD$5)*(Отпуска!$D$5:$D$17&gt;=HD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HD$5)*(Отпуска!$D$5:$D$16&gt;=HD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HE7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HE$5)*(Отпуска!$D$5:$D$17&gt;=HE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HE$5)*(Отпуска!$D$5:$D$16&gt;=HE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HF7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HF$5)*(Отпуска!$D$5:$D$17&gt;=HF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HF$5)*(Отпуска!$D$5:$D$16&gt;=HF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HG7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HG$5)*(Отпуска!$D$5:$D$17&gt;=HG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HG$5)*(Отпуска!$D$5:$D$16&gt;=HG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HH7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HH$5)*(Отпуска!$D$5:$D$17&gt;=HH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HH$5)*(Отпуска!$D$5:$D$16&gt;=HH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HI7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HI$5)*(Отпуска!$D$5:$D$17&gt;=HI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HI$5)*(Отпуска!$D$5:$D$16&gt;=HI$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HJ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HJ$5)*(Отпуска!$D$5:$D$17&gt;=HJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HJ$5)*(Отпуска!$D$5:$D$16&gt;=HJ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HK7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HK$5)*(Отпуска!$D$5:$D$17&gt;=HK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HK$5)*(Отпуска!$D$5:$D$16&gt;=HK$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HL7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HL$5)*(Отпуска!$D$5:$D$17&gt;=HL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HL$5)*(Отпуска!$D$5:$D$16&gt;=HL$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HM7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HM$5)*(Отпуска!$D$5:$D$17&gt;=HM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HM$5)*(Отпуска!$D$5:$D$16&gt;=HM$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HN7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HN$5)*(Отпуска!$D$5:$D$17&gt;=HN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HN$5)*(Отпуска!$D$5:$D$16&gt;=HN$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HO7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HO$5)*(Отпуска!$D$5:$D$17&gt;=HO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HO$5)*(Отпуска!$D$5:$D$16&gt;=HO$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HP7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HP$5)*(Отпуска!$D$5:$D$17&gt;=HP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HP$5)*(Отпуска!$D$5:$D$16&gt;=HP$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HQ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HQ$5)*(Отпуска!$D$5:$D$17&gt;=HQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HQ$5)*(Отпуска!$D$5:$D$16&gt;=HQ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HR7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HR$5)*(Отпуска!$D$5:$D$17&gt;=HR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HR$5)*(Отпуска!$D$5:$D$16&gt;=HR$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HS7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HS$5)*(Отпуска!$D$5:$D$17&gt;=HS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HS$5)*(Отпуска!$D$5:$D$16&gt;=HS$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HT7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HT$5)*(Отпуска!$D$5:$D$17&gt;=HT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HT$5)*(Отпуска!$D$5:$D$16&gt;=HT$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HU7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HU$5)*(Отпуска!$D$5:$D$17&gt;=HU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HU$5)*(Отпуска!$D$5:$D$16&gt;=HU$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HV7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HV$5)*(Отпуска!$D$5:$D$17&gt;=HV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HV$5)*(Отпуска!$D$5:$D$16&gt;=HV$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HW7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HW$5)*(Отпуска!$D$5:$D$17&gt;=HW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HW$5)*(Отпуска!$D$5:$D$16&gt;=HW$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HX7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HX$5)*(Отпуска!$D$5:$D$17&gt;=HX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HX$5)*(Отпуска!$D$5:$D$16&gt;=HX$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HY7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HY$5)*(Отпуска!$D$5:$D$17&gt;=HY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HY$5)*(Отпуска!$D$5:$D$16&gt;=HY$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HZ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=HZ$5)*(Отпуска!$D$5:$D$17&gt;=HZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=HZ$5)*(Отпуска!$D$5:$D$16&gt;=HZ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="IA7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IA$5)*(Отпуска!$D$5:$D$17&gt;=IA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IA$5)*(Отпуска!$D$5:$D$16&gt;=IA$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="IB7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IB$5)*(Отпуска!$D$5:$D$17&gt;=IB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IB$5)*(Отпуска!$D$5:$D$16&gt;=IB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IC7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IC$5)*(Отпуска!$D$5:$D$17&gt;=IC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IC$5)*(Отпуска!$D$5:$D$16&gt;=IC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ID7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=ID$5)*(Отпуска!$D$5:$D$17&gt;=ID$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=ID$5)*(Отпуска!$D$5:$D$16&gt;=ID$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IE7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IE$5)*(Отпуска!$D$5:$D$17&gt;=IE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IE$5)*(Отпуска!$D$5:$D$16&gt;=IE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IF7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IF$5)*(Отпуска!$D$5:$D$17&gt;=IF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IF$5)*(Отпуска!$D$5:$D$16&gt;=IF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IG7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IG$5)*(Отпуска!$D$5:$D$17&gt;=IG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IG$5)*(Отпуска!$D$5:$D$16&gt;=IG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IH7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IH$5)*(Отпуска!$D$5:$D$17&gt;=IH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IH$5)*(Отпуска!$D$5:$D$16&gt;=IH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="II7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=II$5)*(Отпуска!$D$5:$D$17&gt;=II$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=II$5)*(Отпуска!$D$5:$D$16&gt;=II$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IJ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IJ$5)*(Отпуска!$D$5:$D$17&gt;=IJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IJ$5)*(Отпуска!$D$5:$D$16&gt;=IJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IK7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IK$5)*(Отпуска!$D$5:$D$17&gt;=IK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IK$5)*(Отпуска!$D$5:$D$16&gt;=IK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IL7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IL$5)*(Отпуска!$D$5:$D$17&gt;=IL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IL$5)*(Отпуска!$D$5:$D$16&gt;=IL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IM7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IM$5)*(Отпуска!$D$5:$D$17&gt;=IM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IM$5)*(Отпуска!$D$5:$D$16&gt;=IM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IN7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IN$5)*(Отпуска!$D$5:$D$17&gt;=IN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IN$5)*(Отпуска!$D$5:$D$16&gt;=IN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IO7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IO$5)*(Отпуска!$D$5:$D$17&gt;=IO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IO$5)*(Отпуска!$D$5:$D$16&gt;=IO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IP7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IP$5)*(Отпуска!$D$5:$D$17&gt;=IP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IP$5)*(Отпуска!$D$5:$D$16&gt;=IP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IQ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IQ$5)*(Отпуска!$D$5:$D$17&gt;=IQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IQ$5)*(Отпуска!$D$5:$D$16&gt;=IQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IR7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IR$5)*(Отпуска!$D$5:$D$17&gt;=IR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IR$5)*(Отпуска!$D$5:$D$16&gt;=IR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IS7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IS$5)*(Отпуска!$D$5:$D$17&gt;=IS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IS$5)*(Отпуска!$D$5:$D$16&gt;=IS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IT7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IT$5)*(Отпуска!$D$5:$D$17&gt;=IT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IT$5)*(Отпуска!$D$5:$D$16&gt;=IT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IU7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IU$5)*(Отпуска!$D$5:$D$17&gt;=IU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IU$5)*(Отпуска!$D$5:$D$16&gt;=IU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IV7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IV$5)*(Отпуска!$D$5:$D$17&gt;=IV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IV$5)*(Отпуска!$D$5:$D$16&gt;=IV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IW7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IW$5)*(Отпуска!$D$5:$D$17&gt;=IW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IW$5)*(Отпуска!$D$5:$D$16&gt;=IW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IX7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IX$5)*(Отпуска!$D$5:$D$17&gt;=IX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IX$5)*(Отпуска!$D$5:$D$16&gt;=IX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IY7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IY$5)*(Отпуска!$D$5:$D$17&gt;=IY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IY$5)*(Отпуска!$D$5:$D$16&gt;=IY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IZ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=IZ$5)*(Отпуска!$D$5:$D$17&gt;=IZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=IZ$5)*(Отпуска!$D$5:$D$16&gt;=IZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JA7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JA$5)*(Отпуска!$D$5:$D$17&gt;=JA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JA$5)*(Отпуска!$D$5:$D$16&gt;=JA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JB7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JB$5)*(Отпуска!$D$5:$D$17&gt;=JB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JB$5)*(Отпуска!$D$5:$D$16&gt;=JB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JC7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JC$5)*(Отпуска!$D$5:$D$17&gt;=JC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JC$5)*(Отпуска!$D$5:$D$16&gt;=JC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JD7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JD$5)*(Отпуска!$D$5:$D$17&gt;=JD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JD$5)*(Отпуска!$D$5:$D$16&gt;=JD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JE7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JE$5)*(Отпуска!$D$5:$D$17&gt;=JE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JE$5)*(Отпуска!$D$5:$D$16&gt;=JE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JF7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JF$5)*(Отпуска!$D$5:$D$17&gt;=JF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JF$5)*(Отпуска!$D$5:$D$16&gt;=JF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JG7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JG$5)*(Отпуска!$D$5:$D$17&gt;=JG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JG$5)*(Отпуска!$D$5:$D$16&gt;=JG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JH7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JH$5)*(Отпуска!$D$5:$D$17&gt;=JH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JH$5)*(Отпуска!$D$5:$D$16&gt;=JH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JI7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JI$5)*(Отпуска!$D$5:$D$17&gt;=JI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JI$5)*(Отпуска!$D$5:$D$16&gt;=JI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JJ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JJ$5)*(Отпуска!$D$5:$D$17&gt;=JJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JJ$5)*(Отпуска!$D$5:$D$16&gt;=JJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JK7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JK$5)*(Отпуска!$D$5:$D$17&gt;=JK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JK$5)*(Отпуска!$D$5:$D$16&gt;=JK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JL7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JL$5)*(Отпуска!$D$5:$D$17&gt;=JL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JL$5)*(Отпуска!$D$5:$D$16&gt;=JL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JM7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JM$5)*(Отпуска!$D$5:$D$17&gt;=JM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JM$5)*(Отпуска!$D$5:$D$16&gt;=JM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JN7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JN$5)*(Отпуска!$D$5:$D$17&gt;=JN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JN$5)*(Отпуска!$D$5:$D$16&gt;=JN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JO7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JO$5)*(Отпуска!$D$5:$D$17&gt;=JO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JO$5)*(Отпуска!$D$5:$D$16&gt;=JO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JP7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JP$5)*(Отпуска!$D$5:$D$17&gt;=JP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JP$5)*(Отпуска!$D$5:$D$16&gt;=JP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JQ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JQ$5)*(Отпуска!$D$5:$D$17&gt;=JQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JQ$5)*(Отпуска!$D$5:$D$16&gt;=JQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JR7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JR$5)*(Отпуска!$D$5:$D$17&gt;=JR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JR$5)*(Отпуска!$D$5:$D$16&gt;=JR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JS7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JS$5)*(Отпуска!$D$5:$D$17&gt;=JS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JS$5)*(Отпуска!$D$5:$D$16&gt;=JS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JT7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JT$5)*(Отпуска!$D$5:$D$17&gt;=JT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JT$5)*(Отпуска!$D$5:$D$16&gt;=JT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JU7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JU$5)*(Отпуска!$D$5:$D$17&gt;=JU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JU$5)*(Отпуска!$D$5:$D$16&gt;=JU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JV7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JV$5)*(Отпуска!$D$5:$D$17&gt;=JV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JV$5)*(Отпуска!$D$5:$D$16&gt;=JV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JW7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JW$5)*(Отпуска!$D$5:$D$17&gt;=JW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JW$5)*(Отпуска!$D$5:$D$16&gt;=JW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JX7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JX$5)*(Отпуска!$D$5:$D$17&gt;=JX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JX$5)*(Отпуска!$D$5:$D$16&gt;=JX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JY7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JY$5)*(Отпуска!$D$5:$D$17&gt;=JY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JY$5)*(Отпуска!$D$5:$D$16&gt;=JY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JZ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=JZ$5)*(Отпуска!$D$5:$D$17&gt;=JZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=JZ$5)*(Отпуска!$D$5:$D$16&gt;=JZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KA7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KA$5)*(Отпуска!$D$5:$D$17&gt;=KA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KA$5)*(Отпуска!$D$5:$D$16&gt;=KA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KB7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KB$5)*(Отпуска!$D$5:$D$17&gt;=KB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KB$5)*(Отпуска!$D$5:$D$16&gt;=KB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KC7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KC$5)*(Отпуска!$D$5:$D$17&gt;=KC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KC$5)*(Отпуска!$D$5:$D$16&gt;=KC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KD7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KD$5)*(Отпуска!$D$5:$D$17&gt;=KD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KD$5)*(Отпуска!$D$5:$D$16&gt;=KD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KE7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KE$5)*(Отпуска!$D$5:$D$17&gt;=KE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KE$5)*(Отпуска!$D$5:$D$16&gt;=KE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KF7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KF$5)*(Отпуска!$D$5:$D$17&gt;=KF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KF$5)*(Отпуска!$D$5:$D$16&gt;=KF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KG7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KG$5)*(Отпуска!$D$5:$D$17&gt;=KG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KG$5)*(Отпуска!$D$5:$D$16&gt;=KG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KH7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KH$5)*(Отпуска!$D$5:$D$17&gt;=KH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KH$5)*(Отпуска!$D$5:$D$16&gt;=KH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KI7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KI$5)*(Отпуска!$D$5:$D$17&gt;=KI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KI$5)*(Отпуска!$D$5:$D$16&gt;=KI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KJ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KJ$5)*(Отпуска!$D$5:$D$17&gt;=KJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KJ$5)*(Отпуска!$D$5:$D$16&gt;=KJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KK7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KK$5)*(Отпуска!$D$5:$D$17&gt;=KK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KK$5)*(Отпуска!$D$5:$D$16&gt;=KK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KL7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KL$5)*(Отпуска!$D$5:$D$17&gt;=KL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KL$5)*(Отпуска!$D$5:$D$16&gt;=KL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KM7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KM$5)*(Отпуска!$D$5:$D$17&gt;=KM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KM$5)*(Отпуска!$D$5:$D$16&gt;=KM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KN7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KN$5)*(Отпуска!$D$5:$D$17&gt;=KN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KN$5)*(Отпуска!$D$5:$D$16&gt;=KN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KO7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KO$5)*(Отпуска!$D$5:$D$17&gt;=KO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KO$5)*(Отпуска!$D$5:$D$16&gt;=KO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KP7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KP$5)*(Отпуска!$D$5:$D$17&gt;=KP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KP$5)*(Отпуска!$D$5:$D$16&gt;=KP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KQ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KQ$5)*(Отпуска!$D$5:$D$17&gt;=KQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KQ$5)*(Отпуска!$D$5:$D$16&gt;=KQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KR7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KR$5)*(Отпуска!$D$5:$D$17&gt;=KR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KR$5)*(Отпуска!$D$5:$D$16&gt;=KR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KS7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KS$5)*(Отпуска!$D$5:$D$17&gt;=KS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KS$5)*(Отпуска!$D$5:$D$16&gt;=KS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KT7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KT$5)*(Отпуска!$D$5:$D$17&gt;=KT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KT$5)*(Отпуска!$D$5:$D$16&gt;=KT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KU7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KU$5)*(Отпуска!$D$5:$D$17&gt;=KU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KU$5)*(Отпуска!$D$5:$D$16&gt;=KU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KV7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KV$5)*(Отпуска!$D$5:$D$17&gt;=KV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KV$5)*(Отпуска!$D$5:$D$16&gt;=KV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KW7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KW$5)*(Отпуска!$D$5:$D$17&gt;=KW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KW$5)*(Отпуска!$D$5:$D$16&gt;=KW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KX7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KX$5)*(Отпуска!$D$5:$D$17&gt;=KX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KX$5)*(Отпуска!$D$5:$D$16&gt;=KX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KY7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KY$5)*(Отпуска!$D$5:$D$17&gt;=KY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KY$5)*(Отпуска!$D$5:$D$16&gt;=KY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KZ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=KZ$5)*(Отпуска!$D$5:$D$17&gt;=KZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=KZ$5)*(Отпуска!$D$5:$D$16&gt;=KZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LA7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LA$5)*(Отпуска!$D$5:$D$17&gt;=LA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LA$5)*(Отпуска!$D$5:$D$16&gt;=LA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LB7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LB$5)*(Отпуска!$D$5:$D$17&gt;=LB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LB$5)*(Отпуска!$D$5:$D$16&gt;=LB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LC7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LC$5)*(Отпуска!$D$5:$D$17&gt;=LC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LC$5)*(Отпуска!$D$5:$D$16&gt;=LC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LD7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LD$5)*(Отпуска!$D$5:$D$17&gt;=LD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LD$5)*(Отпуска!$D$5:$D$16&gt;=LD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LE7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LE$5)*(Отпуска!$D$5:$D$17&gt;=LE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LE$5)*(Отпуска!$D$5:$D$16&gt;=LE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LF7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LF$5)*(Отпуска!$D$5:$D$17&gt;=LF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LF$5)*(Отпуска!$D$5:$D$16&gt;=LF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LG7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LG$5)*(Отпуска!$D$5:$D$17&gt;=LG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LG$5)*(Отпуска!$D$5:$D$16&gt;=LG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LH7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LH$5)*(Отпуска!$D$5:$D$17&gt;=LH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LH$5)*(Отпуска!$D$5:$D$16&gt;=LH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LI7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LI$5)*(Отпуска!$D$5:$D$17&gt;=LI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LI$5)*(Отпуска!$D$5:$D$16&gt;=LI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LJ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LJ$5)*(Отпуска!$D$5:$D$17&gt;=LJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LJ$5)*(Отпуска!$D$5:$D$16&gt;=LJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LK7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LK$5)*(Отпуска!$D$5:$D$17&gt;=LK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LK$5)*(Отпуска!$D$5:$D$16&gt;=LK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LL7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LL$5)*(Отпуска!$D$5:$D$17&gt;=LL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LL$5)*(Отпуска!$D$5:$D$16&gt;=LL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LM7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LM$5)*(Отпуска!$D$5:$D$17&gt;=LM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LM$5)*(Отпуска!$D$5:$D$16&gt;=LM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LN7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LN$5)*(Отпуска!$D$5:$D$17&gt;=LN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LN$5)*(Отпуска!$D$5:$D$16&gt;=LN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LO7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LO$5)*(Отпуска!$D$5:$D$17&gt;=LO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LO$5)*(Отпуска!$D$5:$D$16&gt;=LO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LP7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LP$5)*(Отпуска!$D$5:$D$17&gt;=LP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LP$5)*(Отпуска!$D$5:$D$16&gt;=LP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LQ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LQ$5)*(Отпуска!$D$5:$D$17&gt;=LQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LQ$5)*(Отпуска!$D$5:$D$16&gt;=LQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LR7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LR$5)*(Отпуска!$D$5:$D$17&gt;=LR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LR$5)*(Отпуска!$D$5:$D$16&gt;=LR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LS7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LS$5)*(Отпуска!$D$5:$D$17&gt;=LS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LS$5)*(Отпуска!$D$5:$D$16&gt;=LS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LT7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LT$5)*(Отпуска!$D$5:$D$17&gt;=LT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LT$5)*(Отпуска!$D$5:$D$16&gt;=LT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LU7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LU$5)*(Отпуска!$D$5:$D$17&gt;=LU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LU$5)*(Отпуска!$D$5:$D$16&gt;=LU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LV7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LV$5)*(Отпуска!$D$5:$D$17&gt;=LV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LV$5)*(Отпуска!$D$5:$D$16&gt;=LV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LW7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LW$5)*(Отпуска!$D$5:$D$17&gt;=LW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LW$5)*(Отпуска!$D$5:$D$16&gt;=LW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LX7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LX$5)*(Отпуска!$D$5:$D$17&gt;=LX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LX$5)*(Отпуска!$D$5:$D$16&gt;=LX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LY7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LY$5)*(Отпуска!$D$5:$D$17&gt;=LY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LY$5)*(Отпуска!$D$5:$D$16&gt;=LY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LZ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=LZ$5)*(Отпуска!$D$5:$D$17&gt;=LZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=LZ$5)*(Отпуска!$D$5:$D$16&gt;=LZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MA7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MA$5)*(Отпуска!$D$5:$D$17&gt;=MA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MA$5)*(Отпуска!$D$5:$D$16&gt;=MA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MB7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MB$5)*(Отпуска!$D$5:$D$17&gt;=MB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MB$5)*(Отпуска!$D$5:$D$16&gt;=MB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MC7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MC$5)*(Отпуска!$D$5:$D$17&gt;=MC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MC$5)*(Отпуска!$D$5:$D$16&gt;=MC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MD7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MD$5)*(Отпуска!$D$5:$D$17&gt;=MD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MD$5)*(Отпуска!$D$5:$D$16&gt;=MD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ME7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=ME$5)*(Отпуска!$D$5:$D$17&gt;=ME$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=ME$5)*(Отпуска!$D$5:$D$16&gt;=ME$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MF7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MF$5)*(Отпуска!$D$5:$D$17&gt;=MF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MF$5)*(Отпуска!$D$5:$D$16&gt;=MF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MG7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MG$5)*(Отпуска!$D$5:$D$17&gt;=MG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MG$5)*(Отпуска!$D$5:$D$16&gt;=MG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MH7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MH$5)*(Отпуска!$D$5:$D$17&gt;=MH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MH$5)*(Отпуска!$D$5:$D$16&gt;=MH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MI7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MI$5)*(Отпуска!$D$5:$D$17&gt;=MI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MI$5)*(Отпуска!$D$5:$D$16&gt;=MI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MJ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MJ$5)*(Отпуска!$D$5:$D$17&gt;=MJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MJ$5)*(Отпуска!$D$5:$D$16&gt;=MJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MK7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MK$5)*(Отпуска!$D$5:$D$17&gt;=MK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MK$5)*(Отпуска!$D$5:$D$16&gt;=MK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ML7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=ML$5)*(Отпуска!$D$5:$D$17&gt;=ML$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=ML$5)*(Отпуска!$D$5:$D$16&gt;=ML$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MM7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MM$5)*(Отпуска!$D$5:$D$17&gt;=MM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MM$5)*(Отпуска!$D$5:$D$16&gt;=MM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MN7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MN$5)*(Отпуска!$D$5:$D$17&gt;=MN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MN$5)*(Отпуска!$D$5:$D$16&gt;=MN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MO7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MO$5)*(Отпуска!$D$5:$D$17&gt;=MO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MO$5)*(Отпуска!$D$5:$D$16&gt;=MO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MP7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MP$5)*(Отпуска!$D$5:$D$17&gt;=MP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MP$5)*(Отпуска!$D$5:$D$16&gt;=MP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MQ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MQ$5)*(Отпуска!$D$5:$D$17&gt;=MQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MQ$5)*(Отпуска!$D$5:$D$16&gt;=MQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MR7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MR$5)*(Отпуска!$D$5:$D$17&gt;=MR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MR$5)*(Отпуска!$D$5:$D$16&gt;=MR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MS7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MS$5)*(Отпуска!$D$5:$D$17&gt;=MS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MS$5)*(Отпуска!$D$5:$D$16&gt;=MS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MT7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MT$5)*(Отпуска!$D$5:$D$17&gt;=MT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MT$5)*(Отпуска!$D$5:$D$16&gt;=MT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MU7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MU$5)*(Отпуска!$D$5:$D$17&gt;=MU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MU$5)*(Отпуска!$D$5:$D$16&gt;=MU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MV7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MV$5)*(Отпуска!$D$5:$D$17&gt;=MV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MV$5)*(Отпуска!$D$5:$D$16&gt;=MV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MW7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MW$5)*(Отпуска!$D$5:$D$17&gt;=MW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MW$5)*(Отпуска!$D$5:$D$16&gt;=MW$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="MX7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MX$5)*(Отпуска!$D$5:$D$17&gt;=MX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MX$5)*(Отпуска!$D$5:$D$16&gt;=MX$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="MY7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MY$5)*(Отпуска!$D$5:$D$17&gt;=MY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MY$5)*(Отпуска!$D$5:$D$16&gt;=MY$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="MZ7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=MZ$5)*(Отпуска!$D$5:$D$17&gt;=MZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=MZ$5)*(Отпуска!$D$5:$D$16&gt;=MZ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="NA7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=NA$5)*(Отпуска!$D$5:$D$17&gt;=NA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=NA$5)*(Отпуска!$D$5:$D$16&gt;=NA$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="NB7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=NB$5)*(Отпуска!$D$5:$D$17&gt;=NB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=NB$5)*(Отпуска!$D$5:$D$16&gt;=NB$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="NC7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=NC$5)*(Отпуска!$D$5:$D$17&gt;=NC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=NC$5)*(Отпуска!$D$5:$D$16&gt;=NC$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="ND7" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A7)*(Отпуска!$B$5:$B$17&lt;=ND$5)*(Отпуска!$D$5:$D$17&gt;=ND$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A7)*(Отпуска!$B$5:$B$16&lt;=ND$5)*(Отпуска!$D$5:$D$16&gt;=ND$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
     </row>
@@ -5663,1467 +5663,1467 @@
         <v>55</v>
       </c>
       <c r="C8" s="9" t="n">
-        <f aca="false">SUMIF(Отпуска!$A$5:$A$17,$A8,Отпуска!$C$5:$C$17)</f>
+        <f aca="false">SUMIF(Отпуска!$A$5:$A$16,$A8,Отпуска!$C$5:$C$16)</f>
         <v>55</v>
       </c>
       <c r="D8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=D$5)*(Отпуска!$D$5:$D$17&gt;=D$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=D$5)*(Отпуска!$D$5:$D$16&gt;=D$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="E8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=E$5)*(Отпуска!$D$5:$D$17&gt;=E$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=E$5)*(Отпуска!$D$5:$D$16&gt;=E$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="F8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=F$5)*(Отпуска!$D$5:$D$17&gt;=F$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=F$5)*(Отпуска!$D$5:$D$16&gt;=F$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="G8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=G$5)*(Отпуска!$D$5:$D$17&gt;=G$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=G$5)*(Отпуска!$D$5:$D$16&gt;=G$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="H8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=H$5)*(Отпуска!$D$5:$D$17&gt;=H$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=H$5)*(Отпуска!$D$5:$D$16&gt;=H$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="I8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=I$5)*(Отпуска!$D$5:$D$17&gt;=I$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=I$5)*(Отпуска!$D$5:$D$16&gt;=I$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="J8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=J$5)*(Отпуска!$D$5:$D$17&gt;=J$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=J$5)*(Отпуска!$D$5:$D$16&gt;=J$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="K8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=K$5)*(Отпуска!$D$5:$D$17&gt;=K$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=K$5)*(Отпуска!$D$5:$D$16&gt;=K$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="L8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=L$5)*(Отпуска!$D$5:$D$17&gt;=L$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=L$5)*(Отпуска!$D$5:$D$16&gt;=L$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="M8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=M$5)*(Отпуска!$D$5:$D$17&gt;=M$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=M$5)*(Отпуска!$D$5:$D$16&gt;=M$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="N8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=N$5)*(Отпуска!$D$5:$D$17&gt;=N$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=N$5)*(Отпуска!$D$5:$D$16&gt;=N$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="O8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=O$5)*(Отпуска!$D$5:$D$17&gt;=O$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=O$5)*(Отпуска!$D$5:$D$16&gt;=O$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="P8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=P$5)*(Отпуска!$D$5:$D$17&gt;=P$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=P$5)*(Отпуска!$D$5:$D$16&gt;=P$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="Q8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=Q$5)*(Отпуска!$D$5:$D$17&gt;=Q$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=Q$5)*(Отпуска!$D$5:$D$16&gt;=Q$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="R8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=R$5)*(Отпуска!$D$5:$D$17&gt;=R$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=R$5)*(Отпуска!$D$5:$D$16&gt;=R$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="S8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=S$5)*(Отпуска!$D$5:$D$17&gt;=S$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=S$5)*(Отпуска!$D$5:$D$16&gt;=S$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="T8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=T$5)*(Отпуска!$D$5:$D$17&gt;=T$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=T$5)*(Отпуска!$D$5:$D$16&gt;=T$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="U8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=U$5)*(Отпуска!$D$5:$D$17&gt;=U$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=U$5)*(Отпуска!$D$5:$D$16&gt;=U$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="V8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=V$5)*(Отпуска!$D$5:$D$17&gt;=V$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=V$5)*(Отпуска!$D$5:$D$16&gt;=V$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="W8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=W$5)*(Отпуска!$D$5:$D$17&gt;=W$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=W$5)*(Отпуска!$D$5:$D$16&gt;=W$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="X8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=X$5)*(Отпуска!$D$5:$D$17&gt;=X$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=X$5)*(Отпуска!$D$5:$D$16&gt;=X$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="Y8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=Y$5)*(Отпуска!$D$5:$D$17&gt;=Y$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=Y$5)*(Отпуска!$D$5:$D$16&gt;=Y$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="Z8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=Z$5)*(Отпуска!$D$5:$D$17&gt;=Z$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=Z$5)*(Отпуска!$D$5:$D$16&gt;=Z$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AA8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AA$5)*(Отпуска!$D$5:$D$17&gt;=AA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AA$5)*(Отпуска!$D$5:$D$16&gt;=AA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AB8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AB$5)*(Отпуска!$D$5:$D$17&gt;=AB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AB$5)*(Отпуска!$D$5:$D$16&gt;=AB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AC8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AC$5)*(Отпуска!$D$5:$D$17&gt;=AC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AC$5)*(Отпуска!$D$5:$D$16&gt;=AC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AD8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AD$5)*(Отпуска!$D$5:$D$17&gt;=AD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AD$5)*(Отпуска!$D$5:$D$16&gt;=AD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AE8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AE$5)*(Отпуска!$D$5:$D$17&gt;=AE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AE$5)*(Отпуска!$D$5:$D$16&gt;=AE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AF8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AF$5)*(Отпуска!$D$5:$D$17&gt;=AF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AF$5)*(Отпуска!$D$5:$D$16&gt;=AF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AG8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AG$5)*(Отпуска!$D$5:$D$17&gt;=AG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AG$5)*(Отпуска!$D$5:$D$16&gt;=AG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AH8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AH$5)*(Отпуска!$D$5:$D$17&gt;=AH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AH$5)*(Отпуска!$D$5:$D$16&gt;=AH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AI8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AI$5)*(Отпуска!$D$5:$D$17&gt;=AI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AI$5)*(Отпуска!$D$5:$D$16&gt;=AI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AJ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AJ$5)*(Отпуска!$D$5:$D$17&gt;=AJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AJ$5)*(Отпуска!$D$5:$D$16&gt;=AJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AK8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AK$5)*(Отпуска!$D$5:$D$17&gt;=AK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AK$5)*(Отпуска!$D$5:$D$16&gt;=AK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AL8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AL$5)*(Отпуска!$D$5:$D$17&gt;=AL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AL$5)*(Отпуска!$D$5:$D$16&gt;=AL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AM8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AM$5)*(Отпуска!$D$5:$D$17&gt;=AM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AM$5)*(Отпуска!$D$5:$D$16&gt;=AM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AN8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AN$5)*(Отпуска!$D$5:$D$17&gt;=AN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AN$5)*(Отпуска!$D$5:$D$16&gt;=AN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AO8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AO$5)*(Отпуска!$D$5:$D$17&gt;=AO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AO$5)*(Отпуска!$D$5:$D$16&gt;=AO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AP8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AP$5)*(Отпуска!$D$5:$D$17&gt;=AP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AP$5)*(Отпуска!$D$5:$D$16&gt;=AP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AQ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AQ$5)*(Отпуска!$D$5:$D$17&gt;=AQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AQ$5)*(Отпуска!$D$5:$D$16&gt;=AQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AR8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AR$5)*(Отпуска!$D$5:$D$17&gt;=AR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AR$5)*(Отпуска!$D$5:$D$16&gt;=AR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AS8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AS$5)*(Отпуска!$D$5:$D$17&gt;=AS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AS$5)*(Отпуска!$D$5:$D$16&gt;=AS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AT8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AT$5)*(Отпуска!$D$5:$D$17&gt;=AT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AT$5)*(Отпуска!$D$5:$D$16&gt;=AT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AU8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AU$5)*(Отпуска!$D$5:$D$17&gt;=AU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AU$5)*(Отпуска!$D$5:$D$16&gt;=AU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AV8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AV$5)*(Отпуска!$D$5:$D$17&gt;=AV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AV$5)*(Отпуска!$D$5:$D$16&gt;=AV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AW8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AW$5)*(Отпуска!$D$5:$D$17&gt;=AW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AW$5)*(Отпуска!$D$5:$D$16&gt;=AW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AX8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AX$5)*(Отпуска!$D$5:$D$17&gt;=AX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AX$5)*(Отпуска!$D$5:$D$16&gt;=AX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AY8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AY$5)*(Отпуска!$D$5:$D$17&gt;=AY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AY$5)*(Отпуска!$D$5:$D$16&gt;=AY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AZ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=AZ$5)*(Отпуска!$D$5:$D$17&gt;=AZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=AZ$5)*(Отпуска!$D$5:$D$16&gt;=AZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BA8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BA$5)*(Отпуска!$D$5:$D$17&gt;=BA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BA$5)*(Отпуска!$D$5:$D$16&gt;=BA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BB8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BB$5)*(Отпуска!$D$5:$D$17&gt;=BB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BB$5)*(Отпуска!$D$5:$D$16&gt;=BB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BC8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BC$5)*(Отпуска!$D$5:$D$17&gt;=BC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BC$5)*(Отпуска!$D$5:$D$16&gt;=BC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BD8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BD$5)*(Отпуска!$D$5:$D$17&gt;=BD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BD$5)*(Отпуска!$D$5:$D$16&gt;=BD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BE8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BE$5)*(Отпуска!$D$5:$D$17&gt;=BE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BE$5)*(Отпуска!$D$5:$D$16&gt;=BE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BF8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BF$5)*(Отпуска!$D$5:$D$17&gt;=BF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BF$5)*(Отпуска!$D$5:$D$16&gt;=BF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BG8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BG$5)*(Отпуска!$D$5:$D$17&gt;=BG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BG$5)*(Отпуска!$D$5:$D$16&gt;=BG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BH8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BH$5)*(Отпуска!$D$5:$D$17&gt;=BH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BH$5)*(Отпуска!$D$5:$D$16&gt;=BH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BI8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BI$5)*(Отпуска!$D$5:$D$17&gt;=BI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BI$5)*(Отпуска!$D$5:$D$16&gt;=BI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BJ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BJ$5)*(Отпуска!$D$5:$D$17&gt;=BJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BJ$5)*(Отпуска!$D$5:$D$16&gt;=BJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BK8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BK$5)*(Отпуска!$D$5:$D$17&gt;=BK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BK$5)*(Отпуска!$D$5:$D$16&gt;=BK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BL8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BL$5)*(Отпуска!$D$5:$D$17&gt;=BL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BL$5)*(Отпуска!$D$5:$D$16&gt;=BL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BM8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BM$5)*(Отпуска!$D$5:$D$17&gt;=BM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BM$5)*(Отпуска!$D$5:$D$16&gt;=BM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BN8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BN$5)*(Отпуска!$D$5:$D$17&gt;=BN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BN$5)*(Отпуска!$D$5:$D$16&gt;=BN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BO8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BO$5)*(Отпуска!$D$5:$D$17&gt;=BO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BO$5)*(Отпуска!$D$5:$D$16&gt;=BO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BP8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BP$5)*(Отпуска!$D$5:$D$17&gt;=BP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BP$5)*(Отпуска!$D$5:$D$16&gt;=BP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BQ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BQ$5)*(Отпуска!$D$5:$D$17&gt;=BQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BQ$5)*(Отпуска!$D$5:$D$16&gt;=BQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BR8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BR$5)*(Отпуска!$D$5:$D$17&gt;=BR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BR$5)*(Отпуска!$D$5:$D$16&gt;=BR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BS8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BS$5)*(Отпуска!$D$5:$D$17&gt;=BS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BS$5)*(Отпуска!$D$5:$D$16&gt;=BS$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="BT8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BT$5)*(Отпуска!$D$5:$D$17&gt;=BT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BT$5)*(Отпуска!$D$5:$D$16&gt;=BT$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="BU8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BU$5)*(Отпуска!$D$5:$D$17&gt;=BU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BU$5)*(Отпуска!$D$5:$D$16&gt;=BU$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="BV8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BV$5)*(Отпуска!$D$5:$D$17&gt;=BV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BV$5)*(Отпуска!$D$5:$D$16&gt;=BV$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="BW8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BW$5)*(Отпуска!$D$5:$D$17&gt;=BW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BW$5)*(Отпуска!$D$5:$D$16&gt;=BW$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="BX8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BX$5)*(Отпуска!$D$5:$D$17&gt;=BX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BX$5)*(Отпуска!$D$5:$D$16&gt;=BX$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="BY8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BY$5)*(Отпуска!$D$5:$D$17&gt;=BY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BY$5)*(Отпуска!$D$5:$D$16&gt;=BY$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="BZ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=BZ$5)*(Отпуска!$D$5:$D$17&gt;=BZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=BZ$5)*(Отпуска!$D$5:$D$16&gt;=BZ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="CA8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CA$5)*(Отпуска!$D$5:$D$17&gt;=CA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CA$5)*(Отпуска!$D$5:$D$16&gt;=CA$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="CB8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CB$5)*(Отпуска!$D$5:$D$17&gt;=CB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CB$5)*(Отпуска!$D$5:$D$16&gt;=CB$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="CC8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CC$5)*(Отпуска!$D$5:$D$17&gt;=CC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CC$5)*(Отпуска!$D$5:$D$16&gt;=CC$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="CD8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CD$5)*(Отпуска!$D$5:$D$17&gt;=CD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CD$5)*(Отпуска!$D$5:$D$16&gt;=CD$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="CE8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CE$5)*(Отпуска!$D$5:$D$17&gt;=CE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CE$5)*(Отпуска!$D$5:$D$16&gt;=CE$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="CF8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CF$5)*(Отпуска!$D$5:$D$17&gt;=CF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CF$5)*(Отпуска!$D$5:$D$16&gt;=CF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CG8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CG$5)*(Отпуска!$D$5:$D$17&gt;=CG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CG$5)*(Отпуска!$D$5:$D$16&gt;=CG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CH8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CH$5)*(Отпуска!$D$5:$D$17&gt;=CH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CH$5)*(Отпуска!$D$5:$D$16&gt;=CH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CI8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CI$5)*(Отпуска!$D$5:$D$17&gt;=CI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CI$5)*(Отпуска!$D$5:$D$16&gt;=CI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CJ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CJ$5)*(Отпуска!$D$5:$D$17&gt;=CJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CJ$5)*(Отпуска!$D$5:$D$16&gt;=CJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CK8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CK$5)*(Отпуска!$D$5:$D$17&gt;=CK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CK$5)*(Отпуска!$D$5:$D$16&gt;=CK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CL8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CL$5)*(Отпуска!$D$5:$D$17&gt;=CL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CL$5)*(Отпуска!$D$5:$D$16&gt;=CL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CM8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CM$5)*(Отпуска!$D$5:$D$17&gt;=CM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CM$5)*(Отпуска!$D$5:$D$16&gt;=CM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CN8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CN$5)*(Отпуска!$D$5:$D$17&gt;=CN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CN$5)*(Отпуска!$D$5:$D$16&gt;=CN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CO8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CO$5)*(Отпуска!$D$5:$D$17&gt;=CO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CO$5)*(Отпуска!$D$5:$D$16&gt;=CO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CP8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CP$5)*(Отпуска!$D$5:$D$17&gt;=CP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CP$5)*(Отпуска!$D$5:$D$16&gt;=CP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CQ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CQ$5)*(Отпуска!$D$5:$D$17&gt;=CQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CQ$5)*(Отпуска!$D$5:$D$16&gt;=CQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CR8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CR$5)*(Отпуска!$D$5:$D$17&gt;=CR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CR$5)*(Отпуска!$D$5:$D$16&gt;=CR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CS8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CS$5)*(Отпуска!$D$5:$D$17&gt;=CS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CS$5)*(Отпуска!$D$5:$D$16&gt;=CS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CT8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CT$5)*(Отпуска!$D$5:$D$17&gt;=CT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CT$5)*(Отпуска!$D$5:$D$16&gt;=CT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CU8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CU$5)*(Отпуска!$D$5:$D$17&gt;=CU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CU$5)*(Отпуска!$D$5:$D$16&gt;=CU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CV8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CV$5)*(Отпуска!$D$5:$D$17&gt;=CV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CV$5)*(Отпуска!$D$5:$D$16&gt;=CV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CW8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CW$5)*(Отпуска!$D$5:$D$17&gt;=CW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CW$5)*(Отпуска!$D$5:$D$16&gt;=CW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CX8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CX$5)*(Отпуска!$D$5:$D$17&gt;=CX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CX$5)*(Отпуска!$D$5:$D$16&gt;=CX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CY8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CY$5)*(Отпуска!$D$5:$D$17&gt;=CY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CY$5)*(Отпуска!$D$5:$D$16&gt;=CY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CZ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=CZ$5)*(Отпуска!$D$5:$D$17&gt;=CZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=CZ$5)*(Отпуска!$D$5:$D$16&gt;=CZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DA8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DA$5)*(Отпуска!$D$5:$D$17&gt;=DA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DA$5)*(Отпуска!$D$5:$D$16&gt;=DA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DB8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DB$5)*(Отпуска!$D$5:$D$17&gt;=DB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DB$5)*(Отпуска!$D$5:$D$16&gt;=DB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DC8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DC$5)*(Отпуска!$D$5:$D$17&gt;=DC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DC$5)*(Отпуска!$D$5:$D$16&gt;=DC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DD8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DD$5)*(Отпуска!$D$5:$D$17&gt;=DD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DD$5)*(Отпуска!$D$5:$D$16&gt;=DD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DE8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DE$5)*(Отпуска!$D$5:$D$17&gt;=DE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DE$5)*(Отпуска!$D$5:$D$16&gt;=DE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DF8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DF$5)*(Отпуска!$D$5:$D$17&gt;=DF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DF$5)*(Отпуска!$D$5:$D$16&gt;=DF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DG8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DG$5)*(Отпуска!$D$5:$D$17&gt;=DG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DG$5)*(Отпуска!$D$5:$D$16&gt;=DG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DH8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DH$5)*(Отпуска!$D$5:$D$17&gt;=DH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DH$5)*(Отпуска!$D$5:$D$16&gt;=DH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DI8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DI$5)*(Отпуска!$D$5:$D$17&gt;=DI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DI$5)*(Отпуска!$D$5:$D$16&gt;=DI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DJ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DJ$5)*(Отпуска!$D$5:$D$17&gt;=DJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DJ$5)*(Отпуска!$D$5:$D$16&gt;=DJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DK8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DK$5)*(Отпуска!$D$5:$D$17&gt;=DK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DK$5)*(Отпуска!$D$5:$D$16&gt;=DK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DL8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DL$5)*(Отпуска!$D$5:$D$17&gt;=DL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DL$5)*(Отпуска!$D$5:$D$16&gt;=DL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DM8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DM$5)*(Отпуска!$D$5:$D$17&gt;=DM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DM$5)*(Отпуска!$D$5:$D$16&gt;=DM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DN8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DN$5)*(Отпуска!$D$5:$D$17&gt;=DN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DN$5)*(Отпуска!$D$5:$D$16&gt;=DN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DO8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DO$5)*(Отпуска!$D$5:$D$17&gt;=DO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DO$5)*(Отпуска!$D$5:$D$16&gt;=DO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DP8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DP$5)*(Отпуска!$D$5:$D$17&gt;=DP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DP$5)*(Отпуска!$D$5:$D$16&gt;=DP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DQ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DQ$5)*(Отпуска!$D$5:$D$17&gt;=DQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DQ$5)*(Отпуска!$D$5:$D$16&gt;=DQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DR8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DR$5)*(Отпуска!$D$5:$D$17&gt;=DR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DR$5)*(Отпуска!$D$5:$D$16&gt;=DR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DS8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DS$5)*(Отпуска!$D$5:$D$17&gt;=DS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DS$5)*(Отпуска!$D$5:$D$16&gt;=DS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DT8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DT$5)*(Отпуска!$D$5:$D$17&gt;=DT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DT$5)*(Отпуска!$D$5:$D$16&gt;=DT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DU8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DU$5)*(Отпуска!$D$5:$D$17&gt;=DU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DU$5)*(Отпуска!$D$5:$D$16&gt;=DU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DV8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DV$5)*(Отпуска!$D$5:$D$17&gt;=DV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DV$5)*(Отпуска!$D$5:$D$16&gt;=DV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DW8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DW$5)*(Отпуска!$D$5:$D$17&gt;=DW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DW$5)*(Отпуска!$D$5:$D$16&gt;=DW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DX8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DX$5)*(Отпуска!$D$5:$D$17&gt;=DX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DX$5)*(Отпуска!$D$5:$D$16&gt;=DX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DY8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DY$5)*(Отпуска!$D$5:$D$17&gt;=DY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DY$5)*(Отпуска!$D$5:$D$16&gt;=DY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DZ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=DZ$5)*(Отпуска!$D$5:$D$17&gt;=DZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=DZ$5)*(Отпуска!$D$5:$D$16&gt;=DZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EA8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EA$5)*(Отпуска!$D$5:$D$17&gt;=EA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EA$5)*(Отпуска!$D$5:$D$16&gt;=EA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EB8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EB$5)*(Отпуска!$D$5:$D$17&gt;=EB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EB$5)*(Отпуска!$D$5:$D$16&gt;=EB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EC8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EC$5)*(Отпуска!$D$5:$D$17&gt;=EC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EC$5)*(Отпуска!$D$5:$D$16&gt;=EC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ED8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=ED$5)*(Отпуска!$D$5:$D$17&gt;=ED$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=ED$5)*(Отпуска!$D$5:$D$16&gt;=ED$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EE8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EE$5)*(Отпуска!$D$5:$D$17&gt;=EE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EE$5)*(Отпуска!$D$5:$D$16&gt;=EE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EF8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EF$5)*(Отпуска!$D$5:$D$17&gt;=EF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EF$5)*(Отпуска!$D$5:$D$16&gt;=EF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EG8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EG$5)*(Отпуска!$D$5:$D$17&gt;=EG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EG$5)*(Отпуска!$D$5:$D$16&gt;=EG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EH8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EH$5)*(Отпуска!$D$5:$D$17&gt;=EH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EH$5)*(Отпуска!$D$5:$D$16&gt;=EH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EI8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EI$5)*(Отпуска!$D$5:$D$17&gt;=EI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EI$5)*(Отпуска!$D$5:$D$16&gt;=EI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EJ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EJ$5)*(Отпуска!$D$5:$D$17&gt;=EJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EJ$5)*(Отпуска!$D$5:$D$16&gt;=EJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EK8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EK$5)*(Отпуска!$D$5:$D$17&gt;=EK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EK$5)*(Отпуска!$D$5:$D$16&gt;=EK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EL8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EL$5)*(Отпуска!$D$5:$D$17&gt;=EL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EL$5)*(Отпуска!$D$5:$D$16&gt;=EL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EM8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EM$5)*(Отпуска!$D$5:$D$17&gt;=EM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EM$5)*(Отпуска!$D$5:$D$16&gt;=EM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EN8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EN$5)*(Отпуска!$D$5:$D$17&gt;=EN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EN$5)*(Отпуска!$D$5:$D$16&gt;=EN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EO8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EO$5)*(Отпуска!$D$5:$D$17&gt;=EO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EO$5)*(Отпуска!$D$5:$D$16&gt;=EO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EP8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EP$5)*(Отпуска!$D$5:$D$17&gt;=EP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EP$5)*(Отпуска!$D$5:$D$16&gt;=EP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EQ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EQ$5)*(Отпуска!$D$5:$D$17&gt;=EQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EQ$5)*(Отпуска!$D$5:$D$16&gt;=EQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ER8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=ER$5)*(Отпуска!$D$5:$D$17&gt;=ER$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=ER$5)*(Отпуска!$D$5:$D$16&gt;=ER$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ES8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=ES$5)*(Отпуска!$D$5:$D$17&gt;=ES$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=ES$5)*(Отпуска!$D$5:$D$16&gt;=ES$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ET8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=ET$5)*(Отпуска!$D$5:$D$17&gt;=ET$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=ET$5)*(Отпуска!$D$5:$D$16&gt;=ET$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EU8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EU$5)*(Отпуска!$D$5:$D$17&gt;=EU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EU$5)*(Отпуска!$D$5:$D$16&gt;=EU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EV8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EV$5)*(Отпуска!$D$5:$D$17&gt;=EV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EV$5)*(Отпуска!$D$5:$D$16&gt;=EV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EW8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EW$5)*(Отпуска!$D$5:$D$17&gt;=EW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EW$5)*(Отпуска!$D$5:$D$16&gt;=EW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EX8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EX$5)*(Отпуска!$D$5:$D$17&gt;=EX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EX$5)*(Отпуска!$D$5:$D$16&gt;=EX$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="EY8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EY$5)*(Отпуска!$D$5:$D$17&gt;=EY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EY$5)*(Отпуска!$D$5:$D$16&gt;=EY$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="EZ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=EZ$5)*(Отпуска!$D$5:$D$17&gt;=EZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=EZ$5)*(Отпуска!$D$5:$D$16&gt;=EZ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FA8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FA$5)*(Отпуска!$D$5:$D$17&gt;=FA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FA$5)*(Отпуска!$D$5:$D$16&gt;=FA$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FB8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FB$5)*(Отпуска!$D$5:$D$17&gt;=FB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FB$5)*(Отпуска!$D$5:$D$16&gt;=FB$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FC8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FC$5)*(Отпуска!$D$5:$D$17&gt;=FC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FC$5)*(Отпуска!$D$5:$D$16&gt;=FC$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FD8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FD$5)*(Отпуска!$D$5:$D$17&gt;=FD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FD$5)*(Отпуска!$D$5:$D$16&gt;=FD$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FE8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FE$5)*(Отпуска!$D$5:$D$17&gt;=FE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FE$5)*(Отпуска!$D$5:$D$16&gt;=FE$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FF8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FF$5)*(Отпуска!$D$5:$D$17&gt;=FF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FF$5)*(Отпуска!$D$5:$D$16&gt;=FF$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FG8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FG$5)*(Отпуска!$D$5:$D$17&gt;=FG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FG$5)*(Отпуска!$D$5:$D$16&gt;=FG$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FH8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FH$5)*(Отпуска!$D$5:$D$17&gt;=FH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FH$5)*(Отпуска!$D$5:$D$16&gt;=FH$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FI8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FI$5)*(Отпуска!$D$5:$D$17&gt;=FI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FI$5)*(Отпуска!$D$5:$D$16&gt;=FI$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FJ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FJ$5)*(Отпуска!$D$5:$D$17&gt;=FJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FJ$5)*(Отпуска!$D$5:$D$16&gt;=FJ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FK8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FK$5)*(Отпуска!$D$5:$D$17&gt;=FK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FK$5)*(Отпуска!$D$5:$D$16&gt;=FK$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FL8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FL$5)*(Отпуска!$D$5:$D$17&gt;=FL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FL$5)*(Отпуска!$D$5:$D$16&gt;=FL$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FM8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FM$5)*(Отпуска!$D$5:$D$17&gt;=FM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FM$5)*(Отпуска!$D$5:$D$16&gt;=FM$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FN8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FN$5)*(Отпуска!$D$5:$D$17&gt;=FN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FN$5)*(Отпуска!$D$5:$D$16&gt;=FN$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FO8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FO$5)*(Отпуска!$D$5:$D$17&gt;=FO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FO$5)*(Отпуска!$D$5:$D$16&gt;=FO$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FP8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FP$5)*(Отпуска!$D$5:$D$17&gt;=FP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FP$5)*(Отпуска!$D$5:$D$16&gt;=FP$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FQ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FQ$5)*(Отпуска!$D$5:$D$17&gt;=FQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FQ$5)*(Отпуска!$D$5:$D$16&gt;=FQ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FR8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FR$5)*(Отпуска!$D$5:$D$17&gt;=FR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FR$5)*(Отпуска!$D$5:$D$16&gt;=FR$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FS8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FS$5)*(Отпуска!$D$5:$D$17&gt;=FS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FS$5)*(Отпуска!$D$5:$D$16&gt;=FS$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FT8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FT$5)*(Отпуска!$D$5:$D$17&gt;=FT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FT$5)*(Отпуска!$D$5:$D$16&gt;=FT$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FU8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FU$5)*(Отпуска!$D$5:$D$17&gt;=FU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FU$5)*(Отпуска!$D$5:$D$16&gt;=FU$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FV8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FV$5)*(Отпуска!$D$5:$D$17&gt;=FV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FV$5)*(Отпуска!$D$5:$D$16&gt;=FV$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FW8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FW$5)*(Отпуска!$D$5:$D$17&gt;=FW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FW$5)*(Отпуска!$D$5:$D$16&gt;=FW$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FX8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FX$5)*(Отпуска!$D$5:$D$17&gt;=FX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FX$5)*(Отпуска!$D$5:$D$16&gt;=FX$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FY8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FY$5)*(Отпуска!$D$5:$D$17&gt;=FY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FY$5)*(Отпуска!$D$5:$D$16&gt;=FY$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FZ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=FZ$5)*(Отпуска!$D$5:$D$17&gt;=FZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=FZ$5)*(Отпуска!$D$5:$D$16&gt;=FZ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GA8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GA$5)*(Отпуска!$D$5:$D$17&gt;=GA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GA$5)*(Отпуска!$D$5:$D$16&gt;=GA$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GB8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GB$5)*(Отпуска!$D$5:$D$17&gt;=GB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GB$5)*(Отпуска!$D$5:$D$16&gt;=GB$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GC8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GC$5)*(Отпуска!$D$5:$D$17&gt;=GC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GC$5)*(Отпуска!$D$5:$D$16&gt;=GC$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GD8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GD$5)*(Отпуска!$D$5:$D$17&gt;=GD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GD$5)*(Отпуска!$D$5:$D$16&gt;=GD$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GE8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GE$5)*(Отпуска!$D$5:$D$17&gt;=GE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GE$5)*(Отпуска!$D$5:$D$16&gt;=GE$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GF8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GF$5)*(Отпуска!$D$5:$D$17&gt;=GF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GF$5)*(Отпуска!$D$5:$D$16&gt;=GF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GG8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GG$5)*(Отпуска!$D$5:$D$17&gt;=GG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GG$5)*(Отпуска!$D$5:$D$16&gt;=GG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GH8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GH$5)*(Отпуска!$D$5:$D$17&gt;=GH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GH$5)*(Отпуска!$D$5:$D$16&gt;=GH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GI8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GI$5)*(Отпуска!$D$5:$D$17&gt;=GI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GI$5)*(Отпуска!$D$5:$D$16&gt;=GI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GJ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GJ$5)*(Отпуска!$D$5:$D$17&gt;=GJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GJ$5)*(Отпуска!$D$5:$D$16&gt;=GJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GK8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GK$5)*(Отпуска!$D$5:$D$17&gt;=GK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GK$5)*(Отпуска!$D$5:$D$16&gt;=GK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GL8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GL$5)*(Отпуска!$D$5:$D$17&gt;=GL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GL$5)*(Отпуска!$D$5:$D$16&gt;=GL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GM8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GM$5)*(Отпуска!$D$5:$D$17&gt;=GM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GM$5)*(Отпуска!$D$5:$D$16&gt;=GM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GN8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GN$5)*(Отпуска!$D$5:$D$17&gt;=GN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GN$5)*(Отпуска!$D$5:$D$16&gt;=GN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GO8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GO$5)*(Отпуска!$D$5:$D$17&gt;=GO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GO$5)*(Отпуска!$D$5:$D$16&gt;=GO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GP8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GP$5)*(Отпуска!$D$5:$D$17&gt;=GP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GP$5)*(Отпуска!$D$5:$D$16&gt;=GP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GQ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GQ$5)*(Отпуска!$D$5:$D$17&gt;=GQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GQ$5)*(Отпуска!$D$5:$D$16&gt;=GQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GR8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GR$5)*(Отпуска!$D$5:$D$17&gt;=GR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GR$5)*(Отпуска!$D$5:$D$16&gt;=GR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GS8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GS$5)*(Отпуска!$D$5:$D$17&gt;=GS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GS$5)*(Отпуска!$D$5:$D$16&gt;=GS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GT8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GT$5)*(Отпуска!$D$5:$D$17&gt;=GT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GT$5)*(Отпуска!$D$5:$D$16&gt;=GT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GU8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GU$5)*(Отпуска!$D$5:$D$17&gt;=GU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GU$5)*(Отпуска!$D$5:$D$16&gt;=GU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GV8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GV$5)*(Отпуска!$D$5:$D$17&gt;=GV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GV$5)*(Отпуска!$D$5:$D$16&gt;=GV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GW8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GW$5)*(Отпуска!$D$5:$D$17&gt;=GW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GW$5)*(Отпуска!$D$5:$D$16&gt;=GW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GX8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GX$5)*(Отпуска!$D$5:$D$17&gt;=GX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GX$5)*(Отпуска!$D$5:$D$16&gt;=GX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GY8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GY$5)*(Отпуска!$D$5:$D$17&gt;=GY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GY$5)*(Отпуска!$D$5:$D$16&gt;=GY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GZ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=GZ$5)*(Отпуска!$D$5:$D$17&gt;=GZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=GZ$5)*(Отпуска!$D$5:$D$16&gt;=GZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HA8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HA$5)*(Отпуска!$D$5:$D$17&gt;=HA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HA$5)*(Отпуска!$D$5:$D$16&gt;=HA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HB8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HB$5)*(Отпуска!$D$5:$D$17&gt;=HB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HB$5)*(Отпуска!$D$5:$D$16&gt;=HB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HC8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HC$5)*(Отпуска!$D$5:$D$17&gt;=HC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HC$5)*(Отпуска!$D$5:$D$16&gt;=HC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HD8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HD$5)*(Отпуска!$D$5:$D$17&gt;=HD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HD$5)*(Отпуска!$D$5:$D$16&gt;=HD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HE8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HE$5)*(Отпуска!$D$5:$D$17&gt;=HE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HE$5)*(Отпуска!$D$5:$D$16&gt;=HE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HF8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HF$5)*(Отпуска!$D$5:$D$17&gt;=HF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HF$5)*(Отпуска!$D$5:$D$16&gt;=HF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HG8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HG$5)*(Отпуска!$D$5:$D$17&gt;=HG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HG$5)*(Отпуска!$D$5:$D$16&gt;=HG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HH8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HH$5)*(Отпуска!$D$5:$D$17&gt;=HH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HH$5)*(Отпуска!$D$5:$D$16&gt;=HH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HI8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HI$5)*(Отпуска!$D$5:$D$17&gt;=HI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HI$5)*(Отпуска!$D$5:$D$16&gt;=HI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HJ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HJ$5)*(Отпуска!$D$5:$D$17&gt;=HJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HJ$5)*(Отпуска!$D$5:$D$16&gt;=HJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HK8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HK$5)*(Отпуска!$D$5:$D$17&gt;=HK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HK$5)*(Отпуска!$D$5:$D$16&gt;=HK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HL8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HL$5)*(Отпуска!$D$5:$D$17&gt;=HL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HL$5)*(Отпуска!$D$5:$D$16&gt;=HL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HM8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HM$5)*(Отпуска!$D$5:$D$17&gt;=HM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HM$5)*(Отпуска!$D$5:$D$16&gt;=HM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HN8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HN$5)*(Отпуска!$D$5:$D$17&gt;=HN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HN$5)*(Отпуска!$D$5:$D$16&gt;=HN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HO8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HO$5)*(Отпуска!$D$5:$D$17&gt;=HO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HO$5)*(Отпуска!$D$5:$D$16&gt;=HO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HP8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HP$5)*(Отпуска!$D$5:$D$17&gt;=HP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HP$5)*(Отпуска!$D$5:$D$16&gt;=HP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HQ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HQ$5)*(Отпуска!$D$5:$D$17&gt;=HQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HQ$5)*(Отпуска!$D$5:$D$16&gt;=HQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HR8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HR$5)*(Отпуска!$D$5:$D$17&gt;=HR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HR$5)*(Отпуска!$D$5:$D$16&gt;=HR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HS8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HS$5)*(Отпуска!$D$5:$D$17&gt;=HS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HS$5)*(Отпуска!$D$5:$D$16&gt;=HS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HT8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HT$5)*(Отпуска!$D$5:$D$17&gt;=HT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HT$5)*(Отпуска!$D$5:$D$16&gt;=HT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HU8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HU$5)*(Отпуска!$D$5:$D$17&gt;=HU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HU$5)*(Отпуска!$D$5:$D$16&gt;=HU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HV8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HV$5)*(Отпуска!$D$5:$D$17&gt;=HV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HV$5)*(Отпуска!$D$5:$D$16&gt;=HV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HW8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HW$5)*(Отпуска!$D$5:$D$17&gt;=HW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HW$5)*(Отпуска!$D$5:$D$16&gt;=HW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HX8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HX$5)*(Отпуска!$D$5:$D$17&gt;=HX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HX$5)*(Отпуска!$D$5:$D$16&gt;=HX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HY8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HY$5)*(Отпуска!$D$5:$D$17&gt;=HY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HY$5)*(Отпуска!$D$5:$D$16&gt;=HY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HZ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=HZ$5)*(Отпуска!$D$5:$D$17&gt;=HZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=HZ$5)*(Отпуска!$D$5:$D$16&gt;=HZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IA8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IA$5)*(Отпуска!$D$5:$D$17&gt;=IA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IA$5)*(Отпуска!$D$5:$D$16&gt;=IA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IB8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IB$5)*(Отпуска!$D$5:$D$17&gt;=IB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IB$5)*(Отпуска!$D$5:$D$16&gt;=IB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IC8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IC$5)*(Отпуска!$D$5:$D$17&gt;=IC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IC$5)*(Отпуска!$D$5:$D$16&gt;=IC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ID8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=ID$5)*(Отпуска!$D$5:$D$17&gt;=ID$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=ID$5)*(Отпуска!$D$5:$D$16&gt;=ID$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IE8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IE$5)*(Отпуска!$D$5:$D$17&gt;=IE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IE$5)*(Отпуска!$D$5:$D$16&gt;=IE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IF8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IF$5)*(Отпуска!$D$5:$D$17&gt;=IF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IF$5)*(Отпуска!$D$5:$D$16&gt;=IF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IG8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IG$5)*(Отпуска!$D$5:$D$17&gt;=IG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IG$5)*(Отпуска!$D$5:$D$16&gt;=IG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IH8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IH$5)*(Отпуска!$D$5:$D$17&gt;=IH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IH$5)*(Отпуска!$D$5:$D$16&gt;=IH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="II8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=II$5)*(Отпуска!$D$5:$D$17&gt;=II$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=II$5)*(Отпуска!$D$5:$D$16&gt;=II$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IJ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IJ$5)*(Отпуска!$D$5:$D$17&gt;=IJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IJ$5)*(Отпуска!$D$5:$D$16&gt;=IJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IK8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IK$5)*(Отпуска!$D$5:$D$17&gt;=IK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IK$5)*(Отпуска!$D$5:$D$16&gt;=IK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IL8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IL$5)*(Отпуска!$D$5:$D$17&gt;=IL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IL$5)*(Отпуска!$D$5:$D$16&gt;=IL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IM8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IM$5)*(Отпуска!$D$5:$D$17&gt;=IM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IM$5)*(Отпуска!$D$5:$D$16&gt;=IM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IN8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IN$5)*(Отпуска!$D$5:$D$17&gt;=IN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IN$5)*(Отпуска!$D$5:$D$16&gt;=IN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IO8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IO$5)*(Отпуска!$D$5:$D$17&gt;=IO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IO$5)*(Отпуска!$D$5:$D$16&gt;=IO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IP8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IP$5)*(Отпуска!$D$5:$D$17&gt;=IP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IP$5)*(Отпуска!$D$5:$D$16&gt;=IP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IQ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IQ$5)*(Отпуска!$D$5:$D$17&gt;=IQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IQ$5)*(Отпуска!$D$5:$D$16&gt;=IQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IR8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IR$5)*(Отпуска!$D$5:$D$17&gt;=IR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IR$5)*(Отпуска!$D$5:$D$16&gt;=IR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IS8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IS$5)*(Отпуска!$D$5:$D$17&gt;=IS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IS$5)*(Отпуска!$D$5:$D$16&gt;=IS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IT8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IT$5)*(Отпуска!$D$5:$D$17&gt;=IT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IT$5)*(Отпуска!$D$5:$D$16&gt;=IT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IU8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IU$5)*(Отпуска!$D$5:$D$17&gt;=IU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IU$5)*(Отпуска!$D$5:$D$16&gt;=IU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IV8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IV$5)*(Отпуска!$D$5:$D$17&gt;=IV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IV$5)*(Отпуска!$D$5:$D$16&gt;=IV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IW8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IW$5)*(Отпуска!$D$5:$D$17&gt;=IW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IW$5)*(Отпуска!$D$5:$D$16&gt;=IW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IX8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IX$5)*(Отпуска!$D$5:$D$17&gt;=IX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IX$5)*(Отпуска!$D$5:$D$16&gt;=IX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IY8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IY$5)*(Отпуска!$D$5:$D$17&gt;=IY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IY$5)*(Отпуска!$D$5:$D$16&gt;=IY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IZ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=IZ$5)*(Отпуска!$D$5:$D$17&gt;=IZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=IZ$5)*(Отпуска!$D$5:$D$16&gt;=IZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JA8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JA$5)*(Отпуска!$D$5:$D$17&gt;=JA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JA$5)*(Отпуска!$D$5:$D$16&gt;=JA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JB8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JB$5)*(Отпуска!$D$5:$D$17&gt;=JB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JB$5)*(Отпуска!$D$5:$D$16&gt;=JB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JC8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JC$5)*(Отпуска!$D$5:$D$17&gt;=JC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JC$5)*(Отпуска!$D$5:$D$16&gt;=JC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JD8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JD$5)*(Отпуска!$D$5:$D$17&gt;=JD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JD$5)*(Отпуска!$D$5:$D$16&gt;=JD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JE8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JE$5)*(Отпуска!$D$5:$D$17&gt;=JE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JE$5)*(Отпуска!$D$5:$D$16&gt;=JE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JF8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JF$5)*(Отпуска!$D$5:$D$17&gt;=JF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JF$5)*(Отпуска!$D$5:$D$16&gt;=JF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JG8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JG$5)*(Отпуска!$D$5:$D$17&gt;=JG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JG$5)*(Отпуска!$D$5:$D$16&gt;=JG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JH8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JH$5)*(Отпуска!$D$5:$D$17&gt;=JH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JH$5)*(Отпуска!$D$5:$D$16&gt;=JH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JI8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JI$5)*(Отпуска!$D$5:$D$17&gt;=JI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JI$5)*(Отпуска!$D$5:$D$16&gt;=JI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JJ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JJ$5)*(Отпуска!$D$5:$D$17&gt;=JJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JJ$5)*(Отпуска!$D$5:$D$16&gt;=JJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JK8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JK$5)*(Отпуска!$D$5:$D$17&gt;=JK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JK$5)*(Отпуска!$D$5:$D$16&gt;=JK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JL8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JL$5)*(Отпуска!$D$5:$D$17&gt;=JL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JL$5)*(Отпуска!$D$5:$D$16&gt;=JL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JM8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JM$5)*(Отпуска!$D$5:$D$17&gt;=JM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JM$5)*(Отпуска!$D$5:$D$16&gt;=JM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JN8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JN$5)*(Отпуска!$D$5:$D$17&gt;=JN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JN$5)*(Отпуска!$D$5:$D$16&gt;=JN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JO8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JO$5)*(Отпуска!$D$5:$D$17&gt;=JO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JO$5)*(Отпуска!$D$5:$D$16&gt;=JO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JP8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JP$5)*(Отпуска!$D$5:$D$17&gt;=JP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JP$5)*(Отпуска!$D$5:$D$16&gt;=JP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JQ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JQ$5)*(Отпуска!$D$5:$D$17&gt;=JQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JQ$5)*(Отпуска!$D$5:$D$16&gt;=JQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JR8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JR$5)*(Отпуска!$D$5:$D$17&gt;=JR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JR$5)*(Отпуска!$D$5:$D$16&gt;=JR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JS8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JS$5)*(Отпуска!$D$5:$D$17&gt;=JS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JS$5)*(Отпуска!$D$5:$D$16&gt;=JS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JT8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JT$5)*(Отпуска!$D$5:$D$17&gt;=JT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JT$5)*(Отпуска!$D$5:$D$16&gt;=JT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JU8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JU$5)*(Отпуска!$D$5:$D$17&gt;=JU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JU$5)*(Отпуска!$D$5:$D$16&gt;=JU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JV8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JV$5)*(Отпуска!$D$5:$D$17&gt;=JV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JV$5)*(Отпуска!$D$5:$D$16&gt;=JV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JW8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JW$5)*(Отпуска!$D$5:$D$17&gt;=JW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JW$5)*(Отпуска!$D$5:$D$16&gt;=JW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JX8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JX$5)*(Отпуска!$D$5:$D$17&gt;=JX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JX$5)*(Отпуска!$D$5:$D$16&gt;=JX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JY8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JY$5)*(Отпуска!$D$5:$D$17&gt;=JY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JY$5)*(Отпуска!$D$5:$D$16&gt;=JY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JZ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=JZ$5)*(Отпуска!$D$5:$D$17&gt;=JZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=JZ$5)*(Отпуска!$D$5:$D$16&gt;=JZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KA8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KA$5)*(Отпуска!$D$5:$D$17&gt;=KA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KA$5)*(Отпуска!$D$5:$D$16&gt;=KA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KB8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KB$5)*(Отпуска!$D$5:$D$17&gt;=KB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KB$5)*(Отпуска!$D$5:$D$16&gt;=KB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KC8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KC$5)*(Отпуска!$D$5:$D$17&gt;=KC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KC$5)*(Отпуска!$D$5:$D$16&gt;=KC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KD8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KD$5)*(Отпуска!$D$5:$D$17&gt;=KD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KD$5)*(Отпуска!$D$5:$D$16&gt;=KD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KE8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KE$5)*(Отпуска!$D$5:$D$17&gt;=KE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KE$5)*(Отпуска!$D$5:$D$16&gt;=KE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KF8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KF$5)*(Отпуска!$D$5:$D$17&gt;=KF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KF$5)*(Отпуска!$D$5:$D$16&gt;=KF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KG8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KG$5)*(Отпуска!$D$5:$D$17&gt;=KG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KG$5)*(Отпуска!$D$5:$D$16&gt;=KG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KH8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KH$5)*(Отпуска!$D$5:$D$17&gt;=KH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KH$5)*(Отпуска!$D$5:$D$16&gt;=KH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KI8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KI$5)*(Отпуска!$D$5:$D$17&gt;=KI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KI$5)*(Отпуска!$D$5:$D$16&gt;=KI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KJ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KJ$5)*(Отпуска!$D$5:$D$17&gt;=KJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KJ$5)*(Отпуска!$D$5:$D$16&gt;=KJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KK8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KK$5)*(Отпуска!$D$5:$D$17&gt;=KK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KK$5)*(Отпуска!$D$5:$D$16&gt;=KK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KL8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KL$5)*(Отпуска!$D$5:$D$17&gt;=KL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KL$5)*(Отпуска!$D$5:$D$16&gt;=KL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KM8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KM$5)*(Отпуска!$D$5:$D$17&gt;=KM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KM$5)*(Отпуска!$D$5:$D$16&gt;=KM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KN8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KN$5)*(Отпуска!$D$5:$D$17&gt;=KN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KN$5)*(Отпуска!$D$5:$D$16&gt;=KN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KO8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KO$5)*(Отпуска!$D$5:$D$17&gt;=KO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KO$5)*(Отпуска!$D$5:$D$16&gt;=KO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KP8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KP$5)*(Отпуска!$D$5:$D$17&gt;=KP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KP$5)*(Отпуска!$D$5:$D$16&gt;=KP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KQ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KQ$5)*(Отпуска!$D$5:$D$17&gt;=KQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KQ$5)*(Отпуска!$D$5:$D$16&gt;=KQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KR8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KR$5)*(Отпуска!$D$5:$D$17&gt;=KR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KR$5)*(Отпуска!$D$5:$D$16&gt;=KR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KS8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KS$5)*(Отпуска!$D$5:$D$17&gt;=KS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KS$5)*(Отпуска!$D$5:$D$16&gt;=KS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KT8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KT$5)*(Отпуска!$D$5:$D$17&gt;=KT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KT$5)*(Отпуска!$D$5:$D$16&gt;=KT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KU8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KU$5)*(Отпуска!$D$5:$D$17&gt;=KU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KU$5)*(Отпуска!$D$5:$D$16&gt;=KU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KV8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KV$5)*(Отпуска!$D$5:$D$17&gt;=KV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KV$5)*(Отпуска!$D$5:$D$16&gt;=KV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KW8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KW$5)*(Отпуска!$D$5:$D$17&gt;=KW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KW$5)*(Отпуска!$D$5:$D$16&gt;=KW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KX8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KX$5)*(Отпуска!$D$5:$D$17&gt;=KX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KX$5)*(Отпуска!$D$5:$D$16&gt;=KX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KY8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KY$5)*(Отпуска!$D$5:$D$17&gt;=KY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KY$5)*(Отпуска!$D$5:$D$16&gt;=KY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KZ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=KZ$5)*(Отпуска!$D$5:$D$17&gt;=KZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=KZ$5)*(Отпуска!$D$5:$D$16&gt;=KZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LA8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LA$5)*(Отпуска!$D$5:$D$17&gt;=LA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LA$5)*(Отпуска!$D$5:$D$16&gt;=LA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LB8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LB$5)*(Отпуска!$D$5:$D$17&gt;=LB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LB$5)*(Отпуска!$D$5:$D$16&gt;=LB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LC8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LC$5)*(Отпуска!$D$5:$D$17&gt;=LC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LC$5)*(Отпуска!$D$5:$D$16&gt;=LC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LD8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LD$5)*(Отпуска!$D$5:$D$17&gt;=LD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LD$5)*(Отпуска!$D$5:$D$16&gt;=LD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LE8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LE$5)*(Отпуска!$D$5:$D$17&gt;=LE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LE$5)*(Отпуска!$D$5:$D$16&gt;=LE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LF8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LF$5)*(Отпуска!$D$5:$D$17&gt;=LF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LF$5)*(Отпуска!$D$5:$D$16&gt;=LF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LG8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LG$5)*(Отпуска!$D$5:$D$17&gt;=LG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LG$5)*(Отпуска!$D$5:$D$16&gt;=LG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LH8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LH$5)*(Отпуска!$D$5:$D$17&gt;=LH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LH$5)*(Отпуска!$D$5:$D$16&gt;=LH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LI8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LI$5)*(Отпуска!$D$5:$D$17&gt;=LI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LI$5)*(Отпуска!$D$5:$D$16&gt;=LI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LJ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LJ$5)*(Отпуска!$D$5:$D$17&gt;=LJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LJ$5)*(Отпуска!$D$5:$D$16&gt;=LJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LK8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LK$5)*(Отпуска!$D$5:$D$17&gt;=LK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LK$5)*(Отпуска!$D$5:$D$16&gt;=LK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LL8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LL$5)*(Отпуска!$D$5:$D$17&gt;=LL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LL$5)*(Отпуска!$D$5:$D$16&gt;=LL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LM8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LM$5)*(Отпуска!$D$5:$D$17&gt;=LM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LM$5)*(Отпуска!$D$5:$D$16&gt;=LM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LN8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LN$5)*(Отпуска!$D$5:$D$17&gt;=LN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LN$5)*(Отпуска!$D$5:$D$16&gt;=LN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LO8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LO$5)*(Отпуска!$D$5:$D$17&gt;=LO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LO$5)*(Отпуска!$D$5:$D$16&gt;=LO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LP8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LP$5)*(Отпуска!$D$5:$D$17&gt;=LP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LP$5)*(Отпуска!$D$5:$D$16&gt;=LP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LQ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LQ$5)*(Отпуска!$D$5:$D$17&gt;=LQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LQ$5)*(Отпуска!$D$5:$D$16&gt;=LQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LR8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LR$5)*(Отпуска!$D$5:$D$17&gt;=LR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LR$5)*(Отпуска!$D$5:$D$16&gt;=LR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LS8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LS$5)*(Отпуска!$D$5:$D$17&gt;=LS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LS$5)*(Отпуска!$D$5:$D$16&gt;=LS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LT8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LT$5)*(Отпуска!$D$5:$D$17&gt;=LT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LT$5)*(Отпуска!$D$5:$D$16&gt;=LT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LU8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LU$5)*(Отпуска!$D$5:$D$17&gt;=LU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LU$5)*(Отпуска!$D$5:$D$16&gt;=LU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LV8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LV$5)*(Отпуска!$D$5:$D$17&gt;=LV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LV$5)*(Отпуска!$D$5:$D$16&gt;=LV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LW8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LW$5)*(Отпуска!$D$5:$D$17&gt;=LW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LW$5)*(Отпуска!$D$5:$D$16&gt;=LW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LX8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LX$5)*(Отпуска!$D$5:$D$17&gt;=LX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LX$5)*(Отпуска!$D$5:$D$16&gt;=LX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LY8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LY$5)*(Отпуска!$D$5:$D$17&gt;=LY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LY$5)*(Отпуска!$D$5:$D$16&gt;=LY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LZ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=LZ$5)*(Отпуска!$D$5:$D$17&gt;=LZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=LZ$5)*(Отпуска!$D$5:$D$16&gt;=LZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MA8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MA$5)*(Отпуска!$D$5:$D$17&gt;=MA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MA$5)*(Отпуска!$D$5:$D$16&gt;=MA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MB8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MB$5)*(Отпуска!$D$5:$D$17&gt;=MB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MB$5)*(Отпуска!$D$5:$D$16&gt;=MB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MC8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MC$5)*(Отпуска!$D$5:$D$17&gt;=MC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MC$5)*(Отпуска!$D$5:$D$16&gt;=MC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MD8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MD$5)*(Отпуска!$D$5:$D$17&gt;=MD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MD$5)*(Отпуска!$D$5:$D$16&gt;=MD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ME8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=ME$5)*(Отпуска!$D$5:$D$17&gt;=ME$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=ME$5)*(Отпуска!$D$5:$D$16&gt;=ME$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MF8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MF$5)*(Отпуска!$D$5:$D$17&gt;=MF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MF$5)*(Отпуска!$D$5:$D$16&gt;=MF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MG8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MG$5)*(Отпуска!$D$5:$D$17&gt;=MG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MG$5)*(Отпуска!$D$5:$D$16&gt;=MG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MH8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MH$5)*(Отпуска!$D$5:$D$17&gt;=MH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MH$5)*(Отпуска!$D$5:$D$16&gt;=MH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MI8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MI$5)*(Отпуска!$D$5:$D$17&gt;=MI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MI$5)*(Отпуска!$D$5:$D$16&gt;=MI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MJ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MJ$5)*(Отпуска!$D$5:$D$17&gt;=MJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MJ$5)*(Отпуска!$D$5:$D$16&gt;=MJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MK8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MK$5)*(Отпуска!$D$5:$D$17&gt;=MK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MK$5)*(Отпуска!$D$5:$D$16&gt;=MK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ML8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=ML$5)*(Отпуска!$D$5:$D$17&gt;=ML$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=ML$5)*(Отпуска!$D$5:$D$16&gt;=ML$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MM8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MM$5)*(Отпуска!$D$5:$D$17&gt;=MM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MM$5)*(Отпуска!$D$5:$D$16&gt;=MM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MN8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MN$5)*(Отпуска!$D$5:$D$17&gt;=MN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MN$5)*(Отпуска!$D$5:$D$16&gt;=MN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MO8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MO$5)*(Отпуска!$D$5:$D$17&gt;=MO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MO$5)*(Отпуска!$D$5:$D$16&gt;=MO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MP8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MP$5)*(Отпуска!$D$5:$D$17&gt;=MP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MP$5)*(Отпуска!$D$5:$D$16&gt;=MP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MQ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MQ$5)*(Отпуска!$D$5:$D$17&gt;=MQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MQ$5)*(Отпуска!$D$5:$D$16&gt;=MQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MR8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MR$5)*(Отпуска!$D$5:$D$17&gt;=MR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MR$5)*(Отпуска!$D$5:$D$16&gt;=MR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MS8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MS$5)*(Отпуска!$D$5:$D$17&gt;=MS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MS$5)*(Отпуска!$D$5:$D$16&gt;=MS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MT8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MT$5)*(Отпуска!$D$5:$D$17&gt;=MT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MT$5)*(Отпуска!$D$5:$D$16&gt;=MT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MU8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MU$5)*(Отпуска!$D$5:$D$17&gt;=MU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MU$5)*(Отпуска!$D$5:$D$16&gt;=MU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MV8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MV$5)*(Отпуска!$D$5:$D$17&gt;=MV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MV$5)*(Отпуска!$D$5:$D$16&gt;=MV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MW8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MW$5)*(Отпуска!$D$5:$D$17&gt;=MW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MW$5)*(Отпуска!$D$5:$D$16&gt;=MW$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="MX8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MX$5)*(Отпуска!$D$5:$D$17&gt;=MX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MX$5)*(Отпуска!$D$5:$D$16&gt;=MX$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="MY8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MY$5)*(Отпуска!$D$5:$D$17&gt;=MY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MY$5)*(Отпуска!$D$5:$D$16&gt;=MY$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="MZ8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=MZ$5)*(Отпуска!$D$5:$D$17&gt;=MZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=MZ$5)*(Отпуска!$D$5:$D$16&gt;=MZ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="NA8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=NA$5)*(Отпуска!$D$5:$D$17&gt;=NA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=NA$5)*(Отпуска!$D$5:$D$16&gt;=NA$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="NB8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=NB$5)*(Отпуска!$D$5:$D$17&gt;=NB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=NB$5)*(Отпуска!$D$5:$D$16&gt;=NB$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="NC8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=NC$5)*(Отпуска!$D$5:$D$17&gt;=NC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=NC$5)*(Отпуска!$D$5:$D$16&gt;=NC$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="ND8" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A8)*(Отпуска!$B$5:$B$17&lt;=ND$5)*(Отпуска!$D$5:$D$17&gt;=ND$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A8)*(Отпуска!$B$5:$B$16&lt;=ND$5)*(Отпуска!$D$5:$D$16&gt;=ND$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
     </row>
@@ -7136,1467 +7136,1467 @@
         <v>55</v>
       </c>
       <c r="C9" s="9" t="n">
-        <f aca="false">SUMIF(Отпуска!$A$5:$A$17,$A9,Отпуска!$C$5:$C$17)</f>
+        <f aca="false">SUMIF(Отпуска!$A$5:$A$16,$A9,Отпуска!$C$5:$C$16)</f>
         <v>55</v>
       </c>
       <c r="D9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=D$5)*(Отпуска!$D$5:$D$17&gt;=D$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=D$5)*(Отпуска!$D$5:$D$16&gt;=D$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="E9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=E$5)*(Отпуска!$D$5:$D$17&gt;=E$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=E$5)*(Отпуска!$D$5:$D$16&gt;=E$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="F9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=F$5)*(Отпуска!$D$5:$D$17&gt;=F$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=F$5)*(Отпуска!$D$5:$D$16&gt;=F$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="G9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=G$5)*(Отпуска!$D$5:$D$17&gt;=G$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=G$5)*(Отпуска!$D$5:$D$16&gt;=G$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="H9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=H$5)*(Отпуска!$D$5:$D$17&gt;=H$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=H$5)*(Отпуска!$D$5:$D$16&gt;=H$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="I9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=I$5)*(Отпуска!$D$5:$D$17&gt;=I$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=I$5)*(Отпуска!$D$5:$D$16&gt;=I$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="J9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=J$5)*(Отпуска!$D$5:$D$17&gt;=J$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=J$5)*(Отпуска!$D$5:$D$16&gt;=J$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="K9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=K$5)*(Отпуска!$D$5:$D$17&gt;=K$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=K$5)*(Отпуска!$D$5:$D$16&gt;=K$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="L9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=L$5)*(Отпуска!$D$5:$D$17&gt;=L$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=L$5)*(Отпуска!$D$5:$D$16&gt;=L$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="M9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=M$5)*(Отпуска!$D$5:$D$17&gt;=M$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=M$5)*(Отпуска!$D$5:$D$16&gt;=M$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="N9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=N$5)*(Отпуска!$D$5:$D$17&gt;=N$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=N$5)*(Отпуска!$D$5:$D$16&gt;=N$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="O9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=O$5)*(Отпуска!$D$5:$D$17&gt;=O$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=O$5)*(Отпуска!$D$5:$D$16&gt;=O$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="P9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=P$5)*(Отпуска!$D$5:$D$17&gt;=P$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=P$5)*(Отпуска!$D$5:$D$16&gt;=P$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="Q9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=Q$5)*(Отпуска!$D$5:$D$17&gt;=Q$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=Q$5)*(Отпуска!$D$5:$D$16&gt;=Q$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="R9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=R$5)*(Отпуска!$D$5:$D$17&gt;=R$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=R$5)*(Отпуска!$D$5:$D$16&gt;=R$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="S9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=S$5)*(Отпуска!$D$5:$D$17&gt;=S$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=S$5)*(Отпуска!$D$5:$D$16&gt;=S$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="T9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=T$5)*(Отпуска!$D$5:$D$17&gt;=T$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=T$5)*(Отпуска!$D$5:$D$16&gt;=T$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="U9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=U$5)*(Отпуска!$D$5:$D$17&gt;=U$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=U$5)*(Отпуска!$D$5:$D$16&gt;=U$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="V9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=V$5)*(Отпуска!$D$5:$D$17&gt;=V$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=V$5)*(Отпуска!$D$5:$D$16&gt;=V$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="W9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=W$5)*(Отпуска!$D$5:$D$17&gt;=W$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=W$5)*(Отпуска!$D$5:$D$16&gt;=W$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="X9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=X$5)*(Отпуска!$D$5:$D$17&gt;=X$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=X$5)*(Отпуска!$D$5:$D$16&gt;=X$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="Y9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=Y$5)*(Отпуска!$D$5:$D$17&gt;=Y$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=Y$5)*(Отпуска!$D$5:$D$16&gt;=Y$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="Z9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=Z$5)*(Отпуска!$D$5:$D$17&gt;=Z$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=Z$5)*(Отпуска!$D$5:$D$16&gt;=Z$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AA9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AA$5)*(Отпуска!$D$5:$D$17&gt;=AA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AA$5)*(Отпуска!$D$5:$D$16&gt;=AA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AB9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AB$5)*(Отпуска!$D$5:$D$17&gt;=AB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AB$5)*(Отпуска!$D$5:$D$16&gt;=AB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AC9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AC$5)*(Отпуска!$D$5:$D$17&gt;=AC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AC$5)*(Отпуска!$D$5:$D$16&gt;=AC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AD9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AD$5)*(Отпуска!$D$5:$D$17&gt;=AD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AD$5)*(Отпуска!$D$5:$D$16&gt;=AD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AE9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AE$5)*(Отпуска!$D$5:$D$17&gt;=AE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AE$5)*(Отпуска!$D$5:$D$16&gt;=AE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AF9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AF$5)*(Отпуска!$D$5:$D$17&gt;=AF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AF$5)*(Отпуска!$D$5:$D$16&gt;=AF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AG9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AG$5)*(Отпуска!$D$5:$D$17&gt;=AG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AG$5)*(Отпуска!$D$5:$D$16&gt;=AG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AH9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AH$5)*(Отпуска!$D$5:$D$17&gt;=AH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AH$5)*(Отпуска!$D$5:$D$16&gt;=AH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AI9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AI$5)*(Отпуска!$D$5:$D$17&gt;=AI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AI$5)*(Отпуска!$D$5:$D$16&gt;=AI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AJ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AJ$5)*(Отпуска!$D$5:$D$17&gt;=AJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AJ$5)*(Отпуска!$D$5:$D$16&gt;=AJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AK9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AK$5)*(Отпуска!$D$5:$D$17&gt;=AK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AK$5)*(Отпуска!$D$5:$D$16&gt;=AK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AL9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AL$5)*(Отпуска!$D$5:$D$17&gt;=AL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AL$5)*(Отпуска!$D$5:$D$16&gt;=AL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AM9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AM$5)*(Отпуска!$D$5:$D$17&gt;=AM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AM$5)*(Отпуска!$D$5:$D$16&gt;=AM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AN9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AN$5)*(Отпуска!$D$5:$D$17&gt;=AN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AN$5)*(Отпуска!$D$5:$D$16&gt;=AN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AO9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AO$5)*(Отпуска!$D$5:$D$17&gt;=AO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AO$5)*(Отпуска!$D$5:$D$16&gt;=AO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AP9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AP$5)*(Отпуска!$D$5:$D$17&gt;=AP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AP$5)*(Отпуска!$D$5:$D$16&gt;=AP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AQ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AQ$5)*(Отпуска!$D$5:$D$17&gt;=AQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AQ$5)*(Отпуска!$D$5:$D$16&gt;=AQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AR9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AR$5)*(Отпуска!$D$5:$D$17&gt;=AR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AR$5)*(Отпуска!$D$5:$D$16&gt;=AR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AS9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AS$5)*(Отпуска!$D$5:$D$17&gt;=AS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AS$5)*(Отпуска!$D$5:$D$16&gt;=AS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AT9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AT$5)*(Отпуска!$D$5:$D$17&gt;=AT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AT$5)*(Отпуска!$D$5:$D$16&gt;=AT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AU9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AU$5)*(Отпуска!$D$5:$D$17&gt;=AU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AU$5)*(Отпуска!$D$5:$D$16&gt;=AU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AV9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AV$5)*(Отпуска!$D$5:$D$17&gt;=AV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AV$5)*(Отпуска!$D$5:$D$16&gt;=AV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AW9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AW$5)*(Отпуска!$D$5:$D$17&gt;=AW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AW$5)*(Отпуска!$D$5:$D$16&gt;=AW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AX9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AX$5)*(Отпуска!$D$5:$D$17&gt;=AX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AX$5)*(Отпуска!$D$5:$D$16&gt;=AX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AY9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AY$5)*(Отпуска!$D$5:$D$17&gt;=AY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AY$5)*(Отпуска!$D$5:$D$16&gt;=AY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AZ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=AZ$5)*(Отпуска!$D$5:$D$17&gt;=AZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=AZ$5)*(Отпуска!$D$5:$D$16&gt;=AZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BA9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BA$5)*(Отпуска!$D$5:$D$17&gt;=BA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BA$5)*(Отпуска!$D$5:$D$16&gt;=BA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BB9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BB$5)*(Отпуска!$D$5:$D$17&gt;=BB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BB$5)*(Отпуска!$D$5:$D$16&gt;=BB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BC9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BC$5)*(Отпуска!$D$5:$D$17&gt;=BC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BC$5)*(Отпуска!$D$5:$D$16&gt;=BC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BD9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BD$5)*(Отпуска!$D$5:$D$17&gt;=BD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BD$5)*(Отпуска!$D$5:$D$16&gt;=BD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BE9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BE$5)*(Отпуска!$D$5:$D$17&gt;=BE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BE$5)*(Отпуска!$D$5:$D$16&gt;=BE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BF9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BF$5)*(Отпуска!$D$5:$D$17&gt;=BF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BF$5)*(Отпуска!$D$5:$D$16&gt;=BF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BG9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BG$5)*(Отпуска!$D$5:$D$17&gt;=BG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BG$5)*(Отпуска!$D$5:$D$16&gt;=BG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BH9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BH$5)*(Отпуска!$D$5:$D$17&gt;=BH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BH$5)*(Отпуска!$D$5:$D$16&gt;=BH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BI9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BI$5)*(Отпуска!$D$5:$D$17&gt;=BI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BI$5)*(Отпуска!$D$5:$D$16&gt;=BI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BJ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BJ$5)*(Отпуска!$D$5:$D$17&gt;=BJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BJ$5)*(Отпуска!$D$5:$D$16&gt;=BJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BK9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BK$5)*(Отпуска!$D$5:$D$17&gt;=BK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BK$5)*(Отпуска!$D$5:$D$16&gt;=BK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BL9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BL$5)*(Отпуска!$D$5:$D$17&gt;=BL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BL$5)*(Отпуска!$D$5:$D$16&gt;=BL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BM9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BM$5)*(Отпуска!$D$5:$D$17&gt;=BM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BM$5)*(Отпуска!$D$5:$D$16&gt;=BM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BN9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BN$5)*(Отпуска!$D$5:$D$17&gt;=BN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BN$5)*(Отпуска!$D$5:$D$16&gt;=BN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BO9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BO$5)*(Отпуска!$D$5:$D$17&gt;=BO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BO$5)*(Отпуска!$D$5:$D$16&gt;=BO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BP9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BP$5)*(Отпуска!$D$5:$D$17&gt;=BP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BP$5)*(Отпуска!$D$5:$D$16&gt;=BP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BQ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BQ$5)*(Отпуска!$D$5:$D$17&gt;=BQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BQ$5)*(Отпуска!$D$5:$D$16&gt;=BQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BR9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BR$5)*(Отпуска!$D$5:$D$17&gt;=BR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BR$5)*(Отпуска!$D$5:$D$16&gt;=BR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BS9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BS$5)*(Отпуска!$D$5:$D$17&gt;=BS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BS$5)*(Отпуска!$D$5:$D$16&gt;=BS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BT9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BT$5)*(Отпуска!$D$5:$D$17&gt;=BT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BT$5)*(Отпуска!$D$5:$D$16&gt;=BT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BU9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BU$5)*(Отпуска!$D$5:$D$17&gt;=BU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BU$5)*(Отпуска!$D$5:$D$16&gt;=BU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BV9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BV$5)*(Отпуска!$D$5:$D$17&gt;=BV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BV$5)*(Отпуска!$D$5:$D$16&gt;=BV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BW9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BW$5)*(Отпуска!$D$5:$D$17&gt;=BW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BW$5)*(Отпуска!$D$5:$D$16&gt;=BW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BX9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BX$5)*(Отпуска!$D$5:$D$17&gt;=BX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BX$5)*(Отпуска!$D$5:$D$16&gt;=BX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BY9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BY$5)*(Отпуска!$D$5:$D$17&gt;=BY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BY$5)*(Отпуска!$D$5:$D$16&gt;=BY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BZ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=BZ$5)*(Отпуска!$D$5:$D$17&gt;=BZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=BZ$5)*(Отпуска!$D$5:$D$16&gt;=BZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CA9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CA$5)*(Отпуска!$D$5:$D$17&gt;=CA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CA$5)*(Отпуска!$D$5:$D$16&gt;=CA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CB9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CB$5)*(Отпуска!$D$5:$D$17&gt;=CB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CB$5)*(Отпуска!$D$5:$D$16&gt;=CB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CC9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CC$5)*(Отпуска!$D$5:$D$17&gt;=CC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CC$5)*(Отпуска!$D$5:$D$16&gt;=CC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CD9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CD$5)*(Отпуска!$D$5:$D$17&gt;=CD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CD$5)*(Отпуска!$D$5:$D$16&gt;=CD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CE9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CE$5)*(Отпуска!$D$5:$D$17&gt;=CE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CE$5)*(Отпуска!$D$5:$D$16&gt;=CE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CF9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CF$5)*(Отпуска!$D$5:$D$17&gt;=CF$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CF$5)*(Отпуска!$D$5:$D$16&gt;=CF$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="CG9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CG$5)*(Отпуска!$D$5:$D$17&gt;=CG$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CG$5)*(Отпуска!$D$5:$D$16&gt;=CG$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="CH9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CH$5)*(Отпуска!$D$5:$D$17&gt;=CH$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CH$5)*(Отпуска!$D$5:$D$16&gt;=CH$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="CI9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CI$5)*(Отпуска!$D$5:$D$17&gt;=CI$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CI$5)*(Отпуска!$D$5:$D$16&gt;=CI$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="CJ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CJ$5)*(Отпуска!$D$5:$D$17&gt;=CJ$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CJ$5)*(Отпуска!$D$5:$D$16&gt;=CJ$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="CK9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CK$5)*(Отпуска!$D$5:$D$17&gt;=CK$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CK$5)*(Отпуска!$D$5:$D$16&gt;=CK$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="CL9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CL$5)*(Отпуска!$D$5:$D$17&gt;=CL$5))&gt;0,"О","")</f>
-        <v>О</v>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CL$5)*(Отпуска!$D$5:$D$16&gt;=CL$5))&gt;0,"О","")</f>
+        <v/>
       </c>
       <c r="CM9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CM$5)*(Отпуска!$D$5:$D$17&gt;=CM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CM$5)*(Отпуска!$D$5:$D$16&gt;=CM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CN9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CN$5)*(Отпуска!$D$5:$D$17&gt;=CN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CN$5)*(Отпуска!$D$5:$D$16&gt;=CN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CO9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CO$5)*(Отпуска!$D$5:$D$17&gt;=CO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CO$5)*(Отпуска!$D$5:$D$16&gt;=CO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CP9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CP$5)*(Отпуска!$D$5:$D$17&gt;=CP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CP$5)*(Отпуска!$D$5:$D$16&gt;=CP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CQ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CQ$5)*(Отпуска!$D$5:$D$17&gt;=CQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CQ$5)*(Отпуска!$D$5:$D$16&gt;=CQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CR9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CR$5)*(Отпуска!$D$5:$D$17&gt;=CR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CR$5)*(Отпуска!$D$5:$D$16&gt;=CR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CS9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CS$5)*(Отпуска!$D$5:$D$17&gt;=CS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CS$5)*(Отпуска!$D$5:$D$16&gt;=CS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CT9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CT$5)*(Отпуска!$D$5:$D$17&gt;=CT$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CT$5)*(Отпуска!$D$5:$D$16&gt;=CT$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="CU9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CU$5)*(Отпуска!$D$5:$D$17&gt;=CU$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CU$5)*(Отпуска!$D$5:$D$16&gt;=CU$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="CV9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CV$5)*(Отпуска!$D$5:$D$17&gt;=CV$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CV$5)*(Отпуска!$D$5:$D$16&gt;=CV$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="CW9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CW$5)*(Отпуска!$D$5:$D$17&gt;=CW$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CW$5)*(Отпуска!$D$5:$D$16&gt;=CW$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="CX9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CX$5)*(Отпуска!$D$5:$D$17&gt;=CX$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CX$5)*(Отпуска!$D$5:$D$16&gt;=CX$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="CY9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CY$5)*(Отпуска!$D$5:$D$17&gt;=CY$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CY$5)*(Отпуска!$D$5:$D$16&gt;=CY$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="CZ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=CZ$5)*(Отпуска!$D$5:$D$17&gt;=CZ$5))&gt;0,"О","")</f>
-        <v/>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=CZ$5)*(Отпуска!$D$5:$D$16&gt;=CZ$5))&gt;0,"О","")</f>
+        <v>О</v>
       </c>
       <c r="DA9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DA$5)*(Отпуска!$D$5:$D$17&gt;=DA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DA$5)*(Отпуска!$D$5:$D$16&gt;=DA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DB9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DB$5)*(Отпуска!$D$5:$D$17&gt;=DB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DB$5)*(Отпуска!$D$5:$D$16&gt;=DB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DC9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DC$5)*(Отпуска!$D$5:$D$17&gt;=DC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DC$5)*(Отпуска!$D$5:$D$16&gt;=DC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DD9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DD$5)*(Отпуска!$D$5:$D$17&gt;=DD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DD$5)*(Отпуска!$D$5:$D$16&gt;=DD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DE9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DE$5)*(Отпуска!$D$5:$D$17&gt;=DE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DE$5)*(Отпуска!$D$5:$D$16&gt;=DE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DF9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DF$5)*(Отпуска!$D$5:$D$17&gt;=DF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DF$5)*(Отпуска!$D$5:$D$16&gt;=DF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DG9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DG$5)*(Отпуска!$D$5:$D$17&gt;=DG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DG$5)*(Отпуска!$D$5:$D$16&gt;=DG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DH9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DH$5)*(Отпуска!$D$5:$D$17&gt;=DH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DH$5)*(Отпуска!$D$5:$D$16&gt;=DH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DI9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DI$5)*(Отпуска!$D$5:$D$17&gt;=DI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DI$5)*(Отпуска!$D$5:$D$16&gt;=DI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DJ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DJ$5)*(Отпуска!$D$5:$D$17&gt;=DJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DJ$5)*(Отпуска!$D$5:$D$16&gt;=DJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DK9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DK$5)*(Отпуска!$D$5:$D$17&gt;=DK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DK$5)*(Отпуска!$D$5:$D$16&gt;=DK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DL9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DL$5)*(Отпуска!$D$5:$D$17&gt;=DL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DL$5)*(Отпуска!$D$5:$D$16&gt;=DL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DM9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DM$5)*(Отпуска!$D$5:$D$17&gt;=DM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DM$5)*(Отпуска!$D$5:$D$16&gt;=DM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DN9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DN$5)*(Отпуска!$D$5:$D$17&gt;=DN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DN$5)*(Отпуска!$D$5:$D$16&gt;=DN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DO9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DO$5)*(Отпуска!$D$5:$D$17&gt;=DO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DO$5)*(Отпуска!$D$5:$D$16&gt;=DO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DP9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DP$5)*(Отпуска!$D$5:$D$17&gt;=DP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DP$5)*(Отпуска!$D$5:$D$16&gt;=DP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DQ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DQ$5)*(Отпуска!$D$5:$D$17&gt;=DQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DQ$5)*(Отпуска!$D$5:$D$16&gt;=DQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DR9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DR$5)*(Отпуска!$D$5:$D$17&gt;=DR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DR$5)*(Отпуска!$D$5:$D$16&gt;=DR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DS9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DS$5)*(Отпуска!$D$5:$D$17&gt;=DS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DS$5)*(Отпуска!$D$5:$D$16&gt;=DS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DT9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DT$5)*(Отпуска!$D$5:$D$17&gt;=DT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DT$5)*(Отпуска!$D$5:$D$16&gt;=DT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DU9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DU$5)*(Отпуска!$D$5:$D$17&gt;=DU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DU$5)*(Отпуска!$D$5:$D$16&gt;=DU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DV9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DV$5)*(Отпуска!$D$5:$D$17&gt;=DV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DV$5)*(Отпуска!$D$5:$D$16&gt;=DV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DW9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DW$5)*(Отпуска!$D$5:$D$17&gt;=DW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DW$5)*(Отпуска!$D$5:$D$16&gt;=DW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DX9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DX$5)*(Отпуска!$D$5:$D$17&gt;=DX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DX$5)*(Отпуска!$D$5:$D$16&gt;=DX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DY9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DY$5)*(Отпуска!$D$5:$D$17&gt;=DY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DY$5)*(Отпуска!$D$5:$D$16&gt;=DY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DZ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=DZ$5)*(Отпуска!$D$5:$D$17&gt;=DZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=DZ$5)*(Отпуска!$D$5:$D$16&gt;=DZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EA9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EA$5)*(Отпуска!$D$5:$D$17&gt;=EA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EA$5)*(Отпуска!$D$5:$D$16&gt;=EA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EB9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EB$5)*(Отпуска!$D$5:$D$17&gt;=EB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EB$5)*(Отпуска!$D$5:$D$16&gt;=EB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EC9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EC$5)*(Отпуска!$D$5:$D$17&gt;=EC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EC$5)*(Отпуска!$D$5:$D$16&gt;=EC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ED9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=ED$5)*(Отпуска!$D$5:$D$17&gt;=ED$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=ED$5)*(Отпуска!$D$5:$D$16&gt;=ED$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EE9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EE$5)*(Отпуска!$D$5:$D$17&gt;=EE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EE$5)*(Отпуска!$D$5:$D$16&gt;=EE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EF9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EF$5)*(Отпуска!$D$5:$D$17&gt;=EF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EF$5)*(Отпуска!$D$5:$D$16&gt;=EF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EG9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EG$5)*(Отпуска!$D$5:$D$17&gt;=EG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EG$5)*(Отпуска!$D$5:$D$16&gt;=EG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EH9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EH$5)*(Отпуска!$D$5:$D$17&gt;=EH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EH$5)*(Отпуска!$D$5:$D$16&gt;=EH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EI9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EI$5)*(Отпуска!$D$5:$D$17&gt;=EI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EI$5)*(Отпуска!$D$5:$D$16&gt;=EI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EJ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EJ$5)*(Отпуска!$D$5:$D$17&gt;=EJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EJ$5)*(Отпуска!$D$5:$D$16&gt;=EJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EK9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EK$5)*(Отпуска!$D$5:$D$17&gt;=EK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EK$5)*(Отпуска!$D$5:$D$16&gt;=EK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EL9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EL$5)*(Отпуска!$D$5:$D$17&gt;=EL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EL$5)*(Отпуска!$D$5:$D$16&gt;=EL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EM9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EM$5)*(Отпуска!$D$5:$D$17&gt;=EM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EM$5)*(Отпуска!$D$5:$D$16&gt;=EM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EN9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EN$5)*(Отпуска!$D$5:$D$17&gt;=EN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EN$5)*(Отпуска!$D$5:$D$16&gt;=EN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EO9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EO$5)*(Отпуска!$D$5:$D$17&gt;=EO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EO$5)*(Отпуска!$D$5:$D$16&gt;=EO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EP9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EP$5)*(Отпуска!$D$5:$D$17&gt;=EP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EP$5)*(Отпуска!$D$5:$D$16&gt;=EP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EQ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EQ$5)*(Отпуска!$D$5:$D$17&gt;=EQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EQ$5)*(Отпуска!$D$5:$D$16&gt;=EQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ER9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=ER$5)*(Отпуска!$D$5:$D$17&gt;=ER$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=ER$5)*(Отпуска!$D$5:$D$16&gt;=ER$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ES9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=ES$5)*(Отпуска!$D$5:$D$17&gt;=ES$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=ES$5)*(Отпуска!$D$5:$D$16&gt;=ES$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ET9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=ET$5)*(Отпуска!$D$5:$D$17&gt;=ET$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=ET$5)*(Отпуска!$D$5:$D$16&gt;=ET$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EU9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EU$5)*(Отпуска!$D$5:$D$17&gt;=EU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EU$5)*(Отпуска!$D$5:$D$16&gt;=EU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EV9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EV$5)*(Отпуска!$D$5:$D$17&gt;=EV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EV$5)*(Отпуска!$D$5:$D$16&gt;=EV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EW9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EW$5)*(Отпуска!$D$5:$D$17&gt;=EW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EW$5)*(Отпуска!$D$5:$D$16&gt;=EW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EX9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EX$5)*(Отпуска!$D$5:$D$17&gt;=EX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EX$5)*(Отпуска!$D$5:$D$16&gt;=EX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EY9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EY$5)*(Отпуска!$D$5:$D$17&gt;=EY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EY$5)*(Отпуска!$D$5:$D$16&gt;=EY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EZ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=EZ$5)*(Отпуска!$D$5:$D$17&gt;=EZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=EZ$5)*(Отпуска!$D$5:$D$16&gt;=EZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FA9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FA$5)*(Отпуска!$D$5:$D$17&gt;=FA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FA$5)*(Отпуска!$D$5:$D$16&gt;=FA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FB9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FB$5)*(Отпуска!$D$5:$D$17&gt;=FB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FB$5)*(Отпуска!$D$5:$D$16&gt;=FB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FC9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FC$5)*(Отпуска!$D$5:$D$17&gt;=FC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FC$5)*(Отпуска!$D$5:$D$16&gt;=FC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FD9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FD$5)*(Отпуска!$D$5:$D$17&gt;=FD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FD$5)*(Отпуска!$D$5:$D$16&gt;=FD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FE9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FE$5)*(Отпуска!$D$5:$D$17&gt;=FE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FE$5)*(Отпуска!$D$5:$D$16&gt;=FE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FF9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FF$5)*(Отпуска!$D$5:$D$17&gt;=FF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FF$5)*(Отпуска!$D$5:$D$16&gt;=FF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FG9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FG$5)*(Отпуска!$D$5:$D$17&gt;=FG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FG$5)*(Отпуска!$D$5:$D$16&gt;=FG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FH9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FH$5)*(Отпуска!$D$5:$D$17&gt;=FH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FH$5)*(Отпуска!$D$5:$D$16&gt;=FH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FI9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FI$5)*(Отпуска!$D$5:$D$17&gt;=FI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FI$5)*(Отпуска!$D$5:$D$16&gt;=FI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FJ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FJ$5)*(Отпуска!$D$5:$D$17&gt;=FJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FJ$5)*(Отпуска!$D$5:$D$16&gt;=FJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FK9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FK$5)*(Отпуска!$D$5:$D$17&gt;=FK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FK$5)*(Отпуска!$D$5:$D$16&gt;=FK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FL9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FL$5)*(Отпуска!$D$5:$D$17&gt;=FL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FL$5)*(Отпуска!$D$5:$D$16&gt;=FL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FM9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FM$5)*(Отпуска!$D$5:$D$17&gt;=FM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FM$5)*(Отпуска!$D$5:$D$16&gt;=FM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FN9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FN$5)*(Отпуска!$D$5:$D$17&gt;=FN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FN$5)*(Отпуска!$D$5:$D$16&gt;=FN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FO9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FO$5)*(Отпуска!$D$5:$D$17&gt;=FO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FO$5)*(Отпуска!$D$5:$D$16&gt;=FO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FP9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FP$5)*(Отпуска!$D$5:$D$17&gt;=FP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FP$5)*(Отпуска!$D$5:$D$16&gt;=FP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FQ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FQ$5)*(Отпуска!$D$5:$D$17&gt;=FQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FQ$5)*(Отпуска!$D$5:$D$16&gt;=FQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FR9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FR$5)*(Отпуска!$D$5:$D$17&gt;=FR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FR$5)*(Отпуска!$D$5:$D$16&gt;=FR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FS9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FS$5)*(Отпуска!$D$5:$D$17&gt;=FS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FS$5)*(Отпуска!$D$5:$D$16&gt;=FS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FT9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FT$5)*(Отпуска!$D$5:$D$17&gt;=FT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FT$5)*(Отпуска!$D$5:$D$16&gt;=FT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FU9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FU$5)*(Отпуска!$D$5:$D$17&gt;=FU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FU$5)*(Отпуска!$D$5:$D$16&gt;=FU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FV9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FV$5)*(Отпуска!$D$5:$D$17&gt;=FV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FV$5)*(Отпуска!$D$5:$D$16&gt;=FV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FW9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FW$5)*(Отпуска!$D$5:$D$17&gt;=FW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FW$5)*(Отпуска!$D$5:$D$16&gt;=FW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FX9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FX$5)*(Отпуска!$D$5:$D$17&gt;=FX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FX$5)*(Отпуска!$D$5:$D$16&gt;=FX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FY9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FY$5)*(Отпуска!$D$5:$D$17&gt;=FY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FY$5)*(Отпуска!$D$5:$D$16&gt;=FY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FZ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=FZ$5)*(Отпуска!$D$5:$D$17&gt;=FZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=FZ$5)*(Отпуска!$D$5:$D$16&gt;=FZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GA9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GA$5)*(Отпуска!$D$5:$D$17&gt;=GA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GA$5)*(Отпуска!$D$5:$D$16&gt;=GA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GB9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GB$5)*(Отпуска!$D$5:$D$17&gt;=GB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GB$5)*(Отпуска!$D$5:$D$16&gt;=GB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GC9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GC$5)*(Отпуска!$D$5:$D$17&gt;=GC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GC$5)*(Отпуска!$D$5:$D$16&gt;=GC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GD9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GD$5)*(Отпуска!$D$5:$D$17&gt;=GD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GD$5)*(Отпуска!$D$5:$D$16&gt;=GD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GE9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GE$5)*(Отпуска!$D$5:$D$17&gt;=GE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GE$5)*(Отпуска!$D$5:$D$16&gt;=GE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GF9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GF$5)*(Отпуска!$D$5:$D$17&gt;=GF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GF$5)*(Отпуска!$D$5:$D$16&gt;=GF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GG9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GG$5)*(Отпуска!$D$5:$D$17&gt;=GG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GG$5)*(Отпуска!$D$5:$D$16&gt;=GG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GH9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GH$5)*(Отпуска!$D$5:$D$17&gt;=GH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GH$5)*(Отпуска!$D$5:$D$16&gt;=GH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GI9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GI$5)*(Отпуска!$D$5:$D$17&gt;=GI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GI$5)*(Отпуска!$D$5:$D$16&gt;=GI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GJ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GJ$5)*(Отпуска!$D$5:$D$17&gt;=GJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GJ$5)*(Отпуска!$D$5:$D$16&gt;=GJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GK9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GK$5)*(Отпуска!$D$5:$D$17&gt;=GK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GK$5)*(Отпуска!$D$5:$D$16&gt;=GK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GL9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GL$5)*(Отпуска!$D$5:$D$17&gt;=GL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GL$5)*(Отпуска!$D$5:$D$16&gt;=GL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GM9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GM$5)*(Отпуска!$D$5:$D$17&gt;=GM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GM$5)*(Отпуска!$D$5:$D$16&gt;=GM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GN9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GN$5)*(Отпуска!$D$5:$D$17&gt;=GN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GN$5)*(Отпуска!$D$5:$D$16&gt;=GN$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GO9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GO$5)*(Отпуска!$D$5:$D$17&gt;=GO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GO$5)*(Отпуска!$D$5:$D$16&gt;=GO$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GP9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GP$5)*(Отпуска!$D$5:$D$17&gt;=GP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GP$5)*(Отпуска!$D$5:$D$16&gt;=GP$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GQ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GQ$5)*(Отпуска!$D$5:$D$17&gt;=GQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GQ$5)*(Отпуска!$D$5:$D$16&gt;=GQ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GR9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GR$5)*(Отпуска!$D$5:$D$17&gt;=GR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GR$5)*(Отпуска!$D$5:$D$16&gt;=GR$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GS9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GS$5)*(Отпуска!$D$5:$D$17&gt;=GS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GS$5)*(Отпуска!$D$5:$D$16&gt;=GS$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GT9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GT$5)*(Отпуска!$D$5:$D$17&gt;=GT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GT$5)*(Отпуска!$D$5:$D$16&gt;=GT$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GU9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GU$5)*(Отпуска!$D$5:$D$17&gt;=GU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GU$5)*(Отпуска!$D$5:$D$16&gt;=GU$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GV9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GV$5)*(Отпуска!$D$5:$D$17&gt;=GV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GV$5)*(Отпуска!$D$5:$D$16&gt;=GV$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GW9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GW$5)*(Отпуска!$D$5:$D$17&gt;=GW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GW$5)*(Отпуска!$D$5:$D$16&gt;=GW$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GX9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GX$5)*(Отпуска!$D$5:$D$17&gt;=GX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GX$5)*(Отпуска!$D$5:$D$16&gt;=GX$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GY9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GY$5)*(Отпуска!$D$5:$D$17&gt;=GY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GY$5)*(Отпуска!$D$5:$D$16&gt;=GY$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GZ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=GZ$5)*(Отпуска!$D$5:$D$17&gt;=GZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=GZ$5)*(Отпуска!$D$5:$D$16&gt;=GZ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HA9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HA$5)*(Отпуска!$D$5:$D$17&gt;=HA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HA$5)*(Отпуска!$D$5:$D$16&gt;=HA$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HB9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HB$5)*(Отпуска!$D$5:$D$17&gt;=HB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HB$5)*(Отпуска!$D$5:$D$16&gt;=HB$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HC9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HC$5)*(Отпуска!$D$5:$D$17&gt;=HC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HC$5)*(Отпуска!$D$5:$D$16&gt;=HC$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HD9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HD$5)*(Отпуска!$D$5:$D$17&gt;=HD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HD$5)*(Отпуска!$D$5:$D$16&gt;=HD$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HE9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HE$5)*(Отпуска!$D$5:$D$17&gt;=HE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HE$5)*(Отпуска!$D$5:$D$16&gt;=HE$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HF9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HF$5)*(Отпуска!$D$5:$D$17&gt;=HF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HF$5)*(Отпуска!$D$5:$D$16&gt;=HF$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HG9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HG$5)*(Отпуска!$D$5:$D$17&gt;=HG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HG$5)*(Отпуска!$D$5:$D$16&gt;=HG$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HH9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HH$5)*(Отпуска!$D$5:$D$17&gt;=HH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HH$5)*(Отпуска!$D$5:$D$16&gt;=HH$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HI9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HI$5)*(Отпуска!$D$5:$D$17&gt;=HI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HI$5)*(Отпуска!$D$5:$D$16&gt;=HI$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HJ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HJ$5)*(Отпуска!$D$5:$D$17&gt;=HJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HJ$5)*(Отпуска!$D$5:$D$16&gt;=HJ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HK9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HK$5)*(Отпуска!$D$5:$D$17&gt;=HK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HK$5)*(Отпуска!$D$5:$D$16&gt;=HK$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HL9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HL$5)*(Отпуска!$D$5:$D$17&gt;=HL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HL$5)*(Отпуска!$D$5:$D$16&gt;=HL$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HM9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HM$5)*(Отпуска!$D$5:$D$17&gt;=HM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HM$5)*(Отпуска!$D$5:$D$16&gt;=HM$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HN9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HN$5)*(Отпуска!$D$5:$D$17&gt;=HN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HN$5)*(Отпуска!$D$5:$D$16&gt;=HN$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HO9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HO$5)*(Отпуска!$D$5:$D$17&gt;=HO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HO$5)*(Отпуска!$D$5:$D$16&gt;=HO$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HP9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HP$5)*(Отпуска!$D$5:$D$17&gt;=HP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HP$5)*(Отпуска!$D$5:$D$16&gt;=HP$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HQ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HQ$5)*(Отпуска!$D$5:$D$17&gt;=HQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HQ$5)*(Отпуска!$D$5:$D$16&gt;=HQ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HR9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HR$5)*(Отпуска!$D$5:$D$17&gt;=HR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HR$5)*(Отпуска!$D$5:$D$16&gt;=HR$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HS9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HS$5)*(Отпуска!$D$5:$D$17&gt;=HS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HS$5)*(Отпуска!$D$5:$D$16&gt;=HS$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HT9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HT$5)*(Отпуска!$D$5:$D$17&gt;=HT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HT$5)*(Отпуска!$D$5:$D$16&gt;=HT$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="HU9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HU$5)*(Отпуска!$D$5:$D$17&gt;=HU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HU$5)*(Отпуска!$D$5:$D$16&gt;=HU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HV9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HV$5)*(Отпуска!$D$5:$D$17&gt;=HV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HV$5)*(Отпуска!$D$5:$D$16&gt;=HV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HW9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HW$5)*(Отпуска!$D$5:$D$17&gt;=HW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HW$5)*(Отпуска!$D$5:$D$16&gt;=HW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HX9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HX$5)*(Отпуска!$D$5:$D$17&gt;=HX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HX$5)*(Отпуска!$D$5:$D$16&gt;=HX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HY9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HY$5)*(Отпуска!$D$5:$D$17&gt;=HY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HY$5)*(Отпуска!$D$5:$D$16&gt;=HY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HZ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=HZ$5)*(Отпуска!$D$5:$D$17&gt;=HZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=HZ$5)*(Отпуска!$D$5:$D$16&gt;=HZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IA9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IA$5)*(Отпуска!$D$5:$D$17&gt;=IA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IA$5)*(Отпуска!$D$5:$D$16&gt;=IA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IB9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IB$5)*(Отпуска!$D$5:$D$17&gt;=IB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IB$5)*(Отпуска!$D$5:$D$16&gt;=IB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IC9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IC$5)*(Отпуска!$D$5:$D$17&gt;=IC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IC$5)*(Отпуска!$D$5:$D$16&gt;=IC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ID9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=ID$5)*(Отпуска!$D$5:$D$17&gt;=ID$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=ID$5)*(Отпуска!$D$5:$D$16&gt;=ID$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IE9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IE$5)*(Отпуска!$D$5:$D$17&gt;=IE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IE$5)*(Отпуска!$D$5:$D$16&gt;=IE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IF9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IF$5)*(Отпуска!$D$5:$D$17&gt;=IF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IF$5)*(Отпуска!$D$5:$D$16&gt;=IF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IG9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IG$5)*(Отпуска!$D$5:$D$17&gt;=IG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IG$5)*(Отпуска!$D$5:$D$16&gt;=IG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IH9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IH$5)*(Отпуска!$D$5:$D$17&gt;=IH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IH$5)*(Отпуска!$D$5:$D$16&gt;=IH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="II9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=II$5)*(Отпуска!$D$5:$D$17&gt;=II$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=II$5)*(Отпуска!$D$5:$D$16&gt;=II$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IJ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IJ$5)*(Отпуска!$D$5:$D$17&gt;=IJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IJ$5)*(Отпуска!$D$5:$D$16&gt;=IJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IK9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IK$5)*(Отпуска!$D$5:$D$17&gt;=IK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IK$5)*(Отпуска!$D$5:$D$16&gt;=IK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IL9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IL$5)*(Отпуска!$D$5:$D$17&gt;=IL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IL$5)*(Отпуска!$D$5:$D$16&gt;=IL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IM9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IM$5)*(Отпуска!$D$5:$D$17&gt;=IM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IM$5)*(Отпуска!$D$5:$D$16&gt;=IM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IN9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IN$5)*(Отпуска!$D$5:$D$17&gt;=IN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IN$5)*(Отпуска!$D$5:$D$16&gt;=IN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IO9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IO$5)*(Отпуска!$D$5:$D$17&gt;=IO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IO$5)*(Отпуска!$D$5:$D$16&gt;=IO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IP9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IP$5)*(Отпуска!$D$5:$D$17&gt;=IP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IP$5)*(Отпуска!$D$5:$D$16&gt;=IP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IQ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IQ$5)*(Отпуска!$D$5:$D$17&gt;=IQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IQ$5)*(Отпуска!$D$5:$D$16&gt;=IQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IR9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IR$5)*(Отпуска!$D$5:$D$17&gt;=IR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IR$5)*(Отпуска!$D$5:$D$16&gt;=IR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IS9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IS$5)*(Отпуска!$D$5:$D$17&gt;=IS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IS$5)*(Отпуска!$D$5:$D$16&gt;=IS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IT9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IT$5)*(Отпуска!$D$5:$D$17&gt;=IT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IT$5)*(Отпуска!$D$5:$D$16&gt;=IT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IU9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IU$5)*(Отпуска!$D$5:$D$17&gt;=IU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IU$5)*(Отпуска!$D$5:$D$16&gt;=IU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IV9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IV$5)*(Отпуска!$D$5:$D$17&gt;=IV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IV$5)*(Отпуска!$D$5:$D$16&gt;=IV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IW9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IW$5)*(Отпуска!$D$5:$D$17&gt;=IW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IW$5)*(Отпуска!$D$5:$D$16&gt;=IW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IX9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IX$5)*(Отпуска!$D$5:$D$17&gt;=IX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IX$5)*(Отпуска!$D$5:$D$16&gt;=IX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IY9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IY$5)*(Отпуска!$D$5:$D$17&gt;=IY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IY$5)*(Отпуска!$D$5:$D$16&gt;=IY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IZ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=IZ$5)*(Отпуска!$D$5:$D$17&gt;=IZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=IZ$5)*(Отпуска!$D$5:$D$16&gt;=IZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JA9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JA$5)*(Отпуска!$D$5:$D$17&gt;=JA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JA$5)*(Отпуска!$D$5:$D$16&gt;=JA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JB9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JB$5)*(Отпуска!$D$5:$D$17&gt;=JB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JB$5)*(Отпуска!$D$5:$D$16&gt;=JB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JC9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JC$5)*(Отпуска!$D$5:$D$17&gt;=JC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JC$5)*(Отпуска!$D$5:$D$16&gt;=JC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JD9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JD$5)*(Отпуска!$D$5:$D$17&gt;=JD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JD$5)*(Отпуска!$D$5:$D$16&gt;=JD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JE9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JE$5)*(Отпуска!$D$5:$D$17&gt;=JE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JE$5)*(Отпуска!$D$5:$D$16&gt;=JE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JF9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JF$5)*(Отпуска!$D$5:$D$17&gt;=JF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JF$5)*(Отпуска!$D$5:$D$16&gt;=JF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JG9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JG$5)*(Отпуска!$D$5:$D$17&gt;=JG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JG$5)*(Отпуска!$D$5:$D$16&gt;=JG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JH9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JH$5)*(Отпуска!$D$5:$D$17&gt;=JH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JH$5)*(Отпуска!$D$5:$D$16&gt;=JH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JI9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JI$5)*(Отпуска!$D$5:$D$17&gt;=JI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JI$5)*(Отпуска!$D$5:$D$16&gt;=JI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JJ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JJ$5)*(Отпуска!$D$5:$D$17&gt;=JJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JJ$5)*(Отпуска!$D$5:$D$16&gt;=JJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JK9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JK$5)*(Отпуска!$D$5:$D$17&gt;=JK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JK$5)*(Отпуска!$D$5:$D$16&gt;=JK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JL9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JL$5)*(Отпуска!$D$5:$D$17&gt;=JL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JL$5)*(Отпуска!$D$5:$D$16&gt;=JL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JM9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JM$5)*(Отпуска!$D$5:$D$17&gt;=JM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JM$5)*(Отпуска!$D$5:$D$16&gt;=JM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JN9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JN$5)*(Отпуска!$D$5:$D$17&gt;=JN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JN$5)*(Отпуска!$D$5:$D$16&gt;=JN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JO9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JO$5)*(Отпуска!$D$5:$D$17&gt;=JO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JO$5)*(Отпуска!$D$5:$D$16&gt;=JO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JP9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JP$5)*(Отпуска!$D$5:$D$17&gt;=JP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JP$5)*(Отпуска!$D$5:$D$16&gt;=JP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JQ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JQ$5)*(Отпуска!$D$5:$D$17&gt;=JQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JQ$5)*(Отпуска!$D$5:$D$16&gt;=JQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JR9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JR$5)*(Отпуска!$D$5:$D$17&gt;=JR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JR$5)*(Отпуска!$D$5:$D$16&gt;=JR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JS9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JS$5)*(Отпуска!$D$5:$D$17&gt;=JS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JS$5)*(Отпуска!$D$5:$D$16&gt;=JS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JT9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JT$5)*(Отпуска!$D$5:$D$17&gt;=JT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JT$5)*(Отпуска!$D$5:$D$16&gt;=JT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JU9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JU$5)*(Отпуска!$D$5:$D$17&gt;=JU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JU$5)*(Отпуска!$D$5:$D$16&gt;=JU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JV9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JV$5)*(Отпуска!$D$5:$D$17&gt;=JV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JV$5)*(Отпуска!$D$5:$D$16&gt;=JV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JW9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JW$5)*(Отпуска!$D$5:$D$17&gt;=JW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JW$5)*(Отпуска!$D$5:$D$16&gt;=JW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JX9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JX$5)*(Отпуска!$D$5:$D$17&gt;=JX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JX$5)*(Отпуска!$D$5:$D$16&gt;=JX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JY9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JY$5)*(Отпуска!$D$5:$D$17&gt;=JY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JY$5)*(Отпуска!$D$5:$D$16&gt;=JY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JZ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=JZ$5)*(Отпуска!$D$5:$D$17&gt;=JZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=JZ$5)*(Отпуска!$D$5:$D$16&gt;=JZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KA9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KA$5)*(Отпуска!$D$5:$D$17&gt;=KA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KA$5)*(Отпуска!$D$5:$D$16&gt;=KA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KB9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KB$5)*(Отпуска!$D$5:$D$17&gt;=KB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KB$5)*(Отпуска!$D$5:$D$16&gt;=KB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KC9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KC$5)*(Отпуска!$D$5:$D$17&gt;=KC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KC$5)*(Отпуска!$D$5:$D$16&gt;=KC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KD9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KD$5)*(Отпуска!$D$5:$D$17&gt;=KD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KD$5)*(Отпуска!$D$5:$D$16&gt;=KD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KE9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KE$5)*(Отпуска!$D$5:$D$17&gt;=KE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KE$5)*(Отпуска!$D$5:$D$16&gt;=KE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KF9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KF$5)*(Отпуска!$D$5:$D$17&gt;=KF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KF$5)*(Отпуска!$D$5:$D$16&gt;=KF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KG9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KG$5)*(Отпуска!$D$5:$D$17&gt;=KG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KG$5)*(Отпуска!$D$5:$D$16&gt;=KG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KH9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KH$5)*(Отпуска!$D$5:$D$17&gt;=KH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KH$5)*(Отпуска!$D$5:$D$16&gt;=KH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KI9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KI$5)*(Отпуска!$D$5:$D$17&gt;=KI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KI$5)*(Отпуска!$D$5:$D$16&gt;=KI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KJ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KJ$5)*(Отпуска!$D$5:$D$17&gt;=KJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KJ$5)*(Отпуска!$D$5:$D$16&gt;=KJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KK9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KK$5)*(Отпуска!$D$5:$D$17&gt;=KK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KK$5)*(Отпуска!$D$5:$D$16&gt;=KK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KL9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KL$5)*(Отпуска!$D$5:$D$17&gt;=KL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KL$5)*(Отпуска!$D$5:$D$16&gt;=KL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KM9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KM$5)*(Отпуска!$D$5:$D$17&gt;=KM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KM$5)*(Отпуска!$D$5:$D$16&gt;=KM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KN9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KN$5)*(Отпуска!$D$5:$D$17&gt;=KN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KN$5)*(Отпуска!$D$5:$D$16&gt;=KN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KO9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KO$5)*(Отпуска!$D$5:$D$17&gt;=KO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KO$5)*(Отпуска!$D$5:$D$16&gt;=KO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KP9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KP$5)*(Отпуска!$D$5:$D$17&gt;=KP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KP$5)*(Отпуска!$D$5:$D$16&gt;=KP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KQ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KQ$5)*(Отпуска!$D$5:$D$17&gt;=KQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KQ$5)*(Отпуска!$D$5:$D$16&gt;=KQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KR9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KR$5)*(Отпуска!$D$5:$D$17&gt;=KR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KR$5)*(Отпуска!$D$5:$D$16&gt;=KR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KS9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KS$5)*(Отпуска!$D$5:$D$17&gt;=KS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KS$5)*(Отпуска!$D$5:$D$16&gt;=KS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KT9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KT$5)*(Отпуска!$D$5:$D$17&gt;=KT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KT$5)*(Отпуска!$D$5:$D$16&gt;=KT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KU9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KU$5)*(Отпуска!$D$5:$D$17&gt;=KU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KU$5)*(Отпуска!$D$5:$D$16&gt;=KU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KV9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KV$5)*(Отпуска!$D$5:$D$17&gt;=KV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KV$5)*(Отпуска!$D$5:$D$16&gt;=KV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KW9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KW$5)*(Отпуска!$D$5:$D$17&gt;=KW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KW$5)*(Отпуска!$D$5:$D$16&gt;=KW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KX9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KX$5)*(Отпуска!$D$5:$D$17&gt;=KX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KX$5)*(Отпуска!$D$5:$D$16&gt;=KX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KY9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KY$5)*(Отпуска!$D$5:$D$17&gt;=KY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KY$5)*(Отпуска!$D$5:$D$16&gt;=KY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KZ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=KZ$5)*(Отпуска!$D$5:$D$17&gt;=KZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=KZ$5)*(Отпуска!$D$5:$D$16&gt;=KZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LA9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LA$5)*(Отпуска!$D$5:$D$17&gt;=LA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LA$5)*(Отпуска!$D$5:$D$16&gt;=LA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LB9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LB$5)*(Отпуска!$D$5:$D$17&gt;=LB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LB$5)*(Отпуска!$D$5:$D$16&gt;=LB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LC9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LC$5)*(Отпуска!$D$5:$D$17&gt;=LC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LC$5)*(Отпуска!$D$5:$D$16&gt;=LC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LD9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LD$5)*(Отпуска!$D$5:$D$17&gt;=LD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LD$5)*(Отпуска!$D$5:$D$16&gt;=LD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LE9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LE$5)*(Отпуска!$D$5:$D$17&gt;=LE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LE$5)*(Отпуска!$D$5:$D$16&gt;=LE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LF9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LF$5)*(Отпуска!$D$5:$D$17&gt;=LF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LF$5)*(Отпуска!$D$5:$D$16&gt;=LF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LG9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LG$5)*(Отпуска!$D$5:$D$17&gt;=LG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LG$5)*(Отпуска!$D$5:$D$16&gt;=LG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LH9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LH$5)*(Отпуска!$D$5:$D$17&gt;=LH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LH$5)*(Отпуска!$D$5:$D$16&gt;=LH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LI9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LI$5)*(Отпуска!$D$5:$D$17&gt;=LI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LI$5)*(Отпуска!$D$5:$D$16&gt;=LI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LJ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LJ$5)*(Отпуска!$D$5:$D$17&gt;=LJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LJ$5)*(Отпуска!$D$5:$D$16&gt;=LJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LK9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LK$5)*(Отпуска!$D$5:$D$17&gt;=LK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LK$5)*(Отпуска!$D$5:$D$16&gt;=LK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LL9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LL$5)*(Отпуска!$D$5:$D$17&gt;=LL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LL$5)*(Отпуска!$D$5:$D$16&gt;=LL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LM9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LM$5)*(Отпуска!$D$5:$D$17&gt;=LM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LM$5)*(Отпуска!$D$5:$D$16&gt;=LM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LN9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LN$5)*(Отпуска!$D$5:$D$17&gt;=LN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LN$5)*(Отпуска!$D$5:$D$16&gt;=LN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LO9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LO$5)*(Отпуска!$D$5:$D$17&gt;=LO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LO$5)*(Отпуска!$D$5:$D$16&gt;=LO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LP9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LP$5)*(Отпуска!$D$5:$D$17&gt;=LP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LP$5)*(Отпуска!$D$5:$D$16&gt;=LP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LQ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LQ$5)*(Отпуска!$D$5:$D$17&gt;=LQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LQ$5)*(Отпуска!$D$5:$D$16&gt;=LQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LR9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LR$5)*(Отпуска!$D$5:$D$17&gt;=LR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LR$5)*(Отпуска!$D$5:$D$16&gt;=LR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LS9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LS$5)*(Отпуска!$D$5:$D$17&gt;=LS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LS$5)*(Отпуска!$D$5:$D$16&gt;=LS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LT9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LT$5)*(Отпуска!$D$5:$D$17&gt;=LT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LT$5)*(Отпуска!$D$5:$D$16&gt;=LT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LU9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LU$5)*(Отпуска!$D$5:$D$17&gt;=LU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LU$5)*(Отпуска!$D$5:$D$16&gt;=LU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LV9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LV$5)*(Отпуска!$D$5:$D$17&gt;=LV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LV$5)*(Отпуска!$D$5:$D$16&gt;=LV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LW9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LW$5)*(Отпуска!$D$5:$D$17&gt;=LW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LW$5)*(Отпуска!$D$5:$D$16&gt;=LW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LX9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LX$5)*(Отпуска!$D$5:$D$17&gt;=LX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LX$5)*(Отпуска!$D$5:$D$16&gt;=LX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LY9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LY$5)*(Отпуска!$D$5:$D$17&gt;=LY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LY$5)*(Отпуска!$D$5:$D$16&gt;=LY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LZ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=LZ$5)*(Отпуска!$D$5:$D$17&gt;=LZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=LZ$5)*(Отпуска!$D$5:$D$16&gt;=LZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MA9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MA$5)*(Отпуска!$D$5:$D$17&gt;=MA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MA$5)*(Отпуска!$D$5:$D$16&gt;=MA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MB9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MB$5)*(Отпуска!$D$5:$D$17&gt;=MB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MB$5)*(Отпуска!$D$5:$D$16&gt;=MB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MC9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MC$5)*(Отпуска!$D$5:$D$17&gt;=MC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MC$5)*(Отпуска!$D$5:$D$16&gt;=MC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MD9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MD$5)*(Отпуска!$D$5:$D$17&gt;=MD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MD$5)*(Отпуска!$D$5:$D$16&gt;=MD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ME9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=ME$5)*(Отпуска!$D$5:$D$17&gt;=ME$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=ME$5)*(Отпуска!$D$5:$D$16&gt;=ME$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MF9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MF$5)*(Отпуска!$D$5:$D$17&gt;=MF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MF$5)*(Отпуска!$D$5:$D$16&gt;=MF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MG9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MG$5)*(Отпуска!$D$5:$D$17&gt;=MG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MG$5)*(Отпуска!$D$5:$D$16&gt;=MG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MH9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MH$5)*(Отпуска!$D$5:$D$17&gt;=MH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MH$5)*(Отпуска!$D$5:$D$16&gt;=MH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MI9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MI$5)*(Отпуска!$D$5:$D$17&gt;=MI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MI$5)*(Отпуска!$D$5:$D$16&gt;=MI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MJ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MJ$5)*(Отпуска!$D$5:$D$17&gt;=MJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MJ$5)*(Отпуска!$D$5:$D$16&gt;=MJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MK9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MK$5)*(Отпуска!$D$5:$D$17&gt;=MK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MK$5)*(Отпуска!$D$5:$D$16&gt;=MK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ML9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=ML$5)*(Отпуска!$D$5:$D$17&gt;=ML$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=ML$5)*(Отпуска!$D$5:$D$16&gt;=ML$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MM9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MM$5)*(Отпуска!$D$5:$D$17&gt;=MM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MM$5)*(Отпуска!$D$5:$D$16&gt;=MM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MN9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MN$5)*(Отпуска!$D$5:$D$17&gt;=MN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MN$5)*(Отпуска!$D$5:$D$16&gt;=MN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MO9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MO$5)*(Отпуска!$D$5:$D$17&gt;=MO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MO$5)*(Отпуска!$D$5:$D$16&gt;=MO$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="MP9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MP$5)*(Отпуска!$D$5:$D$17&gt;=MP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MP$5)*(Отпуска!$D$5:$D$16&gt;=MP$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="MQ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MQ$5)*(Отпуска!$D$5:$D$17&gt;=MQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MQ$5)*(Отпуска!$D$5:$D$16&gt;=MQ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="MR9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MR$5)*(Отпуска!$D$5:$D$17&gt;=MR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MR$5)*(Отпуска!$D$5:$D$16&gt;=MR$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="MS9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MS$5)*(Отпуска!$D$5:$D$17&gt;=MS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MS$5)*(Отпуска!$D$5:$D$16&gt;=MS$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="MT9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MT$5)*(Отпуска!$D$5:$D$17&gt;=MT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MT$5)*(Отпуска!$D$5:$D$16&gt;=MT$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="MU9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MU$5)*(Отпуска!$D$5:$D$17&gt;=MU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MU$5)*(Отпуска!$D$5:$D$16&gt;=MU$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="MV9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MV$5)*(Отпуска!$D$5:$D$17&gt;=MV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MV$5)*(Отпуска!$D$5:$D$16&gt;=MV$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="MW9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MW$5)*(Отпуска!$D$5:$D$17&gt;=MW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MW$5)*(Отпуска!$D$5:$D$16&gt;=MW$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="MX9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MX$5)*(Отпуска!$D$5:$D$17&gt;=MX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MX$5)*(Отпуска!$D$5:$D$16&gt;=MX$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="MY9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MY$5)*(Отпуска!$D$5:$D$17&gt;=MY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MY$5)*(Отпуска!$D$5:$D$16&gt;=MY$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="MZ9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=MZ$5)*(Отпуска!$D$5:$D$17&gt;=MZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=MZ$5)*(Отпуска!$D$5:$D$16&gt;=MZ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="NA9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=NA$5)*(Отпуска!$D$5:$D$17&gt;=NA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=NA$5)*(Отпуска!$D$5:$D$16&gt;=NA$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="NB9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=NB$5)*(Отпуска!$D$5:$D$17&gt;=NB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=NB$5)*(Отпуска!$D$5:$D$16&gt;=NB$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="NC9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=NC$5)*(Отпуска!$D$5:$D$17&gt;=NC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=NC$5)*(Отпуска!$D$5:$D$16&gt;=NC$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="ND9" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A9)*(Отпуска!$B$5:$B$17&lt;=ND$5)*(Отпуска!$D$5:$D$17&gt;=ND$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A9)*(Отпуска!$B$5:$B$16&lt;=ND$5)*(Отпуска!$D$5:$D$16&gt;=ND$5))&gt;0,"О","")</f>
         <v/>
       </c>
     </row>
@@ -8609,1467 +8609,1467 @@
         <v>57</v>
       </c>
       <c r="C10" s="9" t="n">
-        <f aca="false">SUMIF(Отпуска!$A$5:$A$17,$A10,Отпуска!$C$5:$C$17)</f>
+        <f aca="false">SUMIF(Отпуска!$A$5:$A$16,$A10,Отпуска!$C$5:$C$16)</f>
         <v>57</v>
       </c>
       <c r="D10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=D$5)*(Отпуска!$D$5:$D$17&gt;=D$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=D$5)*(Отпуска!$D$5:$D$16&gt;=D$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="E10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=E$5)*(Отпуска!$D$5:$D$17&gt;=E$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=E$5)*(Отпуска!$D$5:$D$16&gt;=E$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="F10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=F$5)*(Отпуска!$D$5:$D$17&gt;=F$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=F$5)*(Отпуска!$D$5:$D$16&gt;=F$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="G10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=G$5)*(Отпуска!$D$5:$D$17&gt;=G$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=G$5)*(Отпуска!$D$5:$D$16&gt;=G$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="H10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=H$5)*(Отпуска!$D$5:$D$17&gt;=H$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=H$5)*(Отпуска!$D$5:$D$16&gt;=H$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="I10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=I$5)*(Отпуска!$D$5:$D$17&gt;=I$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=I$5)*(Отпуска!$D$5:$D$16&gt;=I$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="J10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=J$5)*(Отпуска!$D$5:$D$17&gt;=J$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=J$5)*(Отпуска!$D$5:$D$16&gt;=J$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="K10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=K$5)*(Отпуска!$D$5:$D$17&gt;=K$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=K$5)*(Отпуска!$D$5:$D$16&gt;=K$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="L10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=L$5)*(Отпуска!$D$5:$D$17&gt;=L$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=L$5)*(Отпуска!$D$5:$D$16&gt;=L$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="M10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=M$5)*(Отпуска!$D$5:$D$17&gt;=M$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=M$5)*(Отпуска!$D$5:$D$16&gt;=M$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="N10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=N$5)*(Отпуска!$D$5:$D$17&gt;=N$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=N$5)*(Отпуска!$D$5:$D$16&gt;=N$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="O10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=O$5)*(Отпуска!$D$5:$D$17&gt;=O$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=O$5)*(Отпуска!$D$5:$D$16&gt;=O$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="P10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=P$5)*(Отпуска!$D$5:$D$17&gt;=P$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=P$5)*(Отпуска!$D$5:$D$16&gt;=P$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="Q10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=Q$5)*(Отпуска!$D$5:$D$17&gt;=Q$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=Q$5)*(Отпуска!$D$5:$D$16&gt;=Q$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="R10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=R$5)*(Отпуска!$D$5:$D$17&gt;=R$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=R$5)*(Отпуска!$D$5:$D$16&gt;=R$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="S10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=S$5)*(Отпуска!$D$5:$D$17&gt;=S$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=S$5)*(Отпуска!$D$5:$D$16&gt;=S$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="T10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=T$5)*(Отпуска!$D$5:$D$17&gt;=T$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=T$5)*(Отпуска!$D$5:$D$16&gt;=T$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="U10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=U$5)*(Отпуска!$D$5:$D$17&gt;=U$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=U$5)*(Отпуска!$D$5:$D$16&gt;=U$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="V10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=V$5)*(Отпуска!$D$5:$D$17&gt;=V$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=V$5)*(Отпуска!$D$5:$D$16&gt;=V$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="W10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=W$5)*(Отпуска!$D$5:$D$17&gt;=W$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=W$5)*(Отпуска!$D$5:$D$16&gt;=W$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="X10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=X$5)*(Отпуска!$D$5:$D$17&gt;=X$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=X$5)*(Отпуска!$D$5:$D$16&gt;=X$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="Y10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=Y$5)*(Отпуска!$D$5:$D$17&gt;=Y$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=Y$5)*(Отпуска!$D$5:$D$16&gt;=Y$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="Z10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=Z$5)*(Отпуска!$D$5:$D$17&gt;=Z$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=Z$5)*(Отпуска!$D$5:$D$16&gt;=Z$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AA10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AA$5)*(Отпуска!$D$5:$D$17&gt;=AA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AA$5)*(Отпуска!$D$5:$D$16&gt;=AA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AB10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AB$5)*(Отпуска!$D$5:$D$17&gt;=AB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AB$5)*(Отпуска!$D$5:$D$16&gt;=AB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AC10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AC$5)*(Отпуска!$D$5:$D$17&gt;=AC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AC$5)*(Отпуска!$D$5:$D$16&gt;=AC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AD10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AD$5)*(Отпуска!$D$5:$D$17&gt;=AD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AD$5)*(Отпуска!$D$5:$D$16&gt;=AD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AE10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AE$5)*(Отпуска!$D$5:$D$17&gt;=AE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AE$5)*(Отпуска!$D$5:$D$16&gt;=AE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AF10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AF$5)*(Отпуска!$D$5:$D$17&gt;=AF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AF$5)*(Отпуска!$D$5:$D$16&gt;=AF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AG10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AG$5)*(Отпуска!$D$5:$D$17&gt;=AG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AG$5)*(Отпуска!$D$5:$D$16&gt;=AG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AH10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AH$5)*(Отпуска!$D$5:$D$17&gt;=AH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AH$5)*(Отпуска!$D$5:$D$16&gt;=AH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AI10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AI$5)*(Отпуска!$D$5:$D$17&gt;=AI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AI$5)*(Отпуска!$D$5:$D$16&gt;=AI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AJ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AJ$5)*(Отпуска!$D$5:$D$17&gt;=AJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AJ$5)*(Отпуска!$D$5:$D$16&gt;=AJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AK10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AK$5)*(Отпуска!$D$5:$D$17&gt;=AK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AK$5)*(Отпуска!$D$5:$D$16&gt;=AK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AL10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AL$5)*(Отпуска!$D$5:$D$17&gt;=AL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AL$5)*(Отпуска!$D$5:$D$16&gt;=AL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AM10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AM$5)*(Отпуска!$D$5:$D$17&gt;=AM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AM$5)*(Отпуска!$D$5:$D$16&gt;=AM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AN10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AN$5)*(Отпуска!$D$5:$D$17&gt;=AN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AN$5)*(Отпуска!$D$5:$D$16&gt;=AN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AO10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AO$5)*(Отпуска!$D$5:$D$17&gt;=AO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AO$5)*(Отпуска!$D$5:$D$16&gt;=AO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AP10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AP$5)*(Отпуска!$D$5:$D$17&gt;=AP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AP$5)*(Отпуска!$D$5:$D$16&gt;=AP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AQ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AQ$5)*(Отпуска!$D$5:$D$17&gt;=AQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AQ$5)*(Отпуска!$D$5:$D$16&gt;=AQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AR10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AR$5)*(Отпуска!$D$5:$D$17&gt;=AR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AR$5)*(Отпуска!$D$5:$D$16&gt;=AR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AS10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AS$5)*(Отпуска!$D$5:$D$17&gt;=AS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AS$5)*(Отпуска!$D$5:$D$16&gt;=AS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AT10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AT$5)*(Отпуска!$D$5:$D$17&gt;=AT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AT$5)*(Отпуска!$D$5:$D$16&gt;=AT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AU10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AU$5)*(Отпуска!$D$5:$D$17&gt;=AU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AU$5)*(Отпуска!$D$5:$D$16&gt;=AU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AV10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AV$5)*(Отпуска!$D$5:$D$17&gt;=AV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AV$5)*(Отпуска!$D$5:$D$16&gt;=AV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AW10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AW$5)*(Отпуска!$D$5:$D$17&gt;=AW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AW$5)*(Отпуска!$D$5:$D$16&gt;=AW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AX10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AX$5)*(Отпуска!$D$5:$D$17&gt;=AX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AX$5)*(Отпуска!$D$5:$D$16&gt;=AX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AY10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AY$5)*(Отпуска!$D$5:$D$17&gt;=AY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AY$5)*(Отпуска!$D$5:$D$16&gt;=AY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="AZ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=AZ$5)*(Отпуска!$D$5:$D$17&gt;=AZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=AZ$5)*(Отпуска!$D$5:$D$16&gt;=AZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BA10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BA$5)*(Отпуска!$D$5:$D$17&gt;=BA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BA$5)*(Отпуска!$D$5:$D$16&gt;=BA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BB10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BB$5)*(Отпуска!$D$5:$D$17&gt;=BB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BB$5)*(Отпуска!$D$5:$D$16&gt;=BB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BC10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BC$5)*(Отпуска!$D$5:$D$17&gt;=BC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BC$5)*(Отпуска!$D$5:$D$16&gt;=BC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BD10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BD$5)*(Отпуска!$D$5:$D$17&gt;=BD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BD$5)*(Отпуска!$D$5:$D$16&gt;=BD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BE10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BE$5)*(Отпуска!$D$5:$D$17&gt;=BE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BE$5)*(Отпуска!$D$5:$D$16&gt;=BE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BF10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BF$5)*(Отпуска!$D$5:$D$17&gt;=BF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BF$5)*(Отпуска!$D$5:$D$16&gt;=BF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BG10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BG$5)*(Отпуска!$D$5:$D$17&gt;=BG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BG$5)*(Отпуска!$D$5:$D$16&gt;=BG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BH10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BH$5)*(Отпуска!$D$5:$D$17&gt;=BH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BH$5)*(Отпуска!$D$5:$D$16&gt;=BH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BI10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BI$5)*(Отпуска!$D$5:$D$17&gt;=BI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BI$5)*(Отпуска!$D$5:$D$16&gt;=BI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BJ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BJ$5)*(Отпуска!$D$5:$D$17&gt;=BJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BJ$5)*(Отпуска!$D$5:$D$16&gt;=BJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BK10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BK$5)*(Отпуска!$D$5:$D$17&gt;=BK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BK$5)*(Отпуска!$D$5:$D$16&gt;=BK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BL10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BL$5)*(Отпуска!$D$5:$D$17&gt;=BL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BL$5)*(Отпуска!$D$5:$D$16&gt;=BL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BM10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BM$5)*(Отпуска!$D$5:$D$17&gt;=BM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BM$5)*(Отпуска!$D$5:$D$16&gt;=BM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BN10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BN$5)*(Отпуска!$D$5:$D$17&gt;=BN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BN$5)*(Отпуска!$D$5:$D$16&gt;=BN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BO10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BO$5)*(Отпуска!$D$5:$D$17&gt;=BO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BO$5)*(Отпуска!$D$5:$D$16&gt;=BO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BP10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BP$5)*(Отпуска!$D$5:$D$17&gt;=BP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BP$5)*(Отпуска!$D$5:$D$16&gt;=BP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BQ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BQ$5)*(Отпуска!$D$5:$D$17&gt;=BQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BQ$5)*(Отпуска!$D$5:$D$16&gt;=BQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BR10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BR$5)*(Отпуска!$D$5:$D$17&gt;=BR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BR$5)*(Отпуска!$D$5:$D$16&gt;=BR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="BS10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BS$5)*(Отпуска!$D$5:$D$17&gt;=BS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BS$5)*(Отпуска!$D$5:$D$16&gt;=BS$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="BT10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BT$5)*(Отпуска!$D$5:$D$17&gt;=BT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BT$5)*(Отпуска!$D$5:$D$16&gt;=BT$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="BU10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BU$5)*(Отпуска!$D$5:$D$17&gt;=BU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BU$5)*(Отпуска!$D$5:$D$16&gt;=BU$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="BV10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BV$5)*(Отпуска!$D$5:$D$17&gt;=BV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BV$5)*(Отпуска!$D$5:$D$16&gt;=BV$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="BW10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BW$5)*(Отпуска!$D$5:$D$17&gt;=BW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BW$5)*(Отпуска!$D$5:$D$16&gt;=BW$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="BX10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BX$5)*(Отпуска!$D$5:$D$17&gt;=BX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BX$5)*(Отпуска!$D$5:$D$16&gt;=BX$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="BY10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BY$5)*(Отпуска!$D$5:$D$17&gt;=BY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BY$5)*(Отпуска!$D$5:$D$16&gt;=BY$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="BZ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=BZ$5)*(Отпуска!$D$5:$D$17&gt;=BZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=BZ$5)*(Отпуска!$D$5:$D$16&gt;=BZ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="CA10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CA$5)*(Отпуска!$D$5:$D$17&gt;=CA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CA$5)*(Отпуска!$D$5:$D$16&gt;=CA$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="CB10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CB$5)*(Отпуска!$D$5:$D$17&gt;=CB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CB$5)*(Отпуска!$D$5:$D$16&gt;=CB$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="CC10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CC$5)*(Отпуска!$D$5:$D$17&gt;=CC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CC$5)*(Отпуска!$D$5:$D$16&gt;=CC$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="CD10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CD$5)*(Отпуска!$D$5:$D$17&gt;=CD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CD$5)*(Отпуска!$D$5:$D$16&gt;=CD$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="CE10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CE$5)*(Отпуска!$D$5:$D$17&gt;=CE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CE$5)*(Отпуска!$D$5:$D$16&gt;=CE$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="CF10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CF$5)*(Отпуска!$D$5:$D$17&gt;=CF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CF$5)*(Отпуска!$D$5:$D$16&gt;=CF$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="CG10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CG$5)*(Отпуска!$D$5:$D$17&gt;=CG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CG$5)*(Отпуска!$D$5:$D$16&gt;=CG$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="CH10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CH$5)*(Отпуска!$D$5:$D$17&gt;=CH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CH$5)*(Отпуска!$D$5:$D$16&gt;=CH$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="CI10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CI$5)*(Отпуска!$D$5:$D$17&gt;=CI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CI$5)*(Отпуска!$D$5:$D$16&gt;=CI$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="CJ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CJ$5)*(Отпуска!$D$5:$D$17&gt;=CJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CJ$5)*(Отпуска!$D$5:$D$16&gt;=CJ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="CK10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CK$5)*(Отпуска!$D$5:$D$17&gt;=CK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CK$5)*(Отпуска!$D$5:$D$16&gt;=CK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CL10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CL$5)*(Отпуска!$D$5:$D$17&gt;=CL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CL$5)*(Отпуска!$D$5:$D$16&gt;=CL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CM10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CM$5)*(Отпуска!$D$5:$D$17&gt;=CM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CM$5)*(Отпуска!$D$5:$D$16&gt;=CM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CN10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CN$5)*(Отпуска!$D$5:$D$17&gt;=CN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CN$5)*(Отпуска!$D$5:$D$16&gt;=CN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CO10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CO$5)*(Отпуска!$D$5:$D$17&gt;=CO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CO$5)*(Отпуска!$D$5:$D$16&gt;=CO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CP10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CP$5)*(Отпуска!$D$5:$D$17&gt;=CP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CP$5)*(Отпуска!$D$5:$D$16&gt;=CP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CQ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CQ$5)*(Отпуска!$D$5:$D$17&gt;=CQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CQ$5)*(Отпуска!$D$5:$D$16&gt;=CQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CR10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CR$5)*(Отпуска!$D$5:$D$17&gt;=CR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CR$5)*(Отпуска!$D$5:$D$16&gt;=CR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CS10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CS$5)*(Отпуска!$D$5:$D$17&gt;=CS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CS$5)*(Отпуска!$D$5:$D$16&gt;=CS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CT10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CT$5)*(Отпуска!$D$5:$D$17&gt;=CT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CT$5)*(Отпуска!$D$5:$D$16&gt;=CT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CU10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CU$5)*(Отпуска!$D$5:$D$17&gt;=CU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CU$5)*(Отпуска!$D$5:$D$16&gt;=CU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CV10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CV$5)*(Отпуска!$D$5:$D$17&gt;=CV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CV$5)*(Отпуска!$D$5:$D$16&gt;=CV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CW10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CW$5)*(Отпуска!$D$5:$D$17&gt;=CW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CW$5)*(Отпуска!$D$5:$D$16&gt;=CW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CX10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CX$5)*(Отпуска!$D$5:$D$17&gt;=CX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CX$5)*(Отпуска!$D$5:$D$16&gt;=CX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CY10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CY$5)*(Отпуска!$D$5:$D$17&gt;=CY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CY$5)*(Отпуска!$D$5:$D$16&gt;=CY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="CZ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=CZ$5)*(Отпуска!$D$5:$D$17&gt;=CZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=CZ$5)*(Отпуска!$D$5:$D$16&gt;=CZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DA10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DA$5)*(Отпуска!$D$5:$D$17&gt;=DA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DA$5)*(Отпуска!$D$5:$D$16&gt;=DA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DB10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DB$5)*(Отпуска!$D$5:$D$17&gt;=DB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DB$5)*(Отпуска!$D$5:$D$16&gt;=DB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DC10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DC$5)*(Отпуска!$D$5:$D$17&gt;=DC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DC$5)*(Отпуска!$D$5:$D$16&gt;=DC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DD10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DD$5)*(Отпуска!$D$5:$D$17&gt;=DD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DD$5)*(Отпуска!$D$5:$D$16&gt;=DD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DE10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DE$5)*(Отпуска!$D$5:$D$17&gt;=DE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DE$5)*(Отпуска!$D$5:$D$16&gt;=DE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DF10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DF$5)*(Отпуска!$D$5:$D$17&gt;=DF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DF$5)*(Отпуска!$D$5:$D$16&gt;=DF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DG10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DG$5)*(Отпуска!$D$5:$D$17&gt;=DG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DG$5)*(Отпуска!$D$5:$D$16&gt;=DG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DH10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DH$5)*(Отпуска!$D$5:$D$17&gt;=DH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DH$5)*(Отпуска!$D$5:$D$16&gt;=DH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DI10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DI$5)*(Отпуска!$D$5:$D$17&gt;=DI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DI$5)*(Отпуска!$D$5:$D$16&gt;=DI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DJ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DJ$5)*(Отпуска!$D$5:$D$17&gt;=DJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DJ$5)*(Отпуска!$D$5:$D$16&gt;=DJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DK10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DK$5)*(Отпуска!$D$5:$D$17&gt;=DK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DK$5)*(Отпуска!$D$5:$D$16&gt;=DK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DL10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DL$5)*(Отпуска!$D$5:$D$17&gt;=DL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DL$5)*(Отпуска!$D$5:$D$16&gt;=DL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DM10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DM$5)*(Отпуска!$D$5:$D$17&gt;=DM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DM$5)*(Отпуска!$D$5:$D$16&gt;=DM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DN10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DN$5)*(Отпуска!$D$5:$D$17&gt;=DN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DN$5)*(Отпуска!$D$5:$D$16&gt;=DN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DO10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DO$5)*(Отпуска!$D$5:$D$17&gt;=DO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DO$5)*(Отпуска!$D$5:$D$16&gt;=DO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DP10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DP$5)*(Отпуска!$D$5:$D$17&gt;=DP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DP$5)*(Отпуска!$D$5:$D$16&gt;=DP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DQ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DQ$5)*(Отпуска!$D$5:$D$17&gt;=DQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DQ$5)*(Отпуска!$D$5:$D$16&gt;=DQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DR10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DR$5)*(Отпуска!$D$5:$D$17&gt;=DR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DR$5)*(Отпуска!$D$5:$D$16&gt;=DR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DS10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DS$5)*(Отпуска!$D$5:$D$17&gt;=DS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DS$5)*(Отпуска!$D$5:$D$16&gt;=DS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DT10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DT$5)*(Отпуска!$D$5:$D$17&gt;=DT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DT$5)*(Отпуска!$D$5:$D$16&gt;=DT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DU10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DU$5)*(Отпуска!$D$5:$D$17&gt;=DU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DU$5)*(Отпуска!$D$5:$D$16&gt;=DU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DV10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DV$5)*(Отпуска!$D$5:$D$17&gt;=DV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DV$5)*(Отпуска!$D$5:$D$16&gt;=DV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DW10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DW$5)*(Отпуска!$D$5:$D$17&gt;=DW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DW$5)*(Отпуска!$D$5:$D$16&gt;=DW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DX10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DX$5)*(Отпуска!$D$5:$D$17&gt;=DX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DX$5)*(Отпуска!$D$5:$D$16&gt;=DX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DY10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DY$5)*(Отпуска!$D$5:$D$17&gt;=DY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DY$5)*(Отпуска!$D$5:$D$16&gt;=DY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="DZ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=DZ$5)*(Отпуска!$D$5:$D$17&gt;=DZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=DZ$5)*(Отпуска!$D$5:$D$16&gt;=DZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EA10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EA$5)*(Отпуска!$D$5:$D$17&gt;=EA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EA$5)*(Отпуска!$D$5:$D$16&gt;=EA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EB10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EB$5)*(Отпуска!$D$5:$D$17&gt;=EB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EB$5)*(Отпуска!$D$5:$D$16&gt;=EB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EC10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EC$5)*(Отпуска!$D$5:$D$17&gt;=EC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EC$5)*(Отпуска!$D$5:$D$16&gt;=EC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ED10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=ED$5)*(Отпуска!$D$5:$D$17&gt;=ED$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=ED$5)*(Отпуска!$D$5:$D$16&gt;=ED$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EE10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EE$5)*(Отпуска!$D$5:$D$17&gt;=EE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EE$5)*(Отпуска!$D$5:$D$16&gt;=EE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EF10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EF$5)*(Отпуска!$D$5:$D$17&gt;=EF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EF$5)*(Отпуска!$D$5:$D$16&gt;=EF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EG10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EG$5)*(Отпуска!$D$5:$D$17&gt;=EG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EG$5)*(Отпуска!$D$5:$D$16&gt;=EG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EH10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EH$5)*(Отпуска!$D$5:$D$17&gt;=EH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EH$5)*(Отпуска!$D$5:$D$16&gt;=EH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EI10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EI$5)*(Отпуска!$D$5:$D$17&gt;=EI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EI$5)*(Отпуска!$D$5:$D$16&gt;=EI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EJ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EJ$5)*(Отпуска!$D$5:$D$17&gt;=EJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EJ$5)*(Отпуска!$D$5:$D$16&gt;=EJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EK10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EK$5)*(Отпуска!$D$5:$D$17&gt;=EK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EK$5)*(Отпуска!$D$5:$D$16&gt;=EK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EL10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EL$5)*(Отпуска!$D$5:$D$17&gt;=EL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EL$5)*(Отпуска!$D$5:$D$16&gt;=EL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EM10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EM$5)*(Отпуска!$D$5:$D$17&gt;=EM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EM$5)*(Отпуска!$D$5:$D$16&gt;=EM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EN10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EN$5)*(Отпуска!$D$5:$D$17&gt;=EN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EN$5)*(Отпуска!$D$5:$D$16&gt;=EN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EO10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EO$5)*(Отпуска!$D$5:$D$17&gt;=EO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EO$5)*(Отпуска!$D$5:$D$16&gt;=EO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EP10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EP$5)*(Отпуска!$D$5:$D$17&gt;=EP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EP$5)*(Отпуска!$D$5:$D$16&gt;=EP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EQ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EQ$5)*(Отпуска!$D$5:$D$17&gt;=EQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EQ$5)*(Отпуска!$D$5:$D$16&gt;=EQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ER10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=ER$5)*(Отпуска!$D$5:$D$17&gt;=ER$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=ER$5)*(Отпуска!$D$5:$D$16&gt;=ER$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ES10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=ES$5)*(Отпуска!$D$5:$D$17&gt;=ES$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=ES$5)*(Отпуска!$D$5:$D$16&gt;=ES$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ET10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=ET$5)*(Отпуска!$D$5:$D$17&gt;=ET$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=ET$5)*(Отпуска!$D$5:$D$16&gt;=ET$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EU10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EU$5)*(Отпуска!$D$5:$D$17&gt;=EU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EU$5)*(Отпуска!$D$5:$D$16&gt;=EU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EV10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EV$5)*(Отпуска!$D$5:$D$17&gt;=EV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EV$5)*(Отпуска!$D$5:$D$16&gt;=EV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EW10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EW$5)*(Отпуска!$D$5:$D$17&gt;=EW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EW$5)*(Отпуска!$D$5:$D$16&gt;=EW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EX10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EX$5)*(Отпуска!$D$5:$D$17&gt;=EX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EX$5)*(Отпуска!$D$5:$D$16&gt;=EX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EY10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EY$5)*(Отпуска!$D$5:$D$17&gt;=EY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EY$5)*(Отпуска!$D$5:$D$16&gt;=EY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="EZ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=EZ$5)*(Отпуска!$D$5:$D$17&gt;=EZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=EZ$5)*(Отпуска!$D$5:$D$16&gt;=EZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FA10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FA$5)*(Отпуска!$D$5:$D$17&gt;=FA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FA$5)*(Отпуска!$D$5:$D$16&gt;=FA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FB10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FB$5)*(Отпуска!$D$5:$D$17&gt;=FB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FB$5)*(Отпуска!$D$5:$D$16&gt;=FB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FC10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FC$5)*(Отпуска!$D$5:$D$17&gt;=FC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FC$5)*(Отпуска!$D$5:$D$16&gt;=FC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FD10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FD$5)*(Отпуска!$D$5:$D$17&gt;=FD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FD$5)*(Отпуска!$D$5:$D$16&gt;=FD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FE10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FE$5)*(Отпуска!$D$5:$D$17&gt;=FE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FE$5)*(Отпуска!$D$5:$D$16&gt;=FE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FF10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FF$5)*(Отпуска!$D$5:$D$17&gt;=FF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FF$5)*(Отпуска!$D$5:$D$16&gt;=FF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FG10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FG$5)*(Отпуска!$D$5:$D$17&gt;=FG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FG$5)*(Отпуска!$D$5:$D$16&gt;=FG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FH10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FH$5)*(Отпуска!$D$5:$D$17&gt;=FH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FH$5)*(Отпуска!$D$5:$D$16&gt;=FH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FI10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FI$5)*(Отпуска!$D$5:$D$17&gt;=FI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FI$5)*(Отпуска!$D$5:$D$16&gt;=FI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FJ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FJ$5)*(Отпуска!$D$5:$D$17&gt;=FJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FJ$5)*(Отпуска!$D$5:$D$16&gt;=FJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FK10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FK$5)*(Отпуска!$D$5:$D$17&gt;=FK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FK$5)*(Отпуска!$D$5:$D$16&gt;=FK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FL10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FL$5)*(Отпуска!$D$5:$D$17&gt;=FL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FL$5)*(Отпуска!$D$5:$D$16&gt;=FL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="FM10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FM$5)*(Отпуска!$D$5:$D$17&gt;=FM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FM$5)*(Отпуска!$D$5:$D$16&gt;=FM$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FN10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FN$5)*(Отпуска!$D$5:$D$17&gt;=FN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FN$5)*(Отпуска!$D$5:$D$16&gt;=FN$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FO10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FO$5)*(Отпуска!$D$5:$D$17&gt;=FO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FO$5)*(Отпуска!$D$5:$D$16&gt;=FO$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FP10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FP$5)*(Отпуска!$D$5:$D$17&gt;=FP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FP$5)*(Отпуска!$D$5:$D$16&gt;=FP$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FQ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FQ$5)*(Отпуска!$D$5:$D$17&gt;=FQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FQ$5)*(Отпуска!$D$5:$D$16&gt;=FQ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FR10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FR$5)*(Отпуска!$D$5:$D$17&gt;=FR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FR$5)*(Отпуска!$D$5:$D$16&gt;=FR$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FS10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FS$5)*(Отпуска!$D$5:$D$17&gt;=FS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FS$5)*(Отпуска!$D$5:$D$16&gt;=FS$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FT10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FT$5)*(Отпуска!$D$5:$D$17&gt;=FT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FT$5)*(Отпуска!$D$5:$D$16&gt;=FT$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FU10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FU$5)*(Отпуска!$D$5:$D$17&gt;=FU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FU$5)*(Отпуска!$D$5:$D$16&gt;=FU$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FV10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FV$5)*(Отпуска!$D$5:$D$17&gt;=FV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FV$5)*(Отпуска!$D$5:$D$16&gt;=FV$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FW10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FW$5)*(Отпуска!$D$5:$D$17&gt;=FW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FW$5)*(Отпуска!$D$5:$D$16&gt;=FW$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FX10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FX$5)*(Отпуска!$D$5:$D$17&gt;=FX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FX$5)*(Отпуска!$D$5:$D$16&gt;=FX$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FY10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FY$5)*(Отпуска!$D$5:$D$17&gt;=FY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FY$5)*(Отпуска!$D$5:$D$16&gt;=FY$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="FZ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=FZ$5)*(Отпуска!$D$5:$D$17&gt;=FZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=FZ$5)*(Отпуска!$D$5:$D$16&gt;=FZ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GA10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GA$5)*(Отпуска!$D$5:$D$17&gt;=GA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GA$5)*(Отпуска!$D$5:$D$16&gt;=GA$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GB10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GB$5)*(Отпуска!$D$5:$D$17&gt;=GB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GB$5)*(Отпуска!$D$5:$D$16&gt;=GB$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GC10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GC$5)*(Отпуска!$D$5:$D$17&gt;=GC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GC$5)*(Отпуска!$D$5:$D$16&gt;=GC$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GD10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GD$5)*(Отпуска!$D$5:$D$17&gt;=GD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GD$5)*(Отпуска!$D$5:$D$16&gt;=GD$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GE10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GE$5)*(Отпуска!$D$5:$D$17&gt;=GE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GE$5)*(Отпуска!$D$5:$D$16&gt;=GE$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GF10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GF$5)*(Отпуска!$D$5:$D$17&gt;=GF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GF$5)*(Отпуска!$D$5:$D$16&gt;=GF$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GG10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GG$5)*(Отпуска!$D$5:$D$17&gt;=GG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GG$5)*(Отпуска!$D$5:$D$16&gt;=GG$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GH10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GH$5)*(Отпуска!$D$5:$D$17&gt;=GH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GH$5)*(Отпуска!$D$5:$D$16&gt;=GH$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GI10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GI$5)*(Отпуска!$D$5:$D$17&gt;=GI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GI$5)*(Отпуска!$D$5:$D$16&gt;=GI$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GJ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GJ$5)*(Отпуска!$D$5:$D$17&gt;=GJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GJ$5)*(Отпуска!$D$5:$D$16&gt;=GJ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GK10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GK$5)*(Отпуска!$D$5:$D$17&gt;=GK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GK$5)*(Отпуска!$D$5:$D$16&gt;=GK$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GL10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GL$5)*(Отпуска!$D$5:$D$17&gt;=GL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GL$5)*(Отпуска!$D$5:$D$16&gt;=GL$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GM10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GM$5)*(Отпуска!$D$5:$D$17&gt;=GM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GM$5)*(Отпуска!$D$5:$D$16&gt;=GM$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GN10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GN$5)*(Отпуска!$D$5:$D$17&gt;=GN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GN$5)*(Отпуска!$D$5:$D$16&gt;=GN$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GO10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GO$5)*(Отпуска!$D$5:$D$17&gt;=GO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GO$5)*(Отпуска!$D$5:$D$16&gt;=GO$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="GP10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GP$5)*(Отпуска!$D$5:$D$17&gt;=GP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GP$5)*(Отпуска!$D$5:$D$16&gt;=GP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GQ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GQ$5)*(Отпуска!$D$5:$D$17&gt;=GQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GQ$5)*(Отпуска!$D$5:$D$16&gt;=GQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GR10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GR$5)*(Отпуска!$D$5:$D$17&gt;=GR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GR$5)*(Отпуска!$D$5:$D$16&gt;=GR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GS10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GS$5)*(Отпуска!$D$5:$D$17&gt;=GS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GS$5)*(Отпуска!$D$5:$D$16&gt;=GS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GT10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GT$5)*(Отпуска!$D$5:$D$17&gt;=GT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GT$5)*(Отпуска!$D$5:$D$16&gt;=GT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GU10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GU$5)*(Отпуска!$D$5:$D$17&gt;=GU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GU$5)*(Отпуска!$D$5:$D$16&gt;=GU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GV10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GV$5)*(Отпуска!$D$5:$D$17&gt;=GV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GV$5)*(Отпуска!$D$5:$D$16&gt;=GV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GW10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GW$5)*(Отпуска!$D$5:$D$17&gt;=GW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GW$5)*(Отпуска!$D$5:$D$16&gt;=GW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GX10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GX$5)*(Отпуска!$D$5:$D$17&gt;=GX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GX$5)*(Отпуска!$D$5:$D$16&gt;=GX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GY10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GY$5)*(Отпуска!$D$5:$D$17&gt;=GY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GY$5)*(Отпуска!$D$5:$D$16&gt;=GY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="GZ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=GZ$5)*(Отпуска!$D$5:$D$17&gt;=GZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=GZ$5)*(Отпуска!$D$5:$D$16&gt;=GZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HA10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HA$5)*(Отпуска!$D$5:$D$17&gt;=HA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HA$5)*(Отпуска!$D$5:$D$16&gt;=HA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HB10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HB$5)*(Отпуска!$D$5:$D$17&gt;=HB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HB$5)*(Отпуска!$D$5:$D$16&gt;=HB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HC10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HC$5)*(Отпуска!$D$5:$D$17&gt;=HC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HC$5)*(Отпуска!$D$5:$D$16&gt;=HC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HD10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HD$5)*(Отпуска!$D$5:$D$17&gt;=HD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HD$5)*(Отпуска!$D$5:$D$16&gt;=HD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HE10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HE$5)*(Отпуска!$D$5:$D$17&gt;=HE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HE$5)*(Отпуска!$D$5:$D$16&gt;=HE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HF10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HF$5)*(Отпуска!$D$5:$D$17&gt;=HF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HF$5)*(Отпуска!$D$5:$D$16&gt;=HF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HG10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HG$5)*(Отпуска!$D$5:$D$17&gt;=HG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HG$5)*(Отпуска!$D$5:$D$16&gt;=HG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HH10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HH$5)*(Отпуска!$D$5:$D$17&gt;=HH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HH$5)*(Отпуска!$D$5:$D$16&gt;=HH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HI10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HI$5)*(Отпуска!$D$5:$D$17&gt;=HI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HI$5)*(Отпуска!$D$5:$D$16&gt;=HI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HJ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HJ$5)*(Отпуска!$D$5:$D$17&gt;=HJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HJ$5)*(Отпуска!$D$5:$D$16&gt;=HJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HK10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HK$5)*(Отпуска!$D$5:$D$17&gt;=HK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HK$5)*(Отпуска!$D$5:$D$16&gt;=HK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HL10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HL$5)*(Отпуска!$D$5:$D$17&gt;=HL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HL$5)*(Отпуска!$D$5:$D$16&gt;=HL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HM10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HM$5)*(Отпуска!$D$5:$D$17&gt;=HM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HM$5)*(Отпуска!$D$5:$D$16&gt;=HM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HN10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HN$5)*(Отпуска!$D$5:$D$17&gt;=HN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HN$5)*(Отпуска!$D$5:$D$16&gt;=HN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HO10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HO$5)*(Отпуска!$D$5:$D$17&gt;=HO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HO$5)*(Отпуска!$D$5:$D$16&gt;=HO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HP10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HP$5)*(Отпуска!$D$5:$D$17&gt;=HP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HP$5)*(Отпуска!$D$5:$D$16&gt;=HP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HQ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HQ$5)*(Отпуска!$D$5:$D$17&gt;=HQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HQ$5)*(Отпуска!$D$5:$D$16&gt;=HQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HR10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HR$5)*(Отпуска!$D$5:$D$17&gt;=HR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HR$5)*(Отпуска!$D$5:$D$16&gt;=HR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HS10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HS$5)*(Отпуска!$D$5:$D$17&gt;=HS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HS$5)*(Отпуска!$D$5:$D$16&gt;=HS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HT10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HT$5)*(Отпуска!$D$5:$D$17&gt;=HT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HT$5)*(Отпуска!$D$5:$D$16&gt;=HT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HU10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HU$5)*(Отпуска!$D$5:$D$17&gt;=HU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HU$5)*(Отпуска!$D$5:$D$16&gt;=HU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HV10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HV$5)*(Отпуска!$D$5:$D$17&gt;=HV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HV$5)*(Отпуска!$D$5:$D$16&gt;=HV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HW10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HW$5)*(Отпуска!$D$5:$D$17&gt;=HW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HW$5)*(Отпуска!$D$5:$D$16&gt;=HW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HX10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HX$5)*(Отпуска!$D$5:$D$17&gt;=HX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HX$5)*(Отпуска!$D$5:$D$16&gt;=HX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HY10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HY$5)*(Отпуска!$D$5:$D$17&gt;=HY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HY$5)*(Отпуска!$D$5:$D$16&gt;=HY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="HZ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=HZ$5)*(Отпуска!$D$5:$D$17&gt;=HZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=HZ$5)*(Отпуска!$D$5:$D$16&gt;=HZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IA10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IA$5)*(Отпуска!$D$5:$D$17&gt;=IA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IA$5)*(Отпуска!$D$5:$D$16&gt;=IA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IB10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IB$5)*(Отпуска!$D$5:$D$17&gt;=IB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IB$5)*(Отпуска!$D$5:$D$16&gt;=IB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IC10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IC$5)*(Отпуска!$D$5:$D$17&gt;=IC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IC$5)*(Отпуска!$D$5:$D$16&gt;=IC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ID10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=ID$5)*(Отпуска!$D$5:$D$17&gt;=ID$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=ID$5)*(Отпуска!$D$5:$D$16&gt;=ID$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IE10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IE$5)*(Отпуска!$D$5:$D$17&gt;=IE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IE$5)*(Отпуска!$D$5:$D$16&gt;=IE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IF10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IF$5)*(Отпуска!$D$5:$D$17&gt;=IF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IF$5)*(Отпуска!$D$5:$D$16&gt;=IF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IG10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IG$5)*(Отпуска!$D$5:$D$17&gt;=IG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IG$5)*(Отпуска!$D$5:$D$16&gt;=IG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IH10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IH$5)*(Отпуска!$D$5:$D$17&gt;=IH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IH$5)*(Отпуска!$D$5:$D$16&gt;=IH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="II10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=II$5)*(Отпуска!$D$5:$D$17&gt;=II$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=II$5)*(Отпуска!$D$5:$D$16&gt;=II$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IJ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IJ$5)*(Отпуска!$D$5:$D$17&gt;=IJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IJ$5)*(Отпуска!$D$5:$D$16&gt;=IJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IK10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IK$5)*(Отпуска!$D$5:$D$17&gt;=IK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IK$5)*(Отпуска!$D$5:$D$16&gt;=IK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IL10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IL$5)*(Отпуска!$D$5:$D$17&gt;=IL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IL$5)*(Отпуска!$D$5:$D$16&gt;=IL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IM10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IM$5)*(Отпуска!$D$5:$D$17&gt;=IM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IM$5)*(Отпуска!$D$5:$D$16&gt;=IM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IN10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IN$5)*(Отпуска!$D$5:$D$17&gt;=IN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IN$5)*(Отпуска!$D$5:$D$16&gt;=IN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IO10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IO$5)*(Отпуска!$D$5:$D$17&gt;=IO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IO$5)*(Отпуска!$D$5:$D$16&gt;=IO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IP10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IP$5)*(Отпуска!$D$5:$D$17&gt;=IP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IP$5)*(Отпуска!$D$5:$D$16&gt;=IP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IQ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IQ$5)*(Отпуска!$D$5:$D$17&gt;=IQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IQ$5)*(Отпуска!$D$5:$D$16&gt;=IQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IR10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IR$5)*(Отпуска!$D$5:$D$17&gt;=IR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IR$5)*(Отпуска!$D$5:$D$16&gt;=IR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IS10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IS$5)*(Отпуска!$D$5:$D$17&gt;=IS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IS$5)*(Отпуска!$D$5:$D$16&gt;=IS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IT10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IT$5)*(Отпуска!$D$5:$D$17&gt;=IT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IT$5)*(Отпуска!$D$5:$D$16&gt;=IT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IU10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IU$5)*(Отпуска!$D$5:$D$17&gt;=IU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IU$5)*(Отпуска!$D$5:$D$16&gt;=IU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IV10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IV$5)*(Отпуска!$D$5:$D$17&gt;=IV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IV$5)*(Отпуска!$D$5:$D$16&gt;=IV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IW10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IW$5)*(Отпуска!$D$5:$D$17&gt;=IW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IW$5)*(Отпуска!$D$5:$D$16&gt;=IW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IX10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IX$5)*(Отпуска!$D$5:$D$17&gt;=IX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IX$5)*(Отпуска!$D$5:$D$16&gt;=IX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IY10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IY$5)*(Отпуска!$D$5:$D$17&gt;=IY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IY$5)*(Отпуска!$D$5:$D$16&gt;=IY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="IZ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=IZ$5)*(Отпуска!$D$5:$D$17&gt;=IZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=IZ$5)*(Отпуска!$D$5:$D$16&gt;=IZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JA10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JA$5)*(Отпуска!$D$5:$D$17&gt;=JA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JA$5)*(Отпуска!$D$5:$D$16&gt;=JA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JB10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JB$5)*(Отпуска!$D$5:$D$17&gt;=JB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JB$5)*(Отпуска!$D$5:$D$16&gt;=JB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JC10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JC$5)*(Отпуска!$D$5:$D$17&gt;=JC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JC$5)*(Отпуска!$D$5:$D$16&gt;=JC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JD10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JD$5)*(Отпуска!$D$5:$D$17&gt;=JD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JD$5)*(Отпуска!$D$5:$D$16&gt;=JD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JE10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JE$5)*(Отпуска!$D$5:$D$17&gt;=JE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JE$5)*(Отпуска!$D$5:$D$16&gt;=JE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JF10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JF$5)*(Отпуска!$D$5:$D$17&gt;=JF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JF$5)*(Отпуска!$D$5:$D$16&gt;=JF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JG10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JG$5)*(Отпуска!$D$5:$D$17&gt;=JG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JG$5)*(Отпуска!$D$5:$D$16&gt;=JG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JH10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JH$5)*(Отпуска!$D$5:$D$17&gt;=JH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JH$5)*(Отпуска!$D$5:$D$16&gt;=JH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JI10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JI$5)*(Отпуска!$D$5:$D$17&gt;=JI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JI$5)*(Отпуска!$D$5:$D$16&gt;=JI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JJ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JJ$5)*(Отпуска!$D$5:$D$17&gt;=JJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JJ$5)*(Отпуска!$D$5:$D$16&gt;=JJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JK10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JK$5)*(Отпуска!$D$5:$D$17&gt;=JK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JK$5)*(Отпуска!$D$5:$D$16&gt;=JK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JL10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JL$5)*(Отпуска!$D$5:$D$17&gt;=JL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JL$5)*(Отпуска!$D$5:$D$16&gt;=JL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JM10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JM$5)*(Отпуска!$D$5:$D$17&gt;=JM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JM$5)*(Отпуска!$D$5:$D$16&gt;=JM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JN10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JN$5)*(Отпуска!$D$5:$D$17&gt;=JN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JN$5)*(Отпуска!$D$5:$D$16&gt;=JN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JO10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JO$5)*(Отпуска!$D$5:$D$17&gt;=JO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JO$5)*(Отпуска!$D$5:$D$16&gt;=JO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JP10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JP$5)*(Отпуска!$D$5:$D$17&gt;=JP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JP$5)*(Отпуска!$D$5:$D$16&gt;=JP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JQ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JQ$5)*(Отпуска!$D$5:$D$17&gt;=JQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JQ$5)*(Отпуска!$D$5:$D$16&gt;=JQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JR10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JR$5)*(Отпуска!$D$5:$D$17&gt;=JR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JR$5)*(Отпуска!$D$5:$D$16&gt;=JR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JS10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JS$5)*(Отпуска!$D$5:$D$17&gt;=JS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JS$5)*(Отпуска!$D$5:$D$16&gt;=JS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JT10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JT$5)*(Отпуска!$D$5:$D$17&gt;=JT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JT$5)*(Отпуска!$D$5:$D$16&gt;=JT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JU10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JU$5)*(Отпуска!$D$5:$D$17&gt;=JU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JU$5)*(Отпуска!$D$5:$D$16&gt;=JU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JV10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JV$5)*(Отпуска!$D$5:$D$17&gt;=JV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JV$5)*(Отпуска!$D$5:$D$16&gt;=JV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JW10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JW$5)*(Отпуска!$D$5:$D$17&gt;=JW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JW$5)*(Отпуска!$D$5:$D$16&gt;=JW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JX10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JX$5)*(Отпуска!$D$5:$D$17&gt;=JX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JX$5)*(Отпуска!$D$5:$D$16&gt;=JX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JY10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JY$5)*(Отпуска!$D$5:$D$17&gt;=JY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JY$5)*(Отпуска!$D$5:$D$16&gt;=JY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="JZ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=JZ$5)*(Отпуска!$D$5:$D$17&gt;=JZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=JZ$5)*(Отпуска!$D$5:$D$16&gt;=JZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KA10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KA$5)*(Отпуска!$D$5:$D$17&gt;=KA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KA$5)*(Отпуска!$D$5:$D$16&gt;=KA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KB10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KB$5)*(Отпуска!$D$5:$D$17&gt;=KB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KB$5)*(Отпуска!$D$5:$D$16&gt;=KB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KC10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KC$5)*(Отпуска!$D$5:$D$17&gt;=KC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KC$5)*(Отпуска!$D$5:$D$16&gt;=KC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KD10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KD$5)*(Отпуска!$D$5:$D$17&gt;=KD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KD$5)*(Отпуска!$D$5:$D$16&gt;=KD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KE10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KE$5)*(Отпуска!$D$5:$D$17&gt;=KE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KE$5)*(Отпуска!$D$5:$D$16&gt;=KE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KF10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KF$5)*(Отпуска!$D$5:$D$17&gt;=KF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KF$5)*(Отпуска!$D$5:$D$16&gt;=KF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KG10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KG$5)*(Отпуска!$D$5:$D$17&gt;=KG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KG$5)*(Отпуска!$D$5:$D$16&gt;=KG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KH10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KH$5)*(Отпуска!$D$5:$D$17&gt;=KH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KH$5)*(Отпуска!$D$5:$D$16&gt;=KH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KI10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KI$5)*(Отпуска!$D$5:$D$17&gt;=KI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KI$5)*(Отпуска!$D$5:$D$16&gt;=KI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KJ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KJ$5)*(Отпуска!$D$5:$D$17&gt;=KJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KJ$5)*(Отпуска!$D$5:$D$16&gt;=KJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KK10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KK$5)*(Отпуска!$D$5:$D$17&gt;=KK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KK$5)*(Отпуска!$D$5:$D$16&gt;=KK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KL10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KL$5)*(Отпуска!$D$5:$D$17&gt;=KL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KL$5)*(Отпуска!$D$5:$D$16&gt;=KL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KM10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KM$5)*(Отпуска!$D$5:$D$17&gt;=KM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KM$5)*(Отпуска!$D$5:$D$16&gt;=KM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KN10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KN$5)*(Отпуска!$D$5:$D$17&gt;=KN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KN$5)*(Отпуска!$D$5:$D$16&gt;=KN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KO10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KO$5)*(Отпуска!$D$5:$D$17&gt;=KO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KO$5)*(Отпуска!$D$5:$D$16&gt;=KO$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="KP10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KP$5)*(Отпуска!$D$5:$D$17&gt;=KP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KP$5)*(Отпуска!$D$5:$D$16&gt;=KP$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="KQ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KQ$5)*(Отпуска!$D$5:$D$17&gt;=KQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KQ$5)*(Отпуска!$D$5:$D$16&gt;=KQ$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="KR10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KR$5)*(Отпуска!$D$5:$D$17&gt;=KR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KR$5)*(Отпуска!$D$5:$D$16&gt;=KR$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="KS10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KS$5)*(Отпуска!$D$5:$D$17&gt;=KS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KS$5)*(Отпуска!$D$5:$D$16&gt;=KS$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="KT10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KT$5)*(Отпуска!$D$5:$D$17&gt;=KT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KT$5)*(Отпуска!$D$5:$D$16&gt;=KT$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="KU10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KU$5)*(Отпуска!$D$5:$D$17&gt;=KU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KU$5)*(Отпуска!$D$5:$D$16&gt;=KU$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="KV10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KV$5)*(Отпуска!$D$5:$D$17&gt;=KV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KV$5)*(Отпуска!$D$5:$D$16&gt;=KV$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="KW10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KW$5)*(Отпуска!$D$5:$D$17&gt;=KW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KW$5)*(Отпуска!$D$5:$D$16&gt;=KW$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="KX10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KX$5)*(Отпуска!$D$5:$D$17&gt;=KX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KX$5)*(Отпуска!$D$5:$D$16&gt;=KX$5))&gt;0,"О","")</f>
         <v>О</v>
       </c>
       <c r="KY10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KY$5)*(Отпуска!$D$5:$D$17&gt;=KY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KY$5)*(Отпуска!$D$5:$D$16&gt;=KY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="KZ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=KZ$5)*(Отпуска!$D$5:$D$17&gt;=KZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=KZ$5)*(Отпуска!$D$5:$D$16&gt;=KZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LA10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LA$5)*(Отпуска!$D$5:$D$17&gt;=LA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LA$5)*(Отпуска!$D$5:$D$16&gt;=LA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LB10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LB$5)*(Отпуска!$D$5:$D$17&gt;=LB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LB$5)*(Отпуска!$D$5:$D$16&gt;=LB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LC10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LC$5)*(Отпуска!$D$5:$D$17&gt;=LC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LC$5)*(Отпуска!$D$5:$D$16&gt;=LC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LD10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LD$5)*(Отпуска!$D$5:$D$17&gt;=LD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LD$5)*(Отпуска!$D$5:$D$16&gt;=LD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LE10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LE$5)*(Отпуска!$D$5:$D$17&gt;=LE$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LE$5)*(Отпуска!$D$5:$D$16&gt;=LE$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LF10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LF$5)*(Отпуска!$D$5:$D$17&gt;=LF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LF$5)*(Отпуска!$D$5:$D$16&gt;=LF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LG10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LG$5)*(Отпуска!$D$5:$D$17&gt;=LG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LG$5)*(Отпуска!$D$5:$D$16&gt;=LG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LH10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LH$5)*(Отпуска!$D$5:$D$17&gt;=LH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LH$5)*(Отпуска!$D$5:$D$16&gt;=LH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LI10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LI$5)*(Отпуска!$D$5:$D$17&gt;=LI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LI$5)*(Отпуска!$D$5:$D$16&gt;=LI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LJ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LJ$5)*(Отпуска!$D$5:$D$17&gt;=LJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LJ$5)*(Отпуска!$D$5:$D$16&gt;=LJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LK10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LK$5)*(Отпуска!$D$5:$D$17&gt;=LK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LK$5)*(Отпуска!$D$5:$D$16&gt;=LK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LL10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LL$5)*(Отпуска!$D$5:$D$17&gt;=LL$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LL$5)*(Отпуска!$D$5:$D$16&gt;=LL$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LM10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LM$5)*(Отпуска!$D$5:$D$17&gt;=LM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LM$5)*(Отпуска!$D$5:$D$16&gt;=LM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LN10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LN$5)*(Отпуска!$D$5:$D$17&gt;=LN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LN$5)*(Отпуска!$D$5:$D$16&gt;=LN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LO10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LO$5)*(Отпуска!$D$5:$D$17&gt;=LO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LO$5)*(Отпуска!$D$5:$D$16&gt;=LO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LP10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LP$5)*(Отпуска!$D$5:$D$17&gt;=LP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LP$5)*(Отпуска!$D$5:$D$16&gt;=LP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LQ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LQ$5)*(Отпуска!$D$5:$D$17&gt;=LQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LQ$5)*(Отпуска!$D$5:$D$16&gt;=LQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LR10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LR$5)*(Отпуска!$D$5:$D$17&gt;=LR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LR$5)*(Отпуска!$D$5:$D$16&gt;=LR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LS10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LS$5)*(Отпуска!$D$5:$D$17&gt;=LS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LS$5)*(Отпуска!$D$5:$D$16&gt;=LS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LT10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LT$5)*(Отпуска!$D$5:$D$17&gt;=LT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LT$5)*(Отпуска!$D$5:$D$16&gt;=LT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LU10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LU$5)*(Отпуска!$D$5:$D$17&gt;=LU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LU$5)*(Отпуска!$D$5:$D$16&gt;=LU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LV10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LV$5)*(Отпуска!$D$5:$D$17&gt;=LV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LV$5)*(Отпуска!$D$5:$D$16&gt;=LV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LW10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LW$5)*(Отпуска!$D$5:$D$17&gt;=LW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LW$5)*(Отпуска!$D$5:$D$16&gt;=LW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LX10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LX$5)*(Отпуска!$D$5:$D$17&gt;=LX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LX$5)*(Отпуска!$D$5:$D$16&gt;=LX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LY10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LY$5)*(Отпуска!$D$5:$D$17&gt;=LY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LY$5)*(Отпуска!$D$5:$D$16&gt;=LY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="LZ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=LZ$5)*(Отпуска!$D$5:$D$17&gt;=LZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=LZ$5)*(Отпуска!$D$5:$D$16&gt;=LZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MA10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MA$5)*(Отпуска!$D$5:$D$17&gt;=MA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MA$5)*(Отпуска!$D$5:$D$16&gt;=MA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MB10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MB$5)*(Отпуска!$D$5:$D$17&gt;=MB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MB$5)*(Отпуска!$D$5:$D$16&gt;=MB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MC10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MC$5)*(Отпуска!$D$5:$D$17&gt;=MC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MC$5)*(Отпуска!$D$5:$D$16&gt;=MC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MD10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MD$5)*(Отпуска!$D$5:$D$17&gt;=MD$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MD$5)*(Отпуска!$D$5:$D$16&gt;=MD$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ME10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=ME$5)*(Отпуска!$D$5:$D$17&gt;=ME$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=ME$5)*(Отпуска!$D$5:$D$16&gt;=ME$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MF10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MF$5)*(Отпуска!$D$5:$D$17&gt;=MF$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MF$5)*(Отпуска!$D$5:$D$16&gt;=MF$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MG10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MG$5)*(Отпуска!$D$5:$D$17&gt;=MG$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MG$5)*(Отпуска!$D$5:$D$16&gt;=MG$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MH10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MH$5)*(Отпуска!$D$5:$D$17&gt;=MH$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MH$5)*(Отпуска!$D$5:$D$16&gt;=MH$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MI10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MI$5)*(Отпуска!$D$5:$D$17&gt;=MI$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MI$5)*(Отпуска!$D$5:$D$16&gt;=MI$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MJ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MJ$5)*(Отпуска!$D$5:$D$17&gt;=MJ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MJ$5)*(Отпуска!$D$5:$D$16&gt;=MJ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MK10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MK$5)*(Отпуска!$D$5:$D$17&gt;=MK$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MK$5)*(Отпуска!$D$5:$D$16&gt;=MK$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ML10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=ML$5)*(Отпуска!$D$5:$D$17&gt;=ML$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=ML$5)*(Отпуска!$D$5:$D$16&gt;=ML$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MM10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MM$5)*(Отпуска!$D$5:$D$17&gt;=MM$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MM$5)*(Отпуска!$D$5:$D$16&gt;=MM$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MN10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MN$5)*(Отпуска!$D$5:$D$17&gt;=MN$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MN$5)*(Отпуска!$D$5:$D$16&gt;=MN$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MO10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MO$5)*(Отпуска!$D$5:$D$17&gt;=MO$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MO$5)*(Отпуска!$D$5:$D$16&gt;=MO$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MP10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MP$5)*(Отпуска!$D$5:$D$17&gt;=MP$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MP$5)*(Отпуска!$D$5:$D$16&gt;=MP$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MQ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MQ$5)*(Отпуска!$D$5:$D$17&gt;=MQ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MQ$5)*(Отпуска!$D$5:$D$16&gt;=MQ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MR10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MR$5)*(Отпуска!$D$5:$D$17&gt;=MR$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MR$5)*(Отпуска!$D$5:$D$16&gt;=MR$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MS10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MS$5)*(Отпуска!$D$5:$D$17&gt;=MS$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MS$5)*(Отпуска!$D$5:$D$16&gt;=MS$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MT10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MT$5)*(Отпуска!$D$5:$D$17&gt;=MT$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MT$5)*(Отпуска!$D$5:$D$16&gt;=MT$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MU10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MU$5)*(Отпуска!$D$5:$D$17&gt;=MU$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MU$5)*(Отпуска!$D$5:$D$16&gt;=MU$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MV10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MV$5)*(Отпуска!$D$5:$D$17&gt;=MV$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MV$5)*(Отпуска!$D$5:$D$16&gt;=MV$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MW10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MW$5)*(Отпуска!$D$5:$D$17&gt;=MW$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MW$5)*(Отпуска!$D$5:$D$16&gt;=MW$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MX10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MX$5)*(Отпуска!$D$5:$D$17&gt;=MX$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MX$5)*(Отпуска!$D$5:$D$16&gt;=MX$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MY10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MY$5)*(Отпуска!$D$5:$D$17&gt;=MY$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MY$5)*(Отпуска!$D$5:$D$16&gt;=MY$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="MZ10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=MZ$5)*(Отпуска!$D$5:$D$17&gt;=MZ$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=MZ$5)*(Отпуска!$D$5:$D$16&gt;=MZ$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="NA10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=NA$5)*(Отпуска!$D$5:$D$17&gt;=NA$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=NA$5)*(Отпуска!$D$5:$D$16&gt;=NA$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="NB10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=NB$5)*(Отпуска!$D$5:$D$17&gt;=NB$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=NB$5)*(Отпуска!$D$5:$D$16&gt;=NB$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="NC10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=NC$5)*(Отпуска!$D$5:$D$17&gt;=NC$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=NC$5)*(Отпуска!$D$5:$D$16&gt;=NC$5))&gt;0,"О","")</f>
         <v/>
       </c>
       <c r="ND10" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$17=$A10)*(Отпуска!$B$5:$B$17&lt;=ND$5)*(Отпуска!$D$5:$D$17&gt;=ND$5))&gt;0,"О","")</f>
+        <f aca="false">IF(SUMPRODUCT((Отпуска!$A$5:$A$16=$A10)*(Отпуска!$B$5:$B$16&lt;=ND$5)*(Отпуска!$D$5:$D$16&gt;=ND$5))&gt;0,"О","")</f>
         <v/>
       </c>
     </row>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="B11" s="15" t="n">
         <f aca="false">COUNTIF(D11:ND11,"&gt;=2")</f>
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>22</v>
@@ -10266,47 +10266,47 @@
       </c>
       <c r="AW11" s="17" t="n">
         <f aca="false">COUNTIF(AW7:AW10,"О")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX11" s="17" t="n">
         <f aca="false">COUNTIF(AX7:AX10,"О")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY11" s="17" t="n">
         <f aca="false">COUNTIF(AY7:AY10,"О")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ11" s="17" t="n">
         <f aca="false">COUNTIF(AZ7:AZ10,"О")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA11" s="17" t="n">
         <f aca="false">COUNTIF(BA7:BA10,"О")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB11" s="17" t="n">
         <f aca="false">COUNTIF(BB7:BB10,"О")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC11" s="17" t="n">
         <f aca="false">COUNTIF(BC7:BC10,"О")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD11" s="17" t="n">
         <f aca="false">COUNTIF(BD7:BD10,"О")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE11" s="17" t="n">
         <f aca="false">COUNTIF(BE7:BE10,"О")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF11" s="17" t="n">
         <f aca="false">COUNTIF(BF7:BF10,"О")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG11" s="17" t="n">
         <f aca="false">COUNTIF(BG7:BG10,"О")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH11" s="17" t="n">
         <f aca="false">COUNTIF(BH7:BH10,"О")</f>
@@ -10406,31 +10406,31 @@
       </c>
       <c r="CF11" s="17" t="n">
         <f aca="false">COUNTIF(CF7:CF10,"О")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CG11" s="17" t="n">
         <f aca="false">COUNTIF(CG7:CG10,"О")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CH11" s="17" t="n">
         <f aca="false">COUNTIF(CH7:CH10,"О")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CI11" s="17" t="n">
         <f aca="false">COUNTIF(CI7:CI10,"О")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CJ11" s="17" t="n">
         <f aca="false">COUNTIF(CJ7:CJ10,"О")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CK11" s="17" t="n">
         <f aca="false">COUNTIF(CK7:CK10,"О")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL11" s="17" t="n">
         <f aca="false">COUNTIF(CL7:CL10,"О")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM11" s="17" t="n">
         <f aca="false">COUNTIF(CM7:CM10,"О")</f>
@@ -10462,31 +10462,31 @@
       </c>
       <c r="CT11" s="17" t="n">
         <f aca="false">COUNTIF(CT7:CT10,"О")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU11" s="17" t="n">
         <f aca="false">COUNTIF(CU7:CU10,"О")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV11" s="17" t="n">
         <f aca="false">COUNTIF(CV7:CV10,"О")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CW11" s="17" t="n">
         <f aca="false">COUNTIF(CW7:CW10,"О")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CX11" s="17" t="n">
         <f aca="false">COUNTIF(CX7:CX10,"О")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY11" s="17" t="n">
         <f aca="false">COUNTIF(CY7:CY10,"О")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CZ11" s="17" t="n">
         <f aca="false">COUNTIF(CZ7:CZ10,"О")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DA11" s="17" t="n">
         <f aca="false">COUNTIF(DA7:DA10,"О")</f>
@@ -10646,47 +10646,47 @@
       </c>
       <c r="EN11" s="17" t="n">
         <f aca="false">COUNTIF(EN7:EN10,"О")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EO11" s="17" t="n">
         <f aca="false">COUNTIF(EO7:EO10,"О")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EP11" s="17" t="n">
         <f aca="false">COUNTIF(EP7:EP10,"О")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EQ11" s="17" t="n">
         <f aca="false">COUNTIF(EQ7:EQ10,"О")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ER11" s="17" t="n">
         <f aca="false">COUNTIF(ER7:ER10,"О")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ES11" s="17" t="n">
         <f aca="false">COUNTIF(ES7:ES10,"О")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ET11" s="17" t="n">
         <f aca="false">COUNTIF(ET7:ET10,"О")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EU11" s="17" t="n">
         <f aca="false">COUNTIF(EU7:EU10,"О")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EV11" s="17" t="n">
         <f aca="false">COUNTIF(EV7:EV10,"О")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EW11" s="17" t="n">
         <f aca="false">COUNTIF(EW7:EW10,"О")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EX11" s="17" t="n">
         <f aca="false">COUNTIF(EX7:EX10,"О")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EY11" s="17" t="n">
         <f aca="false">COUNTIF(EY7:EY10,"О")</f>
@@ -11620,7 +11620,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -11663,14 +11663,14 @@
         <v>17</v>
       </c>
       <c r="B5" s="21" t="n">
-        <v>46433</v>
+        <v>46511</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D5" s="23" t="n">
         <f aca="false">B5+C5-1</f>
-        <v>46443</v>
+        <v>46538</v>
       </c>
       <c r="F5" s="21" t="n">
         <v>46388</v>
@@ -11681,14 +11681,14 @@
         <v>17</v>
       </c>
       <c r="B6" s="21" t="n">
-        <v>46511</v>
+        <v>46601</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6" s="23" t="n">
         <f aca="false">B6+C6-1</f>
-        <v>46527</v>
+        <v>46619</v>
       </c>
       <c r="F6" s="21" t="n">
         <v>46389</v>
@@ -11699,14 +11699,14 @@
         <v>17</v>
       </c>
       <c r="B7" s="21" t="n">
-        <v>46601</v>
+        <v>46745</v>
       </c>
       <c r="C7" s="22" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D7" s="23" t="n">
         <f aca="false">B7+C7-1</f>
-        <v>46619</v>
+        <v>46752</v>
       </c>
       <c r="F7" s="21" t="n">
         <v>46390</v>
@@ -11714,17 +11714,17 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="21" t="n">
-        <v>46745</v>
+        <v>46455</v>
       </c>
       <c r="C8" s="22" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D8" s="23" t="n">
         <f aca="false">B8+C8-1</f>
-        <v>46752</v>
+        <v>46467</v>
       </c>
       <c r="F8" s="21" t="n">
         <v>46391</v>
@@ -11735,14 +11735,14 @@
         <v>18</v>
       </c>
       <c r="B9" s="21" t="n">
-        <v>46455</v>
+        <v>46538</v>
       </c>
       <c r="C9" s="22" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D9" s="23" t="n">
         <f aca="false">B9+C9-1</f>
-        <v>46467</v>
+        <v>46571</v>
       </c>
       <c r="F9" s="21" t="n">
         <v>46392</v>
@@ -11753,14 +11753,14 @@
         <v>18</v>
       </c>
       <c r="B10" s="21" t="n">
-        <v>46538</v>
+        <v>46745</v>
       </c>
       <c r="C10" s="22" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D10" s="23" t="n">
         <f aca="false">B10+C10-1</f>
-        <v>46571</v>
+        <v>46752</v>
       </c>
       <c r="F10" s="21" t="n">
         <v>46393</v>
@@ -11768,17 +11768,17 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="21" t="n">
-        <v>46745</v>
+        <v>46482</v>
       </c>
       <c r="C11" s="22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D11" s="23" t="n">
         <f aca="false">B11+C11-1</f>
-        <v>46752</v>
+        <v>46488</v>
       </c>
       <c r="F11" s="21" t="n">
         <v>46394</v>
@@ -11789,14 +11789,14 @@
         <v>19</v>
       </c>
       <c r="B12" s="21" t="n">
-        <v>46468</v>
+        <v>46580</v>
       </c>
       <c r="C12" s="22" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="D12" s="23" t="n">
         <f aca="false">B12+C12-1</f>
-        <v>46474</v>
+        <v>46612</v>
       </c>
       <c r="F12" s="21" t="n">
         <v>46395</v>
@@ -11807,14 +11807,14 @@
         <v>19</v>
       </c>
       <c r="B13" s="21" t="n">
-        <v>46580</v>
+        <v>46737</v>
       </c>
       <c r="C13" s="22" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D13" s="23" t="n">
         <f aca="false">B13+C13-1</f>
-        <v>46612</v>
+        <v>46751</v>
       </c>
       <c r="F13" s="21" t="n">
         <v>46441</v>
@@ -11822,17 +11822,17 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="21" t="n">
-        <v>46737</v>
+        <v>46455</v>
       </c>
       <c r="C14" s="22" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D14" s="23" t="n">
         <f aca="false">B14+C14-1</f>
-        <v>46751</v>
+        <v>46472</v>
       </c>
       <c r="F14" s="21" t="n">
         <v>46454</v>
@@ -11843,14 +11843,14 @@
         <v>20</v>
       </c>
       <c r="B15" s="21" t="n">
-        <v>46455</v>
+        <v>46553</v>
       </c>
       <c r="C15" s="22" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D15" s="23" t="n">
         <f aca="false">B15+C15-1</f>
-        <v>46472</v>
+        <v>46581</v>
       </c>
       <c r="F15" s="21" t="n">
         <v>46508</v>
@@ -11861,53 +11861,47 @@
         <v>20</v>
       </c>
       <c r="B16" s="21" t="n">
-        <v>46553</v>
+        <v>46685</v>
       </c>
       <c r="C16" s="22" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D16" s="23" t="n">
         <f aca="false">B16+C16-1</f>
-        <v>46581</v>
+        <v>46694</v>
       </c>
       <c r="F16" s="21" t="n">
         <v>46516</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="21" t="n">
-        <v>46685</v>
-      </c>
-      <c r="C17" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="D17" s="23" t="n">
-        <f aca="false">B17+C17-1</f>
-        <v>46694</v>
-      </c>
       <c r="F17" s="21" t="n">
         <v>46550</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>29</v>
+      </c>
       <c r="F18" s="21" t="n">
         <v>46695</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
-        <v>29</v>
+      <c r="A19" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <f aca="false">SUMIF($A$5:$A$16,A19,$C$5:$C$16)</f>
+        <v>55</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" s="25" t="n">
-        <f aca="false">SUMIF($A$5:$A$17,A20,$C$5:$C$17)</f>
+        <f aca="false">SUMIF($A$5:$A$16,A20,$C$5:$C$16)</f>
         <v>55</v>
       </c>
       <c r="F20" s="26" t="s">
@@ -11916,28 +11910,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C21" s="25" t="n">
-        <f aca="false">SUMIF($A$5:$A$17,A21,$C$5:$C$17)</f>
+        <f aca="false">SUMIF($A$5:$A$16,A21,$C$5:$C$16)</f>
         <v>55</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C22" s="25" t="n">
-        <f aca="false">SUMIF($A$5:$A$17,A22,$C$5:$C$17)</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="25" t="n">
-        <f aca="false">SUMIF($A$5:$A$17,A23,$C$5:$C$17)</f>
+        <f aca="false">SUMIF($A$5:$A$16,A22,$C$5:$C$16)</f>
         <v>57</v>
       </c>
     </row>
